--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/house_model_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D40E9EC-05BB-034C-87EB-6E364C09151E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C13CF08F-5783-C24A-82AD-6C50D5405FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -39,8 +39,29 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={64FF4A2E-41B6-D242-BD56-86F00F3F130C}</author>
+  </authors>
+  <commentList>
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{64FF4A2E-41B6-D242-BD56-86F00F3F130C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Low: &lt;25%
+Medium: 25-35%
+High: 35-45%
+Very High: &gt;45%</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2066" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2293" uniqueCount="695">
   <si>
     <t>State</t>
   </si>
@@ -2098,6 +2119,33 @@
   </si>
   <si>
     <t>Urban South</t>
+  </si>
+  <si>
+    <t>College Share Tier</t>
+  </si>
+  <si>
+    <t>White Noncollege Share Tier</t>
+  </si>
+  <si>
+    <t>Black Share Tier</t>
+  </si>
+  <si>
+    <t>Hispanic Share Tier</t>
+  </si>
+  <si>
+    <t>Median Income Tier</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Very High</t>
   </si>
 </sst>
 </file>
@@ -2107,7 +2155,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2134,6 +2182,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2181,6 +2235,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Ben Yelin" id="{D1F88E81-7DBF-1B4A-907A-3BF92BC08466}" userId="07346eb483d9d83d" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2498,9 +2558,20 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="L1" dT="2026-05-30T12:46:54.78" personId="{D1F88E81-7DBF-1B4A-907A-3BF92BC08466}" id="{64FF4A2E-41B6-D242-BD56-86F00F3F130C}">
+    <text>Low: &lt;25%
+Medium: 25-35%
+High: 35-45%
+Very High: &gt;45%</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09FA142F-1ED2-0141-A92D-14DC2DE06B34}">
-  <dimension ref="A1:K436"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09FA142F-1ED2-0141-A92D-14DC2DE06B34}">
+  <dimension ref="A1:Q436"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.1640625" customWidth="1"/>
@@ -2508,14 +2579,19 @@
     <col min="3" max="3" width="29.83203125" customWidth="1"/>
     <col min="4" max="5" width="20.6640625" style="3" customWidth="1"/>
     <col min="6" max="6" width="30.1640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="25.33203125" customWidth="1"/>
-    <col min="8" max="8" width="24.1640625" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" customWidth="1"/>
-    <col min="10" max="10" width="18.6640625" customWidth="1"/>
-    <col min="11" max="11" width="30.1640625" customWidth="1"/>
+    <col min="7" max="7" width="25.33203125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="24.1640625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
+    <col min="12" max="12" width="21" customWidth="1"/>
+    <col min="13" max="13" width="29.1640625" customWidth="1"/>
+    <col min="14" max="14" width="19.5" customWidth="1"/>
+    <col min="15" max="15" width="21.33203125" customWidth="1"/>
+    <col min="16" max="16" width="23.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2549,8 +2625,24 @@
       <c r="K1" s="2" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L1" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -2578,7 +2670,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -2606,7 +2698,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -2640,7 +2732,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -2674,7 +2766,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -2702,7 +2794,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -2733,7 +2825,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -2761,7 +2853,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>613</v>
       </c>
@@ -2789,7 +2881,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>614</v>
       </c>
@@ -2817,7 +2909,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>614</v>
       </c>
@@ -2845,7 +2937,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>614</v>
       </c>
@@ -2873,7 +2965,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>614</v>
       </c>
@@ -2901,7 +2993,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>614</v>
       </c>
@@ -2929,7 +3021,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>614</v>
       </c>
@@ -2957,7 +3049,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>614</v>
       </c>
@@ -2985,7 +3077,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>614</v>
       </c>
@@ -3013,7 +3105,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>614</v>
       </c>
@@ -3041,7 +3133,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>615</v>
       </c>
@@ -3074,8 +3166,11 @@
       <c r="J19" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L19" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>615</v>
       </c>
@@ -3108,8 +3203,11 @@
       <c r="J20" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L20" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>615</v>
       </c>
@@ -3142,8 +3240,11 @@
       <c r="J21" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L21" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>615</v>
       </c>
@@ -3176,8 +3277,11 @@
       <c r="J22" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L22" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>616</v>
       </c>
@@ -3204,8 +3308,11 @@
       <c r="J23" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L23" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>616</v>
       </c>
@@ -3232,8 +3339,11 @@
       <c r="J24" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L24" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>616</v>
       </c>
@@ -3260,8 +3370,11 @@
       <c r="J25" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L25" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>616</v>
       </c>
@@ -3288,8 +3401,11 @@
       <c r="J26" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L26" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>616</v>
       </c>
@@ -3316,8 +3432,11 @@
       <c r="J27" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L27" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>616</v>
       </c>
@@ -3344,8 +3463,11 @@
       <c r="J28" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L28" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>616</v>
       </c>
@@ -3372,8 +3494,11 @@
       <c r="J29" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L29" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>616</v>
       </c>
@@ -3400,8 +3525,11 @@
       <c r="J30" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L30" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>616</v>
       </c>
@@ -3428,8 +3556,11 @@
       <c r="J31" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L31" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>616</v>
       </c>
@@ -3456,8 +3587,11 @@
       <c r="J32" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L32" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>616</v>
       </c>
@@ -3484,8 +3618,11 @@
       <c r="J33" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L33" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>616</v>
       </c>
@@ -3512,8 +3649,11 @@
       <c r="J34" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L34" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>616</v>
       </c>
@@ -3540,8 +3680,11 @@
       <c r="J35" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L35" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>616</v>
       </c>
@@ -3568,8 +3711,11 @@
       <c r="J36" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L36" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>616</v>
       </c>
@@ -3596,8 +3742,11 @@
       <c r="J37" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L37" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>616</v>
       </c>
@@ -3624,8 +3773,11 @@
       <c r="J38" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L38" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>616</v>
       </c>
@@ -3652,8 +3804,11 @@
       <c r="J39" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L39" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>616</v>
       </c>
@@ -3680,8 +3835,11 @@
       <c r="J40" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L40" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>616</v>
       </c>
@@ -3708,8 +3866,11 @@
       <c r="J41" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L41" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>616</v>
       </c>
@@ -3736,8 +3897,11 @@
       <c r="J42" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L42" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>616</v>
       </c>
@@ -3764,8 +3928,11 @@
       <c r="J43" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L43" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>616</v>
       </c>
@@ -3792,8 +3959,11 @@
       <c r="J44" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L44" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>616</v>
       </c>
@@ -3820,8 +3990,11 @@
       <c r="J45" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L45" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>616</v>
       </c>
@@ -3848,8 +4021,11 @@
       <c r="J46" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L46" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>616</v>
       </c>
@@ -3876,8 +4052,11 @@
       <c r="J47" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L47" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>616</v>
       </c>
@@ -3904,8 +4083,11 @@
       <c r="J48" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L48" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>616</v>
       </c>
@@ -3932,8 +4114,11 @@
       <c r="J49" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L49" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>616</v>
       </c>
@@ -3960,8 +4145,11 @@
       <c r="J50" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L50" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>616</v>
       </c>
@@ -3988,8 +4176,11 @@
       <c r="J51" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L51" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>616</v>
       </c>
@@ -4016,8 +4207,11 @@
       <c r="J52" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L52" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>616</v>
       </c>
@@ -4044,8 +4238,11 @@
       <c r="J53" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L53" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>616</v>
       </c>
@@ -4072,8 +4269,11 @@
       <c r="J54" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L54" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>616</v>
       </c>
@@ -4100,8 +4300,11 @@
       <c r="J55" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L55" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>616</v>
       </c>
@@ -4128,8 +4331,11 @@
       <c r="J56" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L56" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>616</v>
       </c>
@@ -4156,8 +4362,11 @@
       <c r="J57" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L57" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>616</v>
       </c>
@@ -4184,8 +4393,11 @@
       <c r="J58" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L58" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>616</v>
       </c>
@@ -4212,8 +4424,11 @@
       <c r="J59" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L59" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>616</v>
       </c>
@@ -4240,8 +4455,11 @@
       <c r="J60" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L60" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>616</v>
       </c>
@@ -4268,8 +4486,11 @@
       <c r="J61" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L61" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>616</v>
       </c>
@@ -4296,8 +4517,11 @@
       <c r="J62" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L62" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>616</v>
       </c>
@@ -4324,8 +4548,11 @@
       <c r="J63" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L63" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>616</v>
       </c>
@@ -4352,8 +4579,11 @@
       <c r="J64" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L64" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>616</v>
       </c>
@@ -4380,8 +4610,11 @@
       <c r="J65" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L65" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>616</v>
       </c>
@@ -4408,8 +4641,11 @@
       <c r="J66" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L66" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>616</v>
       </c>
@@ -4436,8 +4672,11 @@
       <c r="J67" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L67" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>616</v>
       </c>
@@ -4464,8 +4703,11 @@
       <c r="J68" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L68" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>616</v>
       </c>
@@ -4492,8 +4734,11 @@
       <c r="J69" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L69" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>616</v>
       </c>
@@ -4520,8 +4765,11 @@
       <c r="J70" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L70" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>616</v>
       </c>
@@ -4548,8 +4796,11 @@
       <c r="J71" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L71" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>616</v>
       </c>
@@ -4576,8 +4827,11 @@
       <c r="J72" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L72" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>616</v>
       </c>
@@ -4604,8 +4858,11 @@
       <c r="J73" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L73" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>616</v>
       </c>
@@ -4632,8 +4889,11 @@
       <c r="J74" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L74" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>617</v>
       </c>
@@ -4660,8 +4920,11 @@
       <c r="J75" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L75" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>617</v>
       </c>
@@ -4688,8 +4951,11 @@
       <c r="J76" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L76" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>617</v>
       </c>
@@ -4716,8 +4982,11 @@
       <c r="J77" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L77" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>617</v>
       </c>
@@ -4744,8 +5013,11 @@
       <c r="J78" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L78" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>617</v>
       </c>
@@ -4772,8 +5044,11 @@
       <c r="J79" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L79" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>617</v>
       </c>
@@ -4800,8 +5075,11 @@
       <c r="J80" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L80" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>617</v>
       </c>
@@ -4828,8 +5106,11 @@
       <c r="J81" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L81" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>617</v>
       </c>
@@ -4856,8 +5137,11 @@
       <c r="J82" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L82" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>618</v>
       </c>
@@ -4884,8 +5168,11 @@
       <c r="J83" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L83" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>618</v>
       </c>
@@ -4912,8 +5199,11 @@
       <c r="J84" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L84" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>618</v>
       </c>
@@ -4940,8 +5230,11 @@
       <c r="J85" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L85" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>618</v>
       </c>
@@ -4968,8 +5261,11 @@
       <c r="J86" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L86" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>618</v>
       </c>
@@ -4996,8 +5292,11 @@
       <c r="J87" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L87" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>619</v>
       </c>
@@ -5024,8 +5323,11 @@
       <c r="J88" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L88" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>620</v>
       </c>
@@ -5053,8 +5355,11 @@
       <c r="J89" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L89" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>620</v>
       </c>
@@ -5082,8 +5387,11 @@
       <c r="J90" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L90" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>620</v>
       </c>
@@ -5111,8 +5419,11 @@
       <c r="J91" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L91" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>620</v>
       </c>
@@ -5140,8 +5451,11 @@
       <c r="J92" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L92" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>620</v>
       </c>
@@ -5169,8 +5483,11 @@
       <c r="J93" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L93" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>620</v>
       </c>
@@ -5198,8 +5515,11 @@
       <c r="J94" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L94" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>620</v>
       </c>
@@ -5227,8 +5547,11 @@
       <c r="J95" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L95" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>620</v>
       </c>
@@ -5256,8 +5579,11 @@
       <c r="J96" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L96" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>620</v>
       </c>
@@ -5285,8 +5611,11 @@
       <c r="J97" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L97" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>620</v>
       </c>
@@ -5314,8 +5643,11 @@
       <c r="J98" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L98" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>620</v>
       </c>
@@ -5343,8 +5675,11 @@
       <c r="J99" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L99" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>620</v>
       </c>
@@ -5372,8 +5707,11 @@
       <c r="J100" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L100" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>620</v>
       </c>
@@ -5401,8 +5739,11 @@
       <c r="J101" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L101" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>620</v>
       </c>
@@ -5430,8 +5771,11 @@
       <c r="J102" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L102" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>620</v>
       </c>
@@ -5459,8 +5803,11 @@
       <c r="J103" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L103" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>620</v>
       </c>
@@ -5488,8 +5835,11 @@
       <c r="J104" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L104" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>620</v>
       </c>
@@ -5517,8 +5867,11 @@
       <c r="J105" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L105" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>620</v>
       </c>
@@ -5546,8 +5899,11 @@
       <c r="J106" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L106" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>620</v>
       </c>
@@ -5575,8 +5931,11 @@
       <c r="J107" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L107" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>620</v>
       </c>
@@ -5604,8 +5963,11 @@
       <c r="J108" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L108" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>620</v>
       </c>
@@ -5633,8 +5995,11 @@
       <c r="J109" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L109" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>620</v>
       </c>
@@ -5662,8 +6027,11 @@
       <c r="J110" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L110" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>620</v>
       </c>
@@ -5691,8 +6059,11 @@
       <c r="J111" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L111" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>620</v>
       </c>
@@ -5720,8 +6091,11 @@
       <c r="J112" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L112" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>620</v>
       </c>
@@ -5749,8 +6123,11 @@
       <c r="J113" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L113" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>620</v>
       </c>
@@ -5778,8 +6155,11 @@
       <c r="J114" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L114" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>620</v>
       </c>
@@ -5807,8 +6187,11 @@
       <c r="J115" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L115" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>620</v>
       </c>
@@ -5836,8 +6219,11 @@
       <c r="J116" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L116" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>621</v>
       </c>
@@ -5864,8 +6250,11 @@
       <c r="J117" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L117" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>621</v>
       </c>
@@ -5898,8 +6287,11 @@
       <c r="J118" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L118" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>621</v>
       </c>
@@ -5932,8 +6324,11 @@
       <c r="J119" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L119" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>621</v>
       </c>
@@ -5966,8 +6361,11 @@
       <c r="J120" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L120" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>621</v>
       </c>
@@ -6000,8 +6398,11 @@
       <c r="J121" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L121" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>621</v>
       </c>
@@ -6031,8 +6432,11 @@
       <c r="J122" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L122" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>621</v>
       </c>
@@ -6062,8 +6466,11 @@
       <c r="J123" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L123" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>621</v>
       </c>
@@ -6096,8 +6503,11 @@
       <c r="J124" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L124" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>621</v>
       </c>
@@ -6130,8 +6540,11 @@
       <c r="J125" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L125" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>621</v>
       </c>
@@ -6161,8 +6574,11 @@
       <c r="J126" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L126" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>621</v>
       </c>
@@ -6192,8 +6608,11 @@
       <c r="J127" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L127" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>621</v>
       </c>
@@ -6223,8 +6642,11 @@
       <c r="J128" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L128" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>621</v>
       </c>
@@ -6257,8 +6679,11 @@
       <c r="J129" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L129" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>621</v>
       </c>
@@ -6291,8 +6716,11 @@
       <c r="J130" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L130" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>622</v>
       </c>
@@ -6319,8 +6747,11 @@
       <c r="J131" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L131" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>622</v>
       </c>
@@ -6347,8 +6778,11 @@
       <c r="J132" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L132" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>623</v>
       </c>
@@ -6381,8 +6815,11 @@
       <c r="J133" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L133" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>623</v>
       </c>
@@ -6415,8 +6852,11 @@
       <c r="J134" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L134" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>624</v>
       </c>
@@ -6449,8 +6889,11 @@
       <c r="J135" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L135" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>624</v>
       </c>
@@ -6483,8 +6926,11 @@
       <c r="J136" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L136" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>624</v>
       </c>
@@ -6517,8 +6963,11 @@
       <c r="J137" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L137" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>624</v>
       </c>
@@ -6551,8 +7000,11 @@
       <c r="J138" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L138" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>624</v>
       </c>
@@ -6585,8 +7037,11 @@
       <c r="J139" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L139" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>624</v>
       </c>
@@ -6619,8 +7074,11 @@
       <c r="J140" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L140" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>624</v>
       </c>
@@ -6653,8 +7111,11 @@
       <c r="J141" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L141" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>624</v>
       </c>
@@ -6687,8 +7148,11 @@
       <c r="J142" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L142" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>624</v>
       </c>
@@ -6721,8 +7185,11 @@
       <c r="J143" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L143" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>624</v>
       </c>
@@ -6755,8 +7222,11 @@
       <c r="J144" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L144" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>624</v>
       </c>
@@ -6789,8 +7259,11 @@
       <c r="J145" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L145" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>624</v>
       </c>
@@ -6823,8 +7296,11 @@
       <c r="J146" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L146" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>624</v>
       </c>
@@ -6857,8 +7333,11 @@
       <c r="J147" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L147" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>624</v>
       </c>
@@ -6891,8 +7370,11 @@
       <c r="J148" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L148" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>624</v>
       </c>
@@ -6925,8 +7407,11 @@
       <c r="J149" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L149" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>624</v>
       </c>
@@ -6959,8 +7444,11 @@
       <c r="J150" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L150" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>624</v>
       </c>
@@ -6993,8 +7481,11 @@
       <c r="J151" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L151" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>625</v>
       </c>
@@ -7027,8 +7518,11 @@
       <c r="J152" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L152" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>625</v>
       </c>
@@ -7061,8 +7555,11 @@
       <c r="J153" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L153" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>625</v>
       </c>
@@ -7095,8 +7592,11 @@
       <c r="J154" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L154" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>625</v>
       </c>
@@ -7129,8 +7629,11 @@
       <c r="J155" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L155" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>625</v>
       </c>
@@ -7163,8 +7666,11 @@
       <c r="J156" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L156" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>625</v>
       </c>
@@ -7197,8 +7703,11 @@
       <c r="J157" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L157" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>625</v>
       </c>
@@ -7231,8 +7740,11 @@
       <c r="J158" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L158" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>625</v>
       </c>
@@ -7265,8 +7777,11 @@
       <c r="J159" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L159" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>625</v>
       </c>
@@ -7299,8 +7814,11 @@
       <c r="J160" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L160" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>626</v>
       </c>
@@ -7327,8 +7845,11 @@
       <c r="J161" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L161" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>626</v>
       </c>
@@ -7355,8 +7876,11 @@
       <c r="J162" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L162" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>626</v>
       </c>
@@ -7383,8 +7907,11 @@
       <c r="J163" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L163" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>626</v>
       </c>
@@ -7411,8 +7938,11 @@
       <c r="J164" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L164" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>627</v>
       </c>
@@ -7439,8 +7969,11 @@
       <c r="J165" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L165" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>627</v>
       </c>
@@ -7467,8 +8000,11 @@
       <c r="J166" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L166" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>627</v>
       </c>
@@ -7495,8 +8031,11 @@
       <c r="J167" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L167" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>627</v>
       </c>
@@ -7523,8 +8062,11 @@
       <c r="J168" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L168" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>628</v>
       </c>
@@ -7557,8 +8099,11 @@
       <c r="J169" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L169" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>628</v>
       </c>
@@ -7591,8 +8136,11 @@
       <c r="J170" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L170" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>628</v>
       </c>
@@ -7625,8 +8173,11 @@
       <c r="J171" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L171" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>628</v>
       </c>
@@ -7659,8 +8210,11 @@
       <c r="J172" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L172" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>628</v>
       </c>
@@ -7693,8 +8247,11 @@
       <c r="J173" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L173" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>628</v>
       </c>
@@ -7727,8 +8284,11 @@
       <c r="J174" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L174" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>629</v>
       </c>
@@ -7757,7 +8317,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>629</v>
       </c>
@@ -7786,7 +8346,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>629</v>
       </c>
@@ -7815,7 +8375,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>629</v>
       </c>
@@ -7844,7 +8404,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>629</v>
       </c>
@@ -7873,7 +8433,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>629</v>
       </c>
@@ -7902,7 +8462,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>630</v>
       </c>
@@ -7929,8 +8489,11 @@
       <c r="J181" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L181" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>630</v>
       </c>
@@ -7957,8 +8520,11 @@
       <c r="J182" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L182" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>631</v>
       </c>
@@ -7985,8 +8551,11 @@
       <c r="J183" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L183" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>631</v>
       </c>
@@ -8013,8 +8582,11 @@
       <c r="J184" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L184" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>631</v>
       </c>
@@ -8041,8 +8613,11 @@
       <c r="J185" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L185" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>631</v>
       </c>
@@ -8069,8 +8644,11 @@
       <c r="J186" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L186" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>631</v>
       </c>
@@ -8097,8 +8675,11 @@
       <c r="J187" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L187" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>631</v>
       </c>
@@ -8125,8 +8706,11 @@
       <c r="J188" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L188" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>631</v>
       </c>
@@ -8153,8 +8737,11 @@
       <c r="J189" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L189" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>631</v>
       </c>
@@ -8181,8 +8768,11 @@
       <c r="J190" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L190" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>632</v>
       </c>
@@ -8209,8 +8799,11 @@
       <c r="J191" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L191" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>632</v>
       </c>
@@ -8237,8 +8830,11 @@
       <c r="J192" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L192" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>632</v>
       </c>
@@ -8265,8 +8861,11 @@
       <c r="J193" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L193" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>632</v>
       </c>
@@ -8293,8 +8892,11 @@
       <c r="J194" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L194" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>632</v>
       </c>
@@ -8321,8 +8923,11 @@
       <c r="J195" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L195" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>632</v>
       </c>
@@ -8349,8 +8954,11 @@
       <c r="J196" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L196" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>632</v>
       </c>
@@ -8377,8 +8985,11 @@
       <c r="J197" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L197" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>632</v>
       </c>
@@ -8405,8 +9016,11 @@
       <c r="J198" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L198" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>632</v>
       </c>
@@ -8433,8 +9047,11 @@
       <c r="J199" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L199" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>633</v>
       </c>
@@ -8461,8 +9078,11 @@
       <c r="J200" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L200" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>633</v>
       </c>
@@ -8489,8 +9109,11 @@
       <c r="J201" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L201" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>633</v>
       </c>
@@ -8517,8 +9140,11 @@
       <c r="J202" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L202" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>633</v>
       </c>
@@ -8545,8 +9171,11 @@
       <c r="J203" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L203" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>633</v>
       </c>
@@ -8573,8 +9202,11 @@
       <c r="J204" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L204" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>633</v>
       </c>
@@ -8601,8 +9233,11 @@
       <c r="J205" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L205" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>633</v>
       </c>
@@ -8629,8 +9264,11 @@
       <c r="J206" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L206" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>633</v>
       </c>
@@ -8657,8 +9295,11 @@
       <c r="J207" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L207" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>633</v>
       </c>
@@ -8685,8 +9326,11 @@
       <c r="J208" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L208" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>633</v>
       </c>
@@ -8713,8 +9357,11 @@
       <c r="J209" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L209" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>633</v>
       </c>
@@ -8741,8 +9388,11 @@
       <c r="J210" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L210" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>633</v>
       </c>
@@ -8769,8 +9419,11 @@
       <c r="J211" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L211" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>633</v>
       </c>
@@ -8797,8 +9450,11 @@
       <c r="J212" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L212" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>634</v>
       </c>
@@ -8825,8 +9481,11 @@
       <c r="J213" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L213" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>634</v>
       </c>
@@ -8853,8 +9512,11 @@
       <c r="J214" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L214" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>634</v>
       </c>
@@ -8881,8 +9543,11 @@
       <c r="J215" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L215" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>634</v>
       </c>
@@ -8909,8 +9574,11 @@
       <c r="J216" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L216" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>634</v>
       </c>
@@ -8937,8 +9605,11 @@
       <c r="J217" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L217" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>634</v>
       </c>
@@ -8965,8 +9636,11 @@
       <c r="J218" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L218" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>634</v>
       </c>
@@ -8993,8 +9667,11 @@
       <c r="J219" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L219" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>634</v>
       </c>
@@ -9021,8 +9698,11 @@
       <c r="J220" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L220" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>635</v>
       </c>
@@ -9055,8 +9735,11 @@
       <c r="J221" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L221" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>635</v>
       </c>
@@ -9089,8 +9772,11 @@
       <c r="J222" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L222" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>635</v>
       </c>
@@ -9123,8 +9809,11 @@
       <c r="J223" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L223" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>635</v>
       </c>
@@ -9157,8 +9846,11 @@
       <c r="J224" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L224" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>636</v>
       </c>
@@ -9185,8 +9877,11 @@
       <c r="J225" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L225" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>636</v>
       </c>
@@ -9213,8 +9908,11 @@
       <c r="J226" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L226" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>636</v>
       </c>
@@ -9241,8 +9939,11 @@
       <c r="J227" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L227" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>636</v>
       </c>
@@ -9269,8 +9970,11 @@
       <c r="J228" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L228" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>636</v>
       </c>
@@ -9297,8 +10001,11 @@
       <c r="J229" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L229" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>636</v>
       </c>
@@ -9325,8 +10032,11 @@
       <c r="J230" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L230" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>636</v>
       </c>
@@ -9353,8 +10063,11 @@
       <c r="J231" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L231" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>636</v>
       </c>
@@ -9381,8 +10094,11 @@
       <c r="J232" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L232" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>637</v>
       </c>
@@ -9409,8 +10125,11 @@
       <c r="J233" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L233" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>637</v>
       </c>
@@ -9437,8 +10156,11 @@
       <c r="J234" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L234" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>638</v>
       </c>
@@ -9471,8 +10193,11 @@
       <c r="J235" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L235" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>638</v>
       </c>
@@ -9505,8 +10230,11 @@
       <c r="J236" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L236" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>638</v>
       </c>
@@ -9539,8 +10267,11 @@
       <c r="J237" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L237" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>639</v>
       </c>
@@ -9567,8 +10298,11 @@
       <c r="J238" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L238" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>639</v>
       </c>
@@ -9595,8 +10329,11 @@
       <c r="J239" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L239" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>639</v>
       </c>
@@ -9623,8 +10360,11 @@
       <c r="J240" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L240" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="241" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>639</v>
       </c>
@@ -9651,8 +10391,11 @@
       <c r="J241" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L241" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="242" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>640</v>
       </c>
@@ -9679,8 +10422,11 @@
       <c r="J242" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L242" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="243" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>640</v>
       </c>
@@ -9707,8 +10453,11 @@
       <c r="J243" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L243" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="244" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>641</v>
       </c>
@@ -9735,8 +10484,11 @@
       <c r="J244" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L244" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="245" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>641</v>
       </c>
@@ -9763,8 +10515,11 @@
       <c r="J245" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L245" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="246" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>641</v>
       </c>
@@ -9791,8 +10546,11 @@
       <c r="J246" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="L246" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="247" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>641</v>
       </c>
@@ -9820,7 +10578,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>641</v>
       </c>
@@ -9848,7 +10606,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>641</v>
       </c>
@@ -9876,7 +10634,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>641</v>
       </c>
@@ -9904,7 +10662,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>641</v>
       </c>
@@ -9932,7 +10690,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>641</v>
       </c>
@@ -9960,7 +10718,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>641</v>
       </c>
@@ -9988,7 +10746,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>641</v>
       </c>
@@ -10016,7 +10774,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>641</v>
       </c>
@@ -10044,7 +10802,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>642</v>
       </c>
@@ -15697,6 +16455,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/house_model_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDA8EB6-6B20-8342-B731-8121F8FCD9D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A540585-2526-9944-916C-8611AB216960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3351" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4225" uniqueCount="709">
   <si>
     <t>State</t>
   </si>
@@ -2173,6 +2173,33 @@
   </si>
   <si>
     <t>Mejia, Anelita</t>
+  </si>
+  <si>
+    <t>Election System</t>
+  </si>
+  <si>
+    <t>top_two</t>
+  </si>
+  <si>
+    <t>standard</t>
+  </si>
+  <si>
+    <t>top_four_rcv</t>
+  </si>
+  <si>
+    <t>General Election Party Structure</t>
+  </si>
+  <si>
+    <t>Unresolved</t>
+  </si>
+  <si>
+    <t>D_vs_R</t>
+  </si>
+  <si>
+    <t>Party Control Override</t>
+  </si>
+  <si>
+    <t>Election System Notes</t>
   </si>
 </sst>
 </file>
@@ -2604,27 +2631,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09FA142F-1ED2-0141-A92D-14DC2DE06B34}">
-  <dimension ref="A1:R436"/>
+  <dimension ref="A1:U436"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.1640625" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
     <col min="3" max="4" width="29.83203125" customWidth="1"/>
-    <col min="5" max="6" width="20.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="30.1640625" style="3" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" style="3" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="30.1640625" style="3" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="25.33203125" customWidth="1"/>
     <col min="9" max="9" width="24.1640625" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" customWidth="1"/>
-    <col min="11" max="11" width="18.6640625" customWidth="1"/>
-    <col min="12" max="12" width="28" customWidth="1"/>
-    <col min="13" max="13" width="21" customWidth="1"/>
-    <col min="14" max="14" width="29.1640625" customWidth="1"/>
-    <col min="15" max="15" width="19.5" customWidth="1"/>
-    <col min="16" max="16" width="21.33203125" customWidth="1"/>
-    <col min="17" max="17" width="23.83203125" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="18.6640625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="28" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="21" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="29.1640625" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="19.5" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="21.33203125" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="23.83203125" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="16.1640625" customWidth="1"/>
+    <col min="19" max="19" width="29.6640625" customWidth="1"/>
+    <col min="20" max="20" width="22" customWidth="1"/>
+    <col min="21" max="21" width="21.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2676,9 +2707,20 @@
       <c r="Q1" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="R1" s="1"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R1" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -2708,8 +2750,14 @@
       <c r="K2" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R2" t="s">
+        <v>702</v>
+      </c>
+      <c r="S2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -2739,8 +2787,14 @@
       <c r="K3" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R3" t="s">
+        <v>702</v>
+      </c>
+      <c r="S3" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -2776,8 +2830,14 @@
       <c r="K4" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R4" t="s">
+        <v>702</v>
+      </c>
+      <c r="S4" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -2813,8 +2873,14 @@
       <c r="K5" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R5" t="s">
+        <v>702</v>
+      </c>
+      <c r="S5" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -2844,8 +2910,14 @@
       <c r="K6" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R6" t="s">
+        <v>702</v>
+      </c>
+      <c r="S6" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -2878,8 +2950,14 @@
       <c r="K7" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R7" t="s">
+        <v>702</v>
+      </c>
+      <c r="S7" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -2909,8 +2987,14 @@
       <c r="K8" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R8" t="s">
+        <v>702</v>
+      </c>
+      <c r="S8" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>612</v>
       </c>
@@ -2946,8 +3030,14 @@
       <c r="N9" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" t="s">
+        <v>703</v>
+      </c>
+      <c r="S9" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>613</v>
       </c>
@@ -2983,8 +3073,14 @@
       <c r="N10" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" t="s">
+        <v>702</v>
+      </c>
+      <c r="S10" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>613</v>
       </c>
@@ -3020,8 +3116,14 @@
       <c r="N11" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R11" t="s">
+        <v>702</v>
+      </c>
+      <c r="S11" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>613</v>
       </c>
@@ -3057,8 +3159,14 @@
       <c r="N12" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" t="s">
+        <v>702</v>
+      </c>
+      <c r="S12" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>613</v>
       </c>
@@ -3094,8 +3202,14 @@
       <c r="N13" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" t="s">
+        <v>702</v>
+      </c>
+      <c r="S13" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>613</v>
       </c>
@@ -3131,8 +3245,14 @@
       <c r="N14" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" t="s">
+        <v>702</v>
+      </c>
+      <c r="S14" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>613</v>
       </c>
@@ -3168,8 +3288,14 @@
       <c r="N15" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" t="s">
+        <v>702</v>
+      </c>
+      <c r="S15" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>613</v>
       </c>
@@ -3205,8 +3331,14 @@
       <c r="N16" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R16" t="s">
+        <v>702</v>
+      </c>
+      <c r="S16" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>613</v>
       </c>
@@ -3242,8 +3374,14 @@
       <c r="N17" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R17" t="s">
+        <v>702</v>
+      </c>
+      <c r="S17" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>613</v>
       </c>
@@ -3279,8 +3417,14 @@
       <c r="N18" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R18" t="s">
+        <v>702</v>
+      </c>
+      <c r="S18" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>614</v>
       </c>
@@ -3322,8 +3466,14 @@
       <c r="N19" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R19" t="s">
+        <v>702</v>
+      </c>
+      <c r="S19" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>614</v>
       </c>
@@ -3365,8 +3515,14 @@
       <c r="N20" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R20" t="s">
+        <v>702</v>
+      </c>
+      <c r="S20" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>614</v>
       </c>
@@ -3408,8 +3564,14 @@
       <c r="N21" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R21" t="s">
+        <v>702</v>
+      </c>
+      <c r="S21" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>614</v>
       </c>
@@ -3451,8 +3613,14 @@
       <c r="N22" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R22" t="s">
+        <v>702</v>
+      </c>
+      <c r="S22" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>615</v>
       </c>
@@ -3488,8 +3656,14 @@
       <c r="N23" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R23" t="s">
+        <v>701</v>
+      </c>
+      <c r="S23" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>615</v>
       </c>
@@ -3525,8 +3699,14 @@
       <c r="N24" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R24" t="s">
+        <v>701</v>
+      </c>
+      <c r="S24" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>615</v>
       </c>
@@ -3562,8 +3742,14 @@
       <c r="N25" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R25" t="s">
+        <v>701</v>
+      </c>
+      <c r="S25" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>615</v>
       </c>
@@ -3599,8 +3785,14 @@
       <c r="N26" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R26" t="s">
+        <v>701</v>
+      </c>
+      <c r="S26" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>615</v>
       </c>
@@ -3636,8 +3828,14 @@
       <c r="N27" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R27" t="s">
+        <v>701</v>
+      </c>
+      <c r="S27" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>615</v>
       </c>
@@ -3673,8 +3871,14 @@
       <c r="N28" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R28" t="s">
+        <v>701</v>
+      </c>
+      <c r="S28" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>615</v>
       </c>
@@ -3710,8 +3914,14 @@
       <c r="N29" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R29" t="s">
+        <v>701</v>
+      </c>
+      <c r="S29" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>615</v>
       </c>
@@ -3747,8 +3957,14 @@
       <c r="N30" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R30" t="s">
+        <v>701</v>
+      </c>
+      <c r="S30" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>615</v>
       </c>
@@ -3784,8 +4000,14 @@
       <c r="N31" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R31" t="s">
+        <v>701</v>
+      </c>
+      <c r="S31" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>615</v>
       </c>
@@ -3821,8 +4043,14 @@
       <c r="N32" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R32" t="s">
+        <v>701</v>
+      </c>
+      <c r="S32" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>615</v>
       </c>
@@ -3858,8 +4086,14 @@
       <c r="N33" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R33" t="s">
+        <v>701</v>
+      </c>
+      <c r="S33" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>615</v>
       </c>
@@ -3895,8 +4129,14 @@
       <c r="N34" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R34" t="s">
+        <v>701</v>
+      </c>
+      <c r="S34" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>615</v>
       </c>
@@ -3932,8 +4172,14 @@
       <c r="N35" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R35" t="s">
+        <v>701</v>
+      </c>
+      <c r="S35" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>615</v>
       </c>
@@ -3969,8 +4215,14 @@
       <c r="N36" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R36" t="s">
+        <v>701</v>
+      </c>
+      <c r="S36" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>615</v>
       </c>
@@ -4006,8 +4258,14 @@
       <c r="N37" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R37" t="s">
+        <v>701</v>
+      </c>
+      <c r="S37" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>615</v>
       </c>
@@ -4043,8 +4301,14 @@
       <c r="N38" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R38" t="s">
+        <v>701</v>
+      </c>
+      <c r="S38" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>615</v>
       </c>
@@ -4080,8 +4344,14 @@
       <c r="N39" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R39" t="s">
+        <v>701</v>
+      </c>
+      <c r="S39" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>615</v>
       </c>
@@ -4117,8 +4387,14 @@
       <c r="N40" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R40" t="s">
+        <v>701</v>
+      </c>
+      <c r="S40" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>615</v>
       </c>
@@ -4154,8 +4430,14 @@
       <c r="N41" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R41" t="s">
+        <v>701</v>
+      </c>
+      <c r="S41" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>615</v>
       </c>
@@ -4191,8 +4473,14 @@
       <c r="N42" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R42" t="s">
+        <v>701</v>
+      </c>
+      <c r="S42" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>615</v>
       </c>
@@ -4228,8 +4516,14 @@
       <c r="N43" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R43" t="s">
+        <v>701</v>
+      </c>
+      <c r="S43" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>615</v>
       </c>
@@ -4265,8 +4559,14 @@
       <c r="N44" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R44" t="s">
+        <v>701</v>
+      </c>
+      <c r="S44" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>615</v>
       </c>
@@ -4302,8 +4602,14 @@
       <c r="N45" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R45" t="s">
+        <v>701</v>
+      </c>
+      <c r="S45" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>615</v>
       </c>
@@ -4339,8 +4645,14 @@
       <c r="N46" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R46" t="s">
+        <v>701</v>
+      </c>
+      <c r="S46" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>615</v>
       </c>
@@ -4376,8 +4688,14 @@
       <c r="N47" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R47" t="s">
+        <v>701</v>
+      </c>
+      <c r="S47" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>615</v>
       </c>
@@ -4413,8 +4731,14 @@
       <c r="N48" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R48" t="s">
+        <v>701</v>
+      </c>
+      <c r="S48" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>615</v>
       </c>
@@ -4450,8 +4774,14 @@
       <c r="N49" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R49" t="s">
+        <v>701</v>
+      </c>
+      <c r="S49" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>615</v>
       </c>
@@ -4487,8 +4817,14 @@
       <c r="N50" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R50" t="s">
+        <v>701</v>
+      </c>
+      <c r="S50" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>615</v>
       </c>
@@ -4524,8 +4860,14 @@
       <c r="N51" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R51" t="s">
+        <v>701</v>
+      </c>
+      <c r="S51" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>615</v>
       </c>
@@ -4561,8 +4903,14 @@
       <c r="N52" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R52" t="s">
+        <v>701</v>
+      </c>
+      <c r="S52" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>615</v>
       </c>
@@ -4598,8 +4946,14 @@
       <c r="N53" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R53" t="s">
+        <v>701</v>
+      </c>
+      <c r="S53" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>615</v>
       </c>
@@ -4635,8 +4989,14 @@
       <c r="N54" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R54" t="s">
+        <v>701</v>
+      </c>
+      <c r="S54" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>615</v>
       </c>
@@ -4672,8 +5032,14 @@
       <c r="N55" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R55" t="s">
+        <v>701</v>
+      </c>
+      <c r="S55" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>615</v>
       </c>
@@ -4709,8 +5075,14 @@
       <c r="N56" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R56" t="s">
+        <v>701</v>
+      </c>
+      <c r="S56" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>615</v>
       </c>
@@ -4746,8 +5118,14 @@
       <c r="N57" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R57" t="s">
+        <v>701</v>
+      </c>
+      <c r="S57" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>615</v>
       </c>
@@ -4783,8 +5161,14 @@
       <c r="N58" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R58" t="s">
+        <v>701</v>
+      </c>
+      <c r="S58" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>615</v>
       </c>
@@ -4820,8 +5204,14 @@
       <c r="N59" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R59" t="s">
+        <v>701</v>
+      </c>
+      <c r="S59" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>615</v>
       </c>
@@ -4857,8 +5247,14 @@
       <c r="N60" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R60" t="s">
+        <v>701</v>
+      </c>
+      <c r="S60" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>615</v>
       </c>
@@ -4894,8 +5290,14 @@
       <c r="N61" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R61" t="s">
+        <v>701</v>
+      </c>
+      <c r="S61" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>615</v>
       </c>
@@ -4931,8 +5333,14 @@
       <c r="N62" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R62" t="s">
+        <v>701</v>
+      </c>
+      <c r="S62" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>615</v>
       </c>
@@ -4968,8 +5376,14 @@
       <c r="N63" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R63" t="s">
+        <v>701</v>
+      </c>
+      <c r="S63" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>615</v>
       </c>
@@ -5005,8 +5419,14 @@
       <c r="N64" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R64" t="s">
+        <v>701</v>
+      </c>
+      <c r="S64" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>615</v>
       </c>
@@ -5042,8 +5462,14 @@
       <c r="N65" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R65" t="s">
+        <v>701</v>
+      </c>
+      <c r="S65" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>615</v>
       </c>
@@ -5079,8 +5505,14 @@
       <c r="N66" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R66" t="s">
+        <v>701</v>
+      </c>
+      <c r="S66" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>615</v>
       </c>
@@ -5116,8 +5548,14 @@
       <c r="N67" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R67" t="s">
+        <v>701</v>
+      </c>
+      <c r="S67" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>615</v>
       </c>
@@ -5153,8 +5591,14 @@
       <c r="N68" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R68" t="s">
+        <v>701</v>
+      </c>
+      <c r="S68" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>615</v>
       </c>
@@ -5190,8 +5634,14 @@
       <c r="N69" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R69" t="s">
+        <v>701</v>
+      </c>
+      <c r="S69" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>615</v>
       </c>
@@ -5227,8 +5677,14 @@
       <c r="N70" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R70" t="s">
+        <v>701</v>
+      </c>
+      <c r="S70" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>615</v>
       </c>
@@ -5264,8 +5720,14 @@
       <c r="N71" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R71" t="s">
+        <v>701</v>
+      </c>
+      <c r="S71" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>615</v>
       </c>
@@ -5301,8 +5763,14 @@
       <c r="N72" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R72" t="s">
+        <v>701</v>
+      </c>
+      <c r="S72" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>615</v>
       </c>
@@ -5338,8 +5806,14 @@
       <c r="N73" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R73" t="s">
+        <v>701</v>
+      </c>
+      <c r="S73" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>615</v>
       </c>
@@ -5375,8 +5849,14 @@
       <c r="N74" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R74" t="s">
+        <v>701</v>
+      </c>
+      <c r="S74" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>616</v>
       </c>
@@ -5412,8 +5892,14 @@
       <c r="N75" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R75" t="s">
+        <v>702</v>
+      </c>
+      <c r="S75" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>616</v>
       </c>
@@ -5449,8 +5935,14 @@
       <c r="N76" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R76" t="s">
+        <v>702</v>
+      </c>
+      <c r="S76" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>616</v>
       </c>
@@ -5486,8 +5978,14 @@
       <c r="N77" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R77" t="s">
+        <v>702</v>
+      </c>
+      <c r="S77" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>616</v>
       </c>
@@ -5523,8 +6021,14 @@
       <c r="N78" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R78" t="s">
+        <v>702</v>
+      </c>
+      <c r="S78" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>616</v>
       </c>
@@ -5560,8 +6064,14 @@
       <c r="N79" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R79" t="s">
+        <v>702</v>
+      </c>
+      <c r="S79" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>616</v>
       </c>
@@ -5597,8 +6107,14 @@
       <c r="N80" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R80" t="s">
+        <v>702</v>
+      </c>
+      <c r="S80" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>616</v>
       </c>
@@ -5634,8 +6150,14 @@
       <c r="N81" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R81" t="s">
+        <v>702</v>
+      </c>
+      <c r="S81" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>616</v>
       </c>
@@ -5671,8 +6193,14 @@
       <c r="N82" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R82" t="s">
+        <v>702</v>
+      </c>
+      <c r="S82" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>617</v>
       </c>
@@ -5708,8 +6236,14 @@
       <c r="N83" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R83" t="s">
+        <v>702</v>
+      </c>
+      <c r="S83" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>617</v>
       </c>
@@ -5745,8 +6279,14 @@
       <c r="N84" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R84" t="s">
+        <v>702</v>
+      </c>
+      <c r="S84" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>617</v>
       </c>
@@ -5782,8 +6322,14 @@
       <c r="N85" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R85" t="s">
+        <v>702</v>
+      </c>
+      <c r="S85" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>617</v>
       </c>
@@ -5819,8 +6365,14 @@
       <c r="N86" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R86" t="s">
+        <v>702</v>
+      </c>
+      <c r="S86" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>617</v>
       </c>
@@ -5856,8 +6408,14 @@
       <c r="N87" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R87" t="s">
+        <v>702</v>
+      </c>
+      <c r="S87" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>618</v>
       </c>
@@ -5893,8 +6451,14 @@
       <c r="N88" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R88" t="s">
+        <v>702</v>
+      </c>
+      <c r="S88" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>619</v>
       </c>
@@ -5931,8 +6495,14 @@
       <c r="N89" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R89" t="s">
+        <v>702</v>
+      </c>
+      <c r="S89" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>619</v>
       </c>
@@ -5969,8 +6539,14 @@
       <c r="N90" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R90" t="s">
+        <v>702</v>
+      </c>
+      <c r="S90" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>619</v>
       </c>
@@ -6007,8 +6583,14 @@
       <c r="N91" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R91" t="s">
+        <v>702</v>
+      </c>
+      <c r="S91" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>619</v>
       </c>
@@ -6045,8 +6627,14 @@
       <c r="N92" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R92" t="s">
+        <v>702</v>
+      </c>
+      <c r="S92" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>619</v>
       </c>
@@ -6083,8 +6671,14 @@
       <c r="N93" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R93" t="s">
+        <v>702</v>
+      </c>
+      <c r="S93" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>619</v>
       </c>
@@ -6121,8 +6715,14 @@
       <c r="N94" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R94" t="s">
+        <v>702</v>
+      </c>
+      <c r="S94" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>619</v>
       </c>
@@ -6159,8 +6759,14 @@
       <c r="N95" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R95" t="s">
+        <v>702</v>
+      </c>
+      <c r="S95" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>619</v>
       </c>
@@ -6197,8 +6803,14 @@
       <c r="N96" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R96" t="s">
+        <v>702</v>
+      </c>
+      <c r="S96" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>619</v>
       </c>
@@ -6235,8 +6847,14 @@
       <c r="N97" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R97" t="s">
+        <v>702</v>
+      </c>
+      <c r="S97" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>619</v>
       </c>
@@ -6273,8 +6891,14 @@
       <c r="N98" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R98" t="s">
+        <v>702</v>
+      </c>
+      <c r="S98" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>619</v>
       </c>
@@ -6311,8 +6935,14 @@
       <c r="N99" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R99" t="s">
+        <v>702</v>
+      </c>
+      <c r="S99" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>619</v>
       </c>
@@ -6349,8 +6979,14 @@
       <c r="N100" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R100" t="s">
+        <v>702</v>
+      </c>
+      <c r="S100" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>619</v>
       </c>
@@ -6387,8 +7023,14 @@
       <c r="N101" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R101" t="s">
+        <v>702</v>
+      </c>
+      <c r="S101" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>619</v>
       </c>
@@ -6425,8 +7067,14 @@
       <c r="N102" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R102" t="s">
+        <v>702</v>
+      </c>
+      <c r="S102" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>619</v>
       </c>
@@ -6463,8 +7111,14 @@
       <c r="N103" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R103" t="s">
+        <v>702</v>
+      </c>
+      <c r="S103" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>619</v>
       </c>
@@ -6501,8 +7155,14 @@
       <c r="N104" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R104" t="s">
+        <v>702</v>
+      </c>
+      <c r="S104" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>619</v>
       </c>
@@ -6539,8 +7199,14 @@
       <c r="N105" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R105" t="s">
+        <v>702</v>
+      </c>
+      <c r="S105" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>619</v>
       </c>
@@ -6577,8 +7243,14 @@
       <c r="N106" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R106" t="s">
+        <v>702</v>
+      </c>
+      <c r="S106" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>619</v>
       </c>
@@ -6615,8 +7287,14 @@
       <c r="N107" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R107" t="s">
+        <v>702</v>
+      </c>
+      <c r="S107" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>619</v>
       </c>
@@ -6653,8 +7331,14 @@
       <c r="N108" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R108" t="s">
+        <v>702</v>
+      </c>
+      <c r="S108" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>619</v>
       </c>
@@ -6691,8 +7375,14 @@
       <c r="N109" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R109" t="s">
+        <v>702</v>
+      </c>
+      <c r="S109" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>619</v>
       </c>
@@ -6729,8 +7419,14 @@
       <c r="N110" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R110" t="s">
+        <v>702</v>
+      </c>
+      <c r="S110" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>619</v>
       </c>
@@ -6767,8 +7463,14 @@
       <c r="N111" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R111" t="s">
+        <v>702</v>
+      </c>
+      <c r="S111" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>619</v>
       </c>
@@ -6805,8 +7507,14 @@
       <c r="N112" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R112" t="s">
+        <v>702</v>
+      </c>
+      <c r="S112" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>619</v>
       </c>
@@ -6843,8 +7551,14 @@
       <c r="N113" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R113" t="s">
+        <v>702</v>
+      </c>
+      <c r="S113" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>619</v>
       </c>
@@ -6881,8 +7595,14 @@
       <c r="N114" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R114" t="s">
+        <v>702</v>
+      </c>
+      <c r="S114" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>619</v>
       </c>
@@ -6919,8 +7639,14 @@
       <c r="N115" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R115" t="s">
+        <v>702</v>
+      </c>
+      <c r="S115" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>619</v>
       </c>
@@ -6957,8 +7683,14 @@
       <c r="N116" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R116" t="s">
+        <v>702</v>
+      </c>
+      <c r="S116" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>620</v>
       </c>
@@ -6994,8 +7726,14 @@
       <c r="N117" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R117" t="s">
+        <v>702</v>
+      </c>
+      <c r="S117" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>620</v>
       </c>
@@ -7037,8 +7775,14 @@
       <c r="N118" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R118" t="s">
+        <v>702</v>
+      </c>
+      <c r="S118" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>620</v>
       </c>
@@ -7080,8 +7824,14 @@
       <c r="N119" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R119" t="s">
+        <v>702</v>
+      </c>
+      <c r="S119" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>620</v>
       </c>
@@ -7123,8 +7873,14 @@
       <c r="N120" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R120" t="s">
+        <v>702</v>
+      </c>
+      <c r="S120" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>620</v>
       </c>
@@ -7166,8 +7922,14 @@
       <c r="N121" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R121" t="s">
+        <v>702</v>
+      </c>
+      <c r="S121" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>620</v>
       </c>
@@ -7206,8 +7968,14 @@
       <c r="N122" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R122" t="s">
+        <v>702</v>
+      </c>
+      <c r="S122" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>620</v>
       </c>
@@ -7246,8 +8014,14 @@
       <c r="N123" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R123" t="s">
+        <v>702</v>
+      </c>
+      <c r="S123" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>620</v>
       </c>
@@ -7289,8 +8063,14 @@
       <c r="N124" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R124" t="s">
+        <v>702</v>
+      </c>
+      <c r="S124" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>620</v>
       </c>
@@ -7332,8 +8112,14 @@
       <c r="N125" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R125" t="s">
+        <v>702</v>
+      </c>
+      <c r="S125" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>620</v>
       </c>
@@ -7372,8 +8158,14 @@
       <c r="N126" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R126" t="s">
+        <v>702</v>
+      </c>
+      <c r="S126" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>620</v>
       </c>
@@ -7412,8 +8204,14 @@
       <c r="N127" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R127" t="s">
+        <v>702</v>
+      </c>
+      <c r="S127" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>620</v>
       </c>
@@ -7452,8 +8250,14 @@
       <c r="N128" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R128" t="s">
+        <v>702</v>
+      </c>
+      <c r="S128" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>620</v>
       </c>
@@ -7495,8 +8299,14 @@
       <c r="N129" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R129" t="s">
+        <v>702</v>
+      </c>
+      <c r="S129" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>620</v>
       </c>
@@ -7538,8 +8348,14 @@
       <c r="N130" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R130" t="s">
+        <v>702</v>
+      </c>
+      <c r="S130" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>621</v>
       </c>
@@ -7575,8 +8391,14 @@
       <c r="N131" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R131" t="s">
+        <v>702</v>
+      </c>
+      <c r="S131" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>621</v>
       </c>
@@ -7612,8 +8434,14 @@
       <c r="N132" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R132" t="s">
+        <v>702</v>
+      </c>
+      <c r="S132" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>622</v>
       </c>
@@ -7655,8 +8483,14 @@
       <c r="N133" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R133" t="s">
+        <v>702</v>
+      </c>
+      <c r="S133" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>622</v>
       </c>
@@ -7698,8 +8532,14 @@
       <c r="N134" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R134" t="s">
+        <v>702</v>
+      </c>
+      <c r="S134" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>623</v>
       </c>
@@ -7741,8 +8581,14 @@
       <c r="N135" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R135" t="s">
+        <v>702</v>
+      </c>
+      <c r="S135" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>623</v>
       </c>
@@ -7784,8 +8630,14 @@
       <c r="N136" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R136" t="s">
+        <v>702</v>
+      </c>
+      <c r="S136" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>623</v>
       </c>
@@ -7827,8 +8679,14 @@
       <c r="N137" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R137" t="s">
+        <v>702</v>
+      </c>
+      <c r="S137" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>623</v>
       </c>
@@ -7870,8 +8728,14 @@
       <c r="N138" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R138" t="s">
+        <v>702</v>
+      </c>
+      <c r="S138" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>623</v>
       </c>
@@ -7913,8 +8777,14 @@
       <c r="N139" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R139" t="s">
+        <v>702</v>
+      </c>
+      <c r="S139" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>623</v>
       </c>
@@ -7956,8 +8826,14 @@
       <c r="N140" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R140" t="s">
+        <v>702</v>
+      </c>
+      <c r="S140" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="141" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>623</v>
       </c>
@@ -7999,8 +8875,14 @@
       <c r="N141" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R141" t="s">
+        <v>702</v>
+      </c>
+      <c r="S141" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="142" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>623</v>
       </c>
@@ -8042,8 +8924,14 @@
       <c r="N142" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R142" t="s">
+        <v>702</v>
+      </c>
+      <c r="S142" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>623</v>
       </c>
@@ -8085,8 +8973,14 @@
       <c r="N143" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R143" t="s">
+        <v>702</v>
+      </c>
+      <c r="S143" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="144" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>623</v>
       </c>
@@ -8128,8 +9022,14 @@
       <c r="N144" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R144" t="s">
+        <v>702</v>
+      </c>
+      <c r="S144" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="145" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>623</v>
       </c>
@@ -8171,8 +9071,14 @@
       <c r="N145" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R145" t="s">
+        <v>702</v>
+      </c>
+      <c r="S145" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="146" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>623</v>
       </c>
@@ -8214,8 +9120,14 @@
       <c r="N146" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R146" t="s">
+        <v>702</v>
+      </c>
+      <c r="S146" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="147" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>623</v>
       </c>
@@ -8257,8 +9169,14 @@
       <c r="N147" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R147" t="s">
+        <v>702</v>
+      </c>
+      <c r="S147" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="148" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>623</v>
       </c>
@@ -8300,8 +9218,14 @@
       <c r="N148" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R148" t="s">
+        <v>702</v>
+      </c>
+      <c r="S148" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="149" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>623</v>
       </c>
@@ -8343,8 +9267,14 @@
       <c r="N149" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R149" t="s">
+        <v>702</v>
+      </c>
+      <c r="S149" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="150" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>623</v>
       </c>
@@ -8386,8 +9316,14 @@
       <c r="N150" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R150" t="s">
+        <v>702</v>
+      </c>
+      <c r="S150" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="151" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>623</v>
       </c>
@@ -8429,8 +9365,14 @@
       <c r="N151" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R151" t="s">
+        <v>702</v>
+      </c>
+      <c r="S151" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="152" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>624</v>
       </c>
@@ -8472,8 +9414,14 @@
       <c r="N152" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R152" t="s">
+        <v>702</v>
+      </c>
+      <c r="S152" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="153" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>624</v>
       </c>
@@ -8515,8 +9463,14 @@
       <c r="N153" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R153" t="s">
+        <v>702</v>
+      </c>
+      <c r="S153" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="154" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>624</v>
       </c>
@@ -8558,8 +9512,14 @@
       <c r="N154" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R154" t="s">
+        <v>702</v>
+      </c>
+      <c r="S154" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="155" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>624</v>
       </c>
@@ -8601,8 +9561,14 @@
       <c r="N155" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R155" t="s">
+        <v>702</v>
+      </c>
+      <c r="S155" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="156" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>624</v>
       </c>
@@ -8644,8 +9610,14 @@
       <c r="N156" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R156" t="s">
+        <v>702</v>
+      </c>
+      <c r="S156" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="157" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>624</v>
       </c>
@@ -8687,8 +9659,14 @@
       <c r="N157" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R157" t="s">
+        <v>702</v>
+      </c>
+      <c r="S157" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>624</v>
       </c>
@@ -8730,8 +9708,14 @@
       <c r="N158" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R158" t="s">
+        <v>702</v>
+      </c>
+      <c r="S158" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="159" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>624</v>
       </c>
@@ -8773,8 +9757,14 @@
       <c r="N159" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R159" t="s">
+        <v>702</v>
+      </c>
+      <c r="S159" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="160" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>624</v>
       </c>
@@ -8816,8 +9806,14 @@
       <c r="N160" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R160" t="s">
+        <v>702</v>
+      </c>
+      <c r="S160" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>625</v>
       </c>
@@ -8853,8 +9849,14 @@
       <c r="N161" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R161" t="s">
+        <v>702</v>
+      </c>
+      <c r="S161" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="162" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>625</v>
       </c>
@@ -8890,8 +9892,14 @@
       <c r="N162" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R162" t="s">
+        <v>702</v>
+      </c>
+      <c r="S162" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="163" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>625</v>
       </c>
@@ -8927,8 +9935,14 @@
       <c r="N163" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R163" t="s">
+        <v>702</v>
+      </c>
+      <c r="S163" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="164" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>625</v>
       </c>
@@ -8964,8 +9978,14 @@
       <c r="N164" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R164" t="s">
+        <v>702</v>
+      </c>
+      <c r="S164" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="165" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>626</v>
       </c>
@@ -9001,8 +10021,14 @@
       <c r="N165" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R165" t="s">
+        <v>702</v>
+      </c>
+      <c r="S165" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="166" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>626</v>
       </c>
@@ -9038,8 +10064,14 @@
       <c r="N166" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R166" t="s">
+        <v>702</v>
+      </c>
+      <c r="S166" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="167" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>626</v>
       </c>
@@ -9075,8 +10107,14 @@
       <c r="N167" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R167" t="s">
+        <v>702</v>
+      </c>
+      <c r="S167" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="168" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>626</v>
       </c>
@@ -9112,8 +10150,14 @@
       <c r="N168" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R168" t="s">
+        <v>702</v>
+      </c>
+      <c r="S168" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="169" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>627</v>
       </c>
@@ -9155,8 +10199,14 @@
       <c r="N169" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R169" t="s">
+        <v>702</v>
+      </c>
+      <c r="S169" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="170" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>627</v>
       </c>
@@ -9198,8 +10248,14 @@
       <c r="N170" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R170" t="s">
+        <v>702</v>
+      </c>
+      <c r="S170" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="171" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>627</v>
       </c>
@@ -9241,8 +10297,14 @@
       <c r="N171" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R171" t="s">
+        <v>702</v>
+      </c>
+      <c r="S171" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="172" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>627</v>
       </c>
@@ -9284,8 +10346,14 @@
       <c r="N172" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R172" t="s">
+        <v>702</v>
+      </c>
+      <c r="S172" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="173" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>627</v>
       </c>
@@ -9327,8 +10395,14 @@
       <c r="N173" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R173" t="s">
+        <v>702</v>
+      </c>
+      <c r="S173" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="174" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>627</v>
       </c>
@@ -9370,8 +10444,14 @@
       <c r="N174" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R174" t="s">
+        <v>702</v>
+      </c>
+      <c r="S174" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="175" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>628</v>
       </c>
@@ -9402,8 +10482,14 @@
       <c r="K175" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R175" t="s">
+        <v>702</v>
+      </c>
+      <c r="S175" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="176" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>628</v>
       </c>
@@ -9434,8 +10520,14 @@
       <c r="K176" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R176" t="s">
+        <v>702</v>
+      </c>
+      <c r="S176" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="177" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>628</v>
       </c>
@@ -9466,8 +10558,14 @@
       <c r="K177" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R177" t="s">
+        <v>702</v>
+      </c>
+      <c r="S177" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="178" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>628</v>
       </c>
@@ -9498,8 +10596,14 @@
       <c r="K178" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R178" t="s">
+        <v>702</v>
+      </c>
+      <c r="S178" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="179" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>628</v>
       </c>
@@ -9530,8 +10634,14 @@
       <c r="K179" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R179" t="s">
+        <v>702</v>
+      </c>
+      <c r="S179" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="180" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>628</v>
       </c>
@@ -9562,8 +10672,14 @@
       <c r="K180" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R180" t="s">
+        <v>702</v>
+      </c>
+      <c r="S180" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="181" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>629</v>
       </c>
@@ -9599,8 +10715,14 @@
       <c r="N181" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R181" t="s">
+        <v>702</v>
+      </c>
+      <c r="S181" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="182" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>629</v>
       </c>
@@ -9636,8 +10758,14 @@
       <c r="N182" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R182" t="s">
+        <v>702</v>
+      </c>
+      <c r="S182" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="183" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>630</v>
       </c>
@@ -9673,8 +10801,14 @@
       <c r="N183" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R183" t="s">
+        <v>702</v>
+      </c>
+      <c r="S183" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="184" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>630</v>
       </c>
@@ -9710,8 +10844,14 @@
       <c r="N184" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R184" t="s">
+        <v>702</v>
+      </c>
+      <c r="S184" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="185" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>630</v>
       </c>
@@ -9747,8 +10887,14 @@
       <c r="N185" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R185" t="s">
+        <v>702</v>
+      </c>
+      <c r="S185" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="186" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>630</v>
       </c>
@@ -9784,8 +10930,14 @@
       <c r="N186" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R186" t="s">
+        <v>702</v>
+      </c>
+      <c r="S186" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="187" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>630</v>
       </c>
@@ -9821,8 +10973,14 @@
       <c r="N187" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R187" t="s">
+        <v>702</v>
+      </c>
+      <c r="S187" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="188" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>630</v>
       </c>
@@ -9858,8 +11016,14 @@
       <c r="N188" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R188" t="s">
+        <v>702</v>
+      </c>
+      <c r="S188" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="189" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>630</v>
       </c>
@@ -9895,8 +11059,14 @@
       <c r="N189" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R189" t="s">
+        <v>702</v>
+      </c>
+      <c r="S189" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="190" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>630</v>
       </c>
@@ -9932,8 +11102,14 @@
       <c r="N190" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R190" t="s">
+        <v>702</v>
+      </c>
+      <c r="S190" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="191" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>631</v>
       </c>
@@ -9969,8 +11145,14 @@
       <c r="N191" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R191" t="s">
+        <v>702</v>
+      </c>
+      <c r="S191" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="192" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>631</v>
       </c>
@@ -10006,8 +11188,14 @@
       <c r="N192" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R192" t="s">
+        <v>702</v>
+      </c>
+      <c r="S192" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="193" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>631</v>
       </c>
@@ -10043,8 +11231,14 @@
       <c r="N193" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R193" t="s">
+        <v>702</v>
+      </c>
+      <c r="S193" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="194" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>631</v>
       </c>
@@ -10080,8 +11274,14 @@
       <c r="N194" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R194" t="s">
+        <v>702</v>
+      </c>
+      <c r="S194" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="195" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>631</v>
       </c>
@@ -10117,8 +11317,14 @@
       <c r="N195" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R195" t="s">
+        <v>702</v>
+      </c>
+      <c r="S195" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="196" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>631</v>
       </c>
@@ -10154,8 +11360,14 @@
       <c r="N196" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R196" t="s">
+        <v>702</v>
+      </c>
+      <c r="S196" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="197" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>631</v>
       </c>
@@ -10191,8 +11403,14 @@
       <c r="N197" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R197" t="s">
+        <v>702</v>
+      </c>
+      <c r="S197" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="198" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>631</v>
       </c>
@@ -10228,8 +11446,14 @@
       <c r="N198" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R198" t="s">
+        <v>702</v>
+      </c>
+      <c r="S198" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="199" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>631</v>
       </c>
@@ -10265,8 +11489,14 @@
       <c r="N199" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R199" t="s">
+        <v>702</v>
+      </c>
+      <c r="S199" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="200" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>632</v>
       </c>
@@ -10302,8 +11532,14 @@
       <c r="N200" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R200" t="s">
+        <v>702</v>
+      </c>
+      <c r="S200" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="201" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>632</v>
       </c>
@@ -10339,8 +11575,14 @@
       <c r="N201" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R201" t="s">
+        <v>702</v>
+      </c>
+      <c r="S201" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="202" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>632</v>
       </c>
@@ -10376,8 +11618,14 @@
       <c r="N202" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R202" t="s">
+        <v>702</v>
+      </c>
+      <c r="S202" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="203" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>632</v>
       </c>
@@ -10413,8 +11661,14 @@
       <c r="N203" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R203" t="s">
+        <v>702</v>
+      </c>
+      <c r="S203" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="204" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>632</v>
       </c>
@@ -10450,8 +11704,14 @@
       <c r="N204" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R204" t="s">
+        <v>702</v>
+      </c>
+      <c r="S204" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="205" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>632</v>
       </c>
@@ -10487,8 +11747,14 @@
       <c r="N205" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R205" t="s">
+        <v>702</v>
+      </c>
+      <c r="S205" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="206" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>632</v>
       </c>
@@ -10524,8 +11790,14 @@
       <c r="N206" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R206" t="s">
+        <v>702</v>
+      </c>
+      <c r="S206" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="207" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>632</v>
       </c>
@@ -10561,8 +11833,14 @@
       <c r="N207" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R207" t="s">
+        <v>702</v>
+      </c>
+      <c r="S207" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="208" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>632</v>
       </c>
@@ -10598,8 +11876,14 @@
       <c r="N208" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R208" t="s">
+        <v>702</v>
+      </c>
+      <c r="S208" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="209" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>632</v>
       </c>
@@ -10635,8 +11919,14 @@
       <c r="N209" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R209" t="s">
+        <v>702</v>
+      </c>
+      <c r="S209" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="210" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>632</v>
       </c>
@@ -10672,8 +11962,14 @@
       <c r="N210" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R210" t="s">
+        <v>702</v>
+      </c>
+      <c r="S210" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="211" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>632</v>
       </c>
@@ -10709,8 +12005,14 @@
       <c r="N211" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R211" t="s">
+        <v>702</v>
+      </c>
+      <c r="S211" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="212" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>632</v>
       </c>
@@ -10746,8 +12048,14 @@
       <c r="N212" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R212" t="s">
+        <v>702</v>
+      </c>
+      <c r="S212" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="213" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>633</v>
       </c>
@@ -10783,8 +12091,14 @@
       <c r="N213" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R213" t="s">
+        <v>702</v>
+      </c>
+      <c r="S213" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="214" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>633</v>
       </c>
@@ -10820,8 +12134,14 @@
       <c r="N214" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R214" t="s">
+        <v>702</v>
+      </c>
+      <c r="S214" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="215" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>633</v>
       </c>
@@ -10857,8 +12177,14 @@
       <c r="N215" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R215" t="s">
+        <v>702</v>
+      </c>
+      <c r="S215" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="216" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>633</v>
       </c>
@@ -10894,8 +12220,14 @@
       <c r="N216" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R216" t="s">
+        <v>702</v>
+      </c>
+      <c r="S216" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="217" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>633</v>
       </c>
@@ -10931,8 +12263,14 @@
       <c r="N217" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R217" t="s">
+        <v>702</v>
+      </c>
+      <c r="S217" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="218" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>633</v>
       </c>
@@ -10968,8 +12306,14 @@
       <c r="N218" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R218" t="s">
+        <v>702</v>
+      </c>
+      <c r="S218" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="219" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>633</v>
       </c>
@@ -11005,8 +12349,14 @@
       <c r="N219" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R219" t="s">
+        <v>702</v>
+      </c>
+      <c r="S219" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="220" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>633</v>
       </c>
@@ -11042,8 +12392,14 @@
       <c r="N220" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R220" t="s">
+        <v>702</v>
+      </c>
+      <c r="S220" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="221" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>634</v>
       </c>
@@ -11085,8 +12441,14 @@
       <c r="N221" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R221" t="s">
+        <v>702</v>
+      </c>
+      <c r="S221" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="222" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>634</v>
       </c>
@@ -11128,8 +12490,14 @@
       <c r="N222" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R222" t="s">
+        <v>702</v>
+      </c>
+      <c r="S222" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="223" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>634</v>
       </c>
@@ -11171,8 +12539,14 @@
       <c r="N223" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R223" t="s">
+        <v>702</v>
+      </c>
+      <c r="S223" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="224" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>634</v>
       </c>
@@ -11214,8 +12588,14 @@
       <c r="N224" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R224" t="s">
+        <v>702</v>
+      </c>
+      <c r="S224" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="225" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>635</v>
       </c>
@@ -11251,8 +12631,14 @@
       <c r="N225" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R225" t="s">
+        <v>702</v>
+      </c>
+      <c r="S225" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="226" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>635</v>
       </c>
@@ -11288,8 +12674,14 @@
       <c r="N226" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R226" t="s">
+        <v>702</v>
+      </c>
+      <c r="S226" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="227" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>635</v>
       </c>
@@ -11325,8 +12717,14 @@
       <c r="N227" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R227" t="s">
+        <v>702</v>
+      </c>
+      <c r="S227" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="228" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>635</v>
       </c>
@@ -11362,8 +12760,14 @@
       <c r="N228" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R228" t="s">
+        <v>702</v>
+      </c>
+      <c r="S228" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="229" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>635</v>
       </c>
@@ -11399,8 +12803,14 @@
       <c r="N229" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R229" t="s">
+        <v>702</v>
+      </c>
+      <c r="S229" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="230" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>635</v>
       </c>
@@ -11436,8 +12846,14 @@
       <c r="N230" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R230" t="s">
+        <v>702</v>
+      </c>
+      <c r="S230" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="231" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>635</v>
       </c>
@@ -11473,8 +12889,14 @@
       <c r="N231" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R231" t="s">
+        <v>702</v>
+      </c>
+      <c r="S231" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="232" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>635</v>
       </c>
@@ -11510,8 +12932,14 @@
       <c r="N232" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R232" t="s">
+        <v>702</v>
+      </c>
+      <c r="S232" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="233" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>636</v>
       </c>
@@ -11547,8 +12975,14 @@
       <c r="N233" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R233" t="s">
+        <v>702</v>
+      </c>
+      <c r="S233" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="234" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>636</v>
       </c>
@@ -11584,8 +13018,14 @@
       <c r="N234" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R234" t="s">
+        <v>702</v>
+      </c>
+      <c r="S234" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="235" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>637</v>
       </c>
@@ -11627,8 +13067,14 @@
       <c r="N235" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R235" t="s">
+        <v>702</v>
+      </c>
+      <c r="S235" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="236" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>637</v>
       </c>
@@ -11670,8 +13116,14 @@
       <c r="N236" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R236" t="s">
+        <v>702</v>
+      </c>
+      <c r="S236" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="237" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>637</v>
       </c>
@@ -11713,8 +13165,14 @@
       <c r="N237" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R237" t="s">
+        <v>702</v>
+      </c>
+      <c r="S237" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="238" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>638</v>
       </c>
@@ -11750,8 +13208,14 @@
       <c r="N238" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R238" t="s">
+        <v>702</v>
+      </c>
+      <c r="S238" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="239" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>638</v>
       </c>
@@ -11787,8 +13251,14 @@
       <c r="N239" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R239" t="s">
+        <v>702</v>
+      </c>
+      <c r="S239" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="240" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>638</v>
       </c>
@@ -11824,8 +13294,14 @@
       <c r="N240" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R240" t="s">
+        <v>702</v>
+      </c>
+      <c r="S240" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="241" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>638</v>
       </c>
@@ -11861,8 +13337,14 @@
       <c r="N241" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R241" t="s">
+        <v>702</v>
+      </c>
+      <c r="S241" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="242" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>639</v>
       </c>
@@ -11898,8 +13380,14 @@
       <c r="N242" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R242" t="s">
+        <v>702</v>
+      </c>
+      <c r="S242" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="243" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>639</v>
       </c>
@@ -11935,8 +13423,14 @@
       <c r="N243" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R243" t="s">
+        <v>702</v>
+      </c>
+      <c r="S243" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="244" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>640</v>
       </c>
@@ -11972,8 +13466,14 @@
       <c r="N244" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R244" t="s">
+        <v>702</v>
+      </c>
+      <c r="S244" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="245" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>640</v>
       </c>
@@ -12009,8 +13509,14 @@
       <c r="N245" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R245" t="s">
+        <v>702</v>
+      </c>
+      <c r="S245" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="246" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>640</v>
       </c>
@@ -12046,8 +13552,14 @@
       <c r="N246" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R246" t="s">
+        <v>702</v>
+      </c>
+      <c r="S246" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="247" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>640</v>
       </c>
@@ -12083,8 +13595,14 @@
       <c r="N247" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R247" t="s">
+        <v>702</v>
+      </c>
+      <c r="S247" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="248" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>640</v>
       </c>
@@ -12120,8 +13638,14 @@
       <c r="N248" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R248" t="s">
+        <v>702</v>
+      </c>
+      <c r="S248" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="249" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>640</v>
       </c>
@@ -12157,8 +13681,14 @@
       <c r="N249" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R249" t="s">
+        <v>702</v>
+      </c>
+      <c r="S249" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="250" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>640</v>
       </c>
@@ -12194,8 +13724,14 @@
       <c r="N250" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R250" t="s">
+        <v>702</v>
+      </c>
+      <c r="S250" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="251" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>640</v>
       </c>
@@ -12231,8 +13767,14 @@
       <c r="N251" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R251" t="s">
+        <v>702</v>
+      </c>
+      <c r="S251" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="252" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>640</v>
       </c>
@@ -12268,8 +13810,14 @@
       <c r="N252" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R252" t="s">
+        <v>702</v>
+      </c>
+      <c r="S252" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="253" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>640</v>
       </c>
@@ -12305,8 +13853,14 @@
       <c r="N253" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R253" t="s">
+        <v>702</v>
+      </c>
+      <c r="S253" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="254" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>640</v>
       </c>
@@ -12342,8 +13896,14 @@
       <c r="N254" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R254" t="s">
+        <v>702</v>
+      </c>
+      <c r="S254" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="255" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>640</v>
       </c>
@@ -12379,8 +13939,14 @@
       <c r="N255" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R255" t="s">
+        <v>702</v>
+      </c>
+      <c r="S255" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="256" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>641</v>
       </c>
@@ -12416,8 +13982,14 @@
       <c r="N256" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R256" t="s">
+        <v>702</v>
+      </c>
+      <c r="S256" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="257" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>641</v>
       </c>
@@ -12453,8 +14025,14 @@
       <c r="N257" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R257" t="s">
+        <v>702</v>
+      </c>
+      <c r="S257" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="258" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>641</v>
       </c>
@@ -12490,8 +14068,14 @@
       <c r="N258" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R258" t="s">
+        <v>702</v>
+      </c>
+      <c r="S258" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="259" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>642</v>
       </c>
@@ -12527,8 +14111,14 @@
       <c r="N259" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R259" t="s">
+        <v>702</v>
+      </c>
+      <c r="S259" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="260" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>642</v>
       </c>
@@ -12564,8 +14154,14 @@
       <c r="N260" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R260" t="s">
+        <v>702</v>
+      </c>
+      <c r="S260" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="261" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>642</v>
       </c>
@@ -12601,8 +14197,14 @@
       <c r="N261" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R261" t="s">
+        <v>702</v>
+      </c>
+      <c r="S261" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="262" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>642</v>
       </c>
@@ -12638,8 +14240,14 @@
       <c r="N262" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R262" t="s">
+        <v>702</v>
+      </c>
+      <c r="S262" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="263" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>642</v>
       </c>
@@ -12675,8 +14283,14 @@
       <c r="N263" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R263" t="s">
+        <v>702</v>
+      </c>
+      <c r="S263" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="264" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>642</v>
       </c>
@@ -12712,8 +14326,14 @@
       <c r="N264" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R264" t="s">
+        <v>702</v>
+      </c>
+      <c r="S264" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="265" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>642</v>
       </c>
@@ -12749,8 +14369,14 @@
       <c r="N265" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R265" t="s">
+        <v>702</v>
+      </c>
+      <c r="S265" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="266" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>642</v>
       </c>
@@ -12786,8 +14412,14 @@
       <c r="N266" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R266" t="s">
+        <v>702</v>
+      </c>
+      <c r="S266" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="267" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>642</v>
       </c>
@@ -12823,8 +14455,14 @@
       <c r="N267" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R267" t="s">
+        <v>702</v>
+      </c>
+      <c r="S267" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="268" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>642</v>
       </c>
@@ -12860,8 +14498,14 @@
       <c r="N268" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R268" t="s">
+        <v>702</v>
+      </c>
+      <c r="S268" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="269" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>642</v>
       </c>
@@ -12897,8 +14541,14 @@
       <c r="N269" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R269" t="s">
+        <v>702</v>
+      </c>
+      <c r="S269" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="270" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>642</v>
       </c>
@@ -12934,8 +14584,14 @@
       <c r="N270" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R270" t="s">
+        <v>702</v>
+      </c>
+      <c r="S270" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="271" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>642</v>
       </c>
@@ -12971,8 +14627,14 @@
       <c r="N271" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R271" t="s">
+        <v>702</v>
+      </c>
+      <c r="S271" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="272" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>642</v>
       </c>
@@ -13008,8 +14670,14 @@
       <c r="N272" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R272" t="s">
+        <v>702</v>
+      </c>
+      <c r="S272" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="273" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>642</v>
       </c>
@@ -13045,8 +14713,14 @@
       <c r="N273" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R273" t="s">
+        <v>702</v>
+      </c>
+      <c r="S273" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="274" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>642</v>
       </c>
@@ -13082,8 +14756,14 @@
       <c r="N274" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R274" t="s">
+        <v>702</v>
+      </c>
+      <c r="S274" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="275" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>642</v>
       </c>
@@ -13119,8 +14799,14 @@
       <c r="N275" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R275" t="s">
+        <v>702</v>
+      </c>
+      <c r="S275" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="276" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>642</v>
       </c>
@@ -13156,8 +14842,14 @@
       <c r="N276" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R276" t="s">
+        <v>702</v>
+      </c>
+      <c r="S276" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="277" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>642</v>
       </c>
@@ -13193,8 +14885,14 @@
       <c r="N277" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R277" t="s">
+        <v>702</v>
+      </c>
+      <c r="S277" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="278" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>642</v>
       </c>
@@ -13231,8 +14929,14 @@
       <c r="N278" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R278" t="s">
+        <v>702</v>
+      </c>
+      <c r="S278" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="279" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>642</v>
       </c>
@@ -13268,8 +14972,14 @@
       <c r="N279" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R279" t="s">
+        <v>702</v>
+      </c>
+      <c r="S279" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="280" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>642</v>
       </c>
@@ -13305,8 +15015,14 @@
       <c r="N280" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R280" t="s">
+        <v>702</v>
+      </c>
+      <c r="S280" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="281" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>642</v>
       </c>
@@ -13342,8 +15058,14 @@
       <c r="N281" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R281" t="s">
+        <v>702</v>
+      </c>
+      <c r="S281" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="282" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>642</v>
       </c>
@@ -13379,8 +15101,14 @@
       <c r="N282" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R282" t="s">
+        <v>702</v>
+      </c>
+      <c r="S282" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="283" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>642</v>
       </c>
@@ -13416,8 +15144,14 @@
       <c r="N283" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R283" t="s">
+        <v>702</v>
+      </c>
+      <c r="S283" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="284" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>642</v>
       </c>
@@ -13453,8 +15187,14 @@
       <c r="N284" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R284" t="s">
+        <v>702</v>
+      </c>
+      <c r="S284" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="285" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>643</v>
       </c>
@@ -13496,8 +15236,14 @@
       <c r="N285" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R285" t="s">
+        <v>702</v>
+      </c>
+      <c r="S285" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="286" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>643</v>
       </c>
@@ -13539,8 +15285,14 @@
       <c r="N286" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R286" t="s">
+        <v>702</v>
+      </c>
+      <c r="S286" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="287" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>643</v>
       </c>
@@ -13582,8 +15334,14 @@
       <c r="N287" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R287" t="s">
+        <v>702</v>
+      </c>
+      <c r="S287" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="288" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>643</v>
       </c>
@@ -13625,8 +15383,14 @@
       <c r="N288" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R288" t="s">
+        <v>702</v>
+      </c>
+      <c r="S288" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="289" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>643</v>
       </c>
@@ -13668,8 +15432,14 @@
       <c r="N289" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R289" t="s">
+        <v>702</v>
+      </c>
+      <c r="S289" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="290" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>643</v>
       </c>
@@ -13711,8 +15481,14 @@
       <c r="N290" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R290" t="s">
+        <v>702</v>
+      </c>
+      <c r="S290" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="291" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>643</v>
       </c>
@@ -13754,8 +15530,14 @@
       <c r="N291" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R291" t="s">
+        <v>702</v>
+      </c>
+      <c r="S291" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="292" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>643</v>
       </c>
@@ -13797,8 +15579,14 @@
       <c r="N292" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R292" t="s">
+        <v>702</v>
+      </c>
+      <c r="S292" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="293" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>643</v>
       </c>
@@ -13840,8 +15628,14 @@
       <c r="N293" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R293" t="s">
+        <v>702</v>
+      </c>
+      <c r="S293" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="294" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>643</v>
       </c>
@@ -13883,8 +15677,14 @@
       <c r="N294" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R294" t="s">
+        <v>702</v>
+      </c>
+      <c r="S294" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="295" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>643</v>
       </c>
@@ -13926,8 +15726,14 @@
       <c r="N295" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R295" t="s">
+        <v>702</v>
+      </c>
+      <c r="S295" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="296" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>643</v>
       </c>
@@ -13969,8 +15775,14 @@
       <c r="N296" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R296" t="s">
+        <v>702</v>
+      </c>
+      <c r="S296" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="297" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>643</v>
       </c>
@@ -14012,8 +15824,14 @@
       <c r="N297" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R297" t="s">
+        <v>702</v>
+      </c>
+      <c r="S297" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="298" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>643</v>
       </c>
@@ -14055,8 +15873,14 @@
       <c r="N298" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R298" t="s">
+        <v>702</v>
+      </c>
+      <c r="S298" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="299" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>644</v>
       </c>
@@ -14092,8 +15916,14 @@
       <c r="N299" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R299" t="s">
+        <v>702</v>
+      </c>
+      <c r="S299" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="300" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>645</v>
       </c>
@@ -14135,8 +15965,14 @@
       <c r="N300" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R300" t="s">
+        <v>702</v>
+      </c>
+      <c r="S300" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="301" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>645</v>
       </c>
@@ -14178,8 +16014,14 @@
       <c r="N301" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R301" t="s">
+        <v>702</v>
+      </c>
+      <c r="S301" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="302" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>645</v>
       </c>
@@ -14221,8 +16063,14 @@
       <c r="N302" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R302" t="s">
+        <v>702</v>
+      </c>
+      <c r="S302" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="303" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>645</v>
       </c>
@@ -14264,8 +16112,14 @@
       <c r="N303" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R303" t="s">
+        <v>702</v>
+      </c>
+      <c r="S303" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="304" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>645</v>
       </c>
@@ -14307,8 +16161,14 @@
       <c r="N304" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R304" t="s">
+        <v>702</v>
+      </c>
+      <c r="S304" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="305" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>645</v>
       </c>
@@ -14350,8 +16210,14 @@
       <c r="N305" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R305" t="s">
+        <v>702</v>
+      </c>
+      <c r="S305" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="306" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>645</v>
       </c>
@@ -14393,8 +16259,14 @@
       <c r="N306" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R306" t="s">
+        <v>702</v>
+      </c>
+      <c r="S306" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="307" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>645</v>
       </c>
@@ -14436,8 +16308,14 @@
       <c r="N307" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R307" t="s">
+        <v>702</v>
+      </c>
+      <c r="S307" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="308" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>645</v>
       </c>
@@ -14479,8 +16357,14 @@
       <c r="N308" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R308" t="s">
+        <v>702</v>
+      </c>
+      <c r="S308" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="309" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>645</v>
       </c>
@@ -14522,8 +16406,14 @@
       <c r="N309" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R309" t="s">
+        <v>702</v>
+      </c>
+      <c r="S309" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="310" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>645</v>
       </c>
@@ -14565,8 +16455,14 @@
       <c r="N310" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R310" t="s">
+        <v>702</v>
+      </c>
+      <c r="S310" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="311" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>645</v>
       </c>
@@ -14608,8 +16504,14 @@
       <c r="N311" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R311" t="s">
+        <v>702</v>
+      </c>
+      <c r="S311" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="312" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>645</v>
       </c>
@@ -14651,8 +16553,14 @@
       <c r="N312" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R312" t="s">
+        <v>702</v>
+      </c>
+      <c r="S312" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="313" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>645</v>
       </c>
@@ -14694,8 +16602,14 @@
       <c r="N313" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R313" t="s">
+        <v>702</v>
+      </c>
+      <c r="S313" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="314" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>645</v>
       </c>
@@ -14737,8 +16651,14 @@
       <c r="N314" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R314" t="s">
+        <v>702</v>
+      </c>
+      <c r="S314" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="315" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>646</v>
       </c>
@@ -14774,8 +16694,14 @@
       <c r="N315" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R315" t="s">
+        <v>702</v>
+      </c>
+      <c r="S315" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="316" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>646</v>
       </c>
@@ -14811,8 +16737,14 @@
       <c r="N316" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R316" t="s">
+        <v>702</v>
+      </c>
+      <c r="S316" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="317" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>646</v>
       </c>
@@ -14848,8 +16780,14 @@
       <c r="N317" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R317" t="s">
+        <v>702</v>
+      </c>
+      <c r="S317" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="318" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>646</v>
       </c>
@@ -14885,8 +16823,14 @@
       <c r="N318" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R318" t="s">
+        <v>702</v>
+      </c>
+      <c r="S318" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="319" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>646</v>
       </c>
@@ -14922,8 +16866,14 @@
       <c r="N319" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R319" t="s">
+        <v>702</v>
+      </c>
+      <c r="S319" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="320" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>647</v>
       </c>
@@ -14965,8 +16915,14 @@
       <c r="N320" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R320" t="s">
+        <v>702</v>
+      </c>
+      <c r="S320" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="321" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>647</v>
       </c>
@@ -15008,8 +16964,14 @@
       <c r="N321" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R321" t="s">
+        <v>702</v>
+      </c>
+      <c r="S321" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="322" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>647</v>
       </c>
@@ -15051,8 +17013,14 @@
       <c r="N322" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R322" t="s">
+        <v>702</v>
+      </c>
+      <c r="S322" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="323" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>647</v>
       </c>
@@ -15094,8 +17062,14 @@
       <c r="N323" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R323" t="s">
+        <v>702</v>
+      </c>
+      <c r="S323" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="324" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>647</v>
       </c>
@@ -15137,8 +17111,14 @@
       <c r="N324" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R324" t="s">
+        <v>702</v>
+      </c>
+      <c r="S324" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="325" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>647</v>
       </c>
@@ -15180,8 +17160,14 @@
       <c r="N325" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R325" t="s">
+        <v>702</v>
+      </c>
+      <c r="S325" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="326" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>648</v>
       </c>
@@ -15223,8 +17209,14 @@
       <c r="N326" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R326" t="s">
+        <v>702</v>
+      </c>
+      <c r="S326" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="327" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>648</v>
       </c>
@@ -15266,8 +17258,14 @@
       <c r="N327" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R327" t="s">
+        <v>702</v>
+      </c>
+      <c r="S327" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="328" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>648</v>
       </c>
@@ -15309,8 +17307,14 @@
       <c r="N328" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R328" t="s">
+        <v>702</v>
+      </c>
+      <c r="S328" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="329" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>648</v>
       </c>
@@ -15352,8 +17356,14 @@
       <c r="N329" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R329" t="s">
+        <v>702</v>
+      </c>
+      <c r="S329" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="330" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>648</v>
       </c>
@@ -15395,8 +17405,14 @@
       <c r="N330" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R330" t="s">
+        <v>702</v>
+      </c>
+      <c r="S330" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="331" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>648</v>
       </c>
@@ -15438,8 +17454,14 @@
       <c r="N331" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R331" t="s">
+        <v>702</v>
+      </c>
+      <c r="S331" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="332" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>648</v>
       </c>
@@ -15481,8 +17503,14 @@
       <c r="N332" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R332" t="s">
+        <v>702</v>
+      </c>
+      <c r="S332" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="333" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>648</v>
       </c>
@@ -15524,8 +17552,14 @@
       <c r="N333" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R333" t="s">
+        <v>702</v>
+      </c>
+      <c r="S333" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="334" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>648</v>
       </c>
@@ -15567,8 +17601,14 @@
       <c r="N334" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R334" t="s">
+        <v>702</v>
+      </c>
+      <c r="S334" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="335" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>648</v>
       </c>
@@ -15610,8 +17650,14 @@
       <c r="N335" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R335" t="s">
+        <v>702</v>
+      </c>
+      <c r="S335" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="336" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>648</v>
       </c>
@@ -15653,8 +17699,14 @@
       <c r="N336" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R336" t="s">
+        <v>702</v>
+      </c>
+      <c r="S336" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="337" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>648</v>
       </c>
@@ -15696,8 +17748,14 @@
       <c r="N337" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R337" t="s">
+        <v>702</v>
+      </c>
+      <c r="S337" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="338" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>648</v>
       </c>
@@ -15739,8 +17797,14 @@
       <c r="N338" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R338" t="s">
+        <v>702</v>
+      </c>
+      <c r="S338" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="339" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>648</v>
       </c>
@@ -15782,8 +17846,14 @@
       <c r="N339" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R339" t="s">
+        <v>702</v>
+      </c>
+      <c r="S339" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="340" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>648</v>
       </c>
@@ -15825,8 +17895,14 @@
       <c r="N340" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R340" t="s">
+        <v>702</v>
+      </c>
+      <c r="S340" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="341" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>648</v>
       </c>
@@ -15868,8 +17944,14 @@
       <c r="N341" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R341" t="s">
+        <v>702</v>
+      </c>
+      <c r="S341" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="342" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>648</v>
       </c>
@@ -15911,8 +17993,14 @@
       <c r="N342" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R342" t="s">
+        <v>702</v>
+      </c>
+      <c r="S342" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="343" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>649</v>
       </c>
@@ -15948,8 +18036,14 @@
       <c r="N343" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R343" t="s">
+        <v>702</v>
+      </c>
+      <c r="S343" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="344" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>649</v>
       </c>
@@ -15985,8 +18079,14 @@
       <c r="N344" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R344" t="s">
+        <v>702</v>
+      </c>
+      <c r="S344" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="345" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>650</v>
       </c>
@@ -16022,8 +18122,14 @@
       <c r="N345" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R345" t="s">
+        <v>702</v>
+      </c>
+      <c r="S345" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="346" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>650</v>
       </c>
@@ -16059,8 +18165,14 @@
       <c r="N346" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R346" t="s">
+        <v>702</v>
+      </c>
+      <c r="S346" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="347" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>650</v>
       </c>
@@ -16096,8 +18208,14 @@
       <c r="N347" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R347" t="s">
+        <v>702</v>
+      </c>
+      <c r="S347" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="348" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>650</v>
       </c>
@@ -16133,8 +18251,14 @@
       <c r="N348" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R348" t="s">
+        <v>702</v>
+      </c>
+      <c r="S348" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="349" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>650</v>
       </c>
@@ -16170,8 +18294,14 @@
       <c r="N349" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R349" t="s">
+        <v>702</v>
+      </c>
+      <c r="S349" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="350" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>650</v>
       </c>
@@ -16207,8 +18337,14 @@
       <c r="N350" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R350" t="s">
+        <v>702</v>
+      </c>
+      <c r="S350" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="351" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>650</v>
       </c>
@@ -16244,8 +18380,14 @@
       <c r="N351" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R351" t="s">
+        <v>702</v>
+      </c>
+      <c r="S351" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="352" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>651</v>
       </c>
@@ -16281,8 +18423,14 @@
       <c r="N352" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R352" t="s">
+        <v>702</v>
+      </c>
+      <c r="S352" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="353" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>652</v>
       </c>
@@ -16319,8 +18467,14 @@
       <c r="N353" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R353" t="s">
+        <v>702</v>
+      </c>
+      <c r="S353" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="354" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>652</v>
       </c>
@@ -16357,8 +18511,14 @@
       <c r="N354" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R354" t="s">
+        <v>702</v>
+      </c>
+      <c r="S354" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="355" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>652</v>
       </c>
@@ -16395,8 +18555,14 @@
       <c r="N355" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R355" t="s">
+        <v>702</v>
+      </c>
+      <c r="S355" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="356" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>652</v>
       </c>
@@ -16433,8 +18599,14 @@
       <c r="N356" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R356" t="s">
+        <v>702</v>
+      </c>
+      <c r="S356" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="357" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>652</v>
       </c>
@@ -16471,8 +18643,14 @@
       <c r="N357" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R357" t="s">
+        <v>702</v>
+      </c>
+      <c r="S357" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="358" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>652</v>
       </c>
@@ -16509,8 +18687,14 @@
       <c r="N358" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R358" t="s">
+        <v>702</v>
+      </c>
+      <c r="S358" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="359" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>652</v>
       </c>
@@ -16547,8 +18731,14 @@
       <c r="N359" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R359" t="s">
+        <v>702</v>
+      </c>
+      <c r="S359" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="360" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>652</v>
       </c>
@@ -16585,8 +18775,14 @@
       <c r="N360" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R360" t="s">
+        <v>702</v>
+      </c>
+      <c r="S360" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="361" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>652</v>
       </c>
@@ -16623,8 +18819,14 @@
       <c r="N361" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R361" t="s">
+        <v>702</v>
+      </c>
+      <c r="S361" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="362" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>653</v>
       </c>
@@ -16666,8 +18868,14 @@
       <c r="N362" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R362" t="s">
+        <v>702</v>
+      </c>
+      <c r="S362" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="363" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>653</v>
       </c>
@@ -16709,8 +18917,14 @@
       <c r="N363" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R363" t="s">
+        <v>702</v>
+      </c>
+      <c r="S363" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="364" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>653</v>
       </c>
@@ -16752,8 +18966,14 @@
       <c r="N364" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R364" t="s">
+        <v>702</v>
+      </c>
+      <c r="S364" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="365" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>653</v>
       </c>
@@ -16795,8 +19015,14 @@
       <c r="N365" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R365" t="s">
+        <v>702</v>
+      </c>
+      <c r="S365" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="366" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>653</v>
       </c>
@@ -16838,8 +19064,14 @@
       <c r="N366" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R366" t="s">
+        <v>702</v>
+      </c>
+      <c r="S366" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="367" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>653</v>
       </c>
@@ -16881,8 +19113,14 @@
       <c r="N367" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R367" t="s">
+        <v>702</v>
+      </c>
+      <c r="S367" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="368" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>653</v>
       </c>
@@ -16924,8 +19162,14 @@
       <c r="N368" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R368" t="s">
+        <v>702</v>
+      </c>
+      <c r="S368" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="369" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>653</v>
       </c>
@@ -16967,8 +19211,14 @@
       <c r="N369" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R369" t="s">
+        <v>702</v>
+      </c>
+      <c r="S369" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="370" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>653</v>
       </c>
@@ -17010,8 +19260,14 @@
       <c r="N370" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R370" t="s">
+        <v>702</v>
+      </c>
+      <c r="S370" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="371" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>653</v>
       </c>
@@ -17053,8 +19309,14 @@
       <c r="N371" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R371" t="s">
+        <v>702</v>
+      </c>
+      <c r="S371" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="372" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>653</v>
       </c>
@@ -17096,8 +19358,14 @@
       <c r="N372" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R372" t="s">
+        <v>702</v>
+      </c>
+      <c r="S372" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="373" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>653</v>
       </c>
@@ -17139,8 +19407,14 @@
       <c r="N373" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R373" t="s">
+        <v>702</v>
+      </c>
+      <c r="S373" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="374" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>653</v>
       </c>
@@ -17182,8 +19456,14 @@
       <c r="N374" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R374" t="s">
+        <v>702</v>
+      </c>
+      <c r="S374" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="375" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>653</v>
       </c>
@@ -17222,8 +19502,14 @@
       <c r="N375" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R375" t="s">
+        <v>702</v>
+      </c>
+      <c r="S375" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="376" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>653</v>
       </c>
@@ -17265,8 +19551,14 @@
       <c r="N376" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R376" t="s">
+        <v>702</v>
+      </c>
+      <c r="S376" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="377" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>653</v>
       </c>
@@ -17308,8 +19600,14 @@
       <c r="N377" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R377" t="s">
+        <v>702</v>
+      </c>
+      <c r="S377" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="378" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>653</v>
       </c>
@@ -17352,8 +19650,14 @@
       <c r="N378" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R378" t="s">
+        <v>702</v>
+      </c>
+      <c r="S378" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="379" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>653</v>
       </c>
@@ -17395,8 +19699,14 @@
       <c r="N379" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R379" t="s">
+        <v>702</v>
+      </c>
+      <c r="S379" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="380" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>653</v>
       </c>
@@ -17438,8 +19748,14 @@
       <c r="N380" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R380" t="s">
+        <v>702</v>
+      </c>
+      <c r="S380" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="381" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>653</v>
       </c>
@@ -17481,8 +19797,14 @@
       <c r="N381" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R381" t="s">
+        <v>702</v>
+      </c>
+      <c r="S381" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="382" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>653</v>
       </c>
@@ -17524,8 +19846,14 @@
       <c r="N382" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R382" t="s">
+        <v>702</v>
+      </c>
+      <c r="S382" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="383" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>653</v>
       </c>
@@ -17567,8 +19895,14 @@
       <c r="N383" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R383" t="s">
+        <v>702</v>
+      </c>
+      <c r="S383" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="384" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>653</v>
       </c>
@@ -17610,8 +19944,14 @@
       <c r="N384" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R384" t="s">
+        <v>702</v>
+      </c>
+      <c r="S384" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="385" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>653</v>
       </c>
@@ -17653,8 +19993,14 @@
       <c r="N385" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R385" t="s">
+        <v>702</v>
+      </c>
+      <c r="S385" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="386" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>653</v>
       </c>
@@ -17696,8 +20042,14 @@
       <c r="N386" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R386" t="s">
+        <v>702</v>
+      </c>
+      <c r="S386" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="387" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>653</v>
       </c>
@@ -17739,8 +20091,14 @@
       <c r="N387" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R387" t="s">
+        <v>702</v>
+      </c>
+      <c r="S387" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="388" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>653</v>
       </c>
@@ -17782,8 +20140,14 @@
       <c r="N388" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R388" t="s">
+        <v>702</v>
+      </c>
+      <c r="S388" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="389" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>653</v>
       </c>
@@ -17825,8 +20189,14 @@
       <c r="N389" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R389" t="s">
+        <v>702</v>
+      </c>
+      <c r="S389" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="390" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>653</v>
       </c>
@@ -17868,8 +20238,14 @@
       <c r="N390" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R390" t="s">
+        <v>702</v>
+      </c>
+      <c r="S390" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="391" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>653</v>
       </c>
@@ -17911,8 +20287,14 @@
       <c r="N391" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R391" t="s">
+        <v>702</v>
+      </c>
+      <c r="S391" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="392" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>653</v>
       </c>
@@ -17954,8 +20336,14 @@
       <c r="N392" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R392" t="s">
+        <v>702</v>
+      </c>
+      <c r="S392" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="393" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>653</v>
       </c>
@@ -17997,8 +20385,14 @@
       <c r="N393" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R393" t="s">
+        <v>702</v>
+      </c>
+      <c r="S393" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="394" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>653</v>
       </c>
@@ -18040,8 +20434,14 @@
       <c r="N394" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R394" t="s">
+        <v>702</v>
+      </c>
+      <c r="S394" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="395" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>653</v>
       </c>
@@ -18083,8 +20483,14 @@
       <c r="N395" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R395" t="s">
+        <v>702</v>
+      </c>
+      <c r="S395" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="396" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>653</v>
       </c>
@@ -18126,8 +20532,14 @@
       <c r="N396" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R396" t="s">
+        <v>702</v>
+      </c>
+      <c r="S396" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="397" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>653</v>
       </c>
@@ -18169,8 +20581,14 @@
       <c r="N397" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R397" t="s">
+        <v>702</v>
+      </c>
+      <c r="S397" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="398" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>653</v>
       </c>
@@ -18212,8 +20630,14 @@
       <c r="N398" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R398" t="s">
+        <v>702</v>
+      </c>
+      <c r="S398" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="399" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>653</v>
       </c>
@@ -18255,8 +20679,14 @@
       <c r="N399" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R399" t="s">
+        <v>702</v>
+      </c>
+      <c r="S399" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="400" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>654</v>
       </c>
@@ -18292,8 +20722,14 @@
       <c r="N400" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R400" t="s">
+        <v>702</v>
+      </c>
+      <c r="S400" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="401" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>654</v>
       </c>
@@ -18329,8 +20765,14 @@
       <c r="N401" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R401" t="s">
+        <v>702</v>
+      </c>
+      <c r="S401" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="402" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>654</v>
       </c>
@@ -18366,8 +20808,14 @@
       <c r="N402" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R402" t="s">
+        <v>702</v>
+      </c>
+      <c r="S402" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="403" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>654</v>
       </c>
@@ -18403,8 +20851,14 @@
       <c r="N403" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="404" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R403" t="s">
+        <v>702</v>
+      </c>
+      <c r="S403" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="404" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>655</v>
       </c>
@@ -18440,8 +20894,14 @@
       <c r="N404" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="405" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R404" t="s">
+        <v>702</v>
+      </c>
+      <c r="S404" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="405" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>656</v>
       </c>
@@ -18478,8 +20938,14 @@
       <c r="N405" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="406" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R405" t="s">
+        <v>702</v>
+      </c>
+      <c r="S405" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="406" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>656</v>
       </c>
@@ -18516,8 +20982,14 @@
       <c r="N406" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="407" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R406" t="s">
+        <v>702</v>
+      </c>
+      <c r="S406" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="407" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>656</v>
       </c>
@@ -18554,8 +21026,14 @@
       <c r="N407" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="408" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R407" t="s">
+        <v>702</v>
+      </c>
+      <c r="S407" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="408" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>656</v>
       </c>
@@ -18592,8 +21070,14 @@
       <c r="N408" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="409" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R408" t="s">
+        <v>702</v>
+      </c>
+      <c r="S408" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="409" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>656</v>
       </c>
@@ -18630,8 +21114,14 @@
       <c r="N409" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="410" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R409" t="s">
+        <v>702</v>
+      </c>
+      <c r="S409" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="410" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>656</v>
       </c>
@@ -18668,8 +21158,14 @@
       <c r="N410" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="411" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R410" t="s">
+        <v>702</v>
+      </c>
+      <c r="S410" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="411" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>656</v>
       </c>
@@ -18706,8 +21202,14 @@
       <c r="N411" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="412" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R411" t="s">
+        <v>702</v>
+      </c>
+      <c r="S411" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="412" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>656</v>
       </c>
@@ -18744,8 +21246,14 @@
       <c r="N412" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="413" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R412" t="s">
+        <v>702</v>
+      </c>
+      <c r="S412" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="413" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>656</v>
       </c>
@@ -18782,8 +21290,14 @@
       <c r="N413" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="414" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R413" t="s">
+        <v>702</v>
+      </c>
+      <c r="S413" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="414" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>656</v>
       </c>
@@ -18820,8 +21334,14 @@
       <c r="N414" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="415" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R414" t="s">
+        <v>702</v>
+      </c>
+      <c r="S414" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="415" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>656</v>
       </c>
@@ -18858,8 +21378,14 @@
       <c r="N415" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="416" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R415" t="s">
+        <v>702</v>
+      </c>
+      <c r="S415" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="416" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>657</v>
       </c>
@@ -18895,8 +21421,14 @@
       <c r="N416" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="417" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R416" t="s">
+        <v>701</v>
+      </c>
+      <c r="S416" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="417" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>657</v>
       </c>
@@ -18932,8 +21464,14 @@
       <c r="N417" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="418" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R417" t="s">
+        <v>701</v>
+      </c>
+      <c r="S417" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="418" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>657</v>
       </c>
@@ -18969,8 +21507,14 @@
       <c r="N418" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="419" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R418" t="s">
+        <v>701</v>
+      </c>
+      <c r="S418" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="419" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>657</v>
       </c>
@@ -19006,8 +21550,14 @@
       <c r="N419" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="420" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R419" t="s">
+        <v>701</v>
+      </c>
+      <c r="S419" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="420" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>657</v>
       </c>
@@ -19043,8 +21593,14 @@
       <c r="N420" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="421" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R420" t="s">
+        <v>701</v>
+      </c>
+      <c r="S420" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="421" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>657</v>
       </c>
@@ -19080,8 +21636,14 @@
       <c r="N421" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="422" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R421" t="s">
+        <v>701</v>
+      </c>
+      <c r="S421" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="422" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>657</v>
       </c>
@@ -19117,8 +21679,14 @@
       <c r="N422" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="423" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R422" t="s">
+        <v>701</v>
+      </c>
+      <c r="S422" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="423" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>657</v>
       </c>
@@ -19154,8 +21722,14 @@
       <c r="N423" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="424" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R423" t="s">
+        <v>701</v>
+      </c>
+      <c r="S423" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="424" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>657</v>
       </c>
@@ -19191,8 +21765,14 @@
       <c r="N424" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="425" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R424" t="s">
+        <v>701</v>
+      </c>
+      <c r="S424" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="425" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>657</v>
       </c>
@@ -19228,8 +21808,14 @@
       <c r="N425" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="426" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R425" t="s">
+        <v>701</v>
+      </c>
+      <c r="S425" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="426" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>658</v>
       </c>
@@ -19271,8 +21857,14 @@
       <c r="N426" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="427" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R426" t="s">
+        <v>702</v>
+      </c>
+      <c r="S426" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="427" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>658</v>
       </c>
@@ -19314,8 +21906,14 @@
       <c r="N427" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="428" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R427" t="s">
+        <v>702</v>
+      </c>
+      <c r="S427" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="428" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>659</v>
       </c>
@@ -19351,8 +21949,14 @@
       <c r="N428" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="429" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R428" t="s">
+        <v>702</v>
+      </c>
+      <c r="S428" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="429" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>659</v>
       </c>
@@ -19388,8 +21992,14 @@
       <c r="N429" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="430" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R429" t="s">
+        <v>702</v>
+      </c>
+      <c r="S429" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="430" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>659</v>
       </c>
@@ -19425,8 +22035,14 @@
       <c r="N430" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="431" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R430" t="s">
+        <v>702</v>
+      </c>
+      <c r="S430" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="431" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>659</v>
       </c>
@@ -19462,8 +22078,14 @@
       <c r="N431" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="432" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R431" t="s">
+        <v>702</v>
+      </c>
+      <c r="S431" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="432" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>659</v>
       </c>
@@ -19499,8 +22121,14 @@
       <c r="N432" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="433" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R432" t="s">
+        <v>702</v>
+      </c>
+      <c r="S432" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="433" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>659</v>
       </c>
@@ -19536,8 +22164,14 @@
       <c r="N433" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="434" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R433" t="s">
+        <v>702</v>
+      </c>
+      <c r="S433" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="434" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>659</v>
       </c>
@@ -19573,8 +22207,14 @@
       <c r="N434" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="435" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R434" t="s">
+        <v>702</v>
+      </c>
+      <c r="S434" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="435" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>659</v>
       </c>
@@ -19610,8 +22250,14 @@
       <c r="N435" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="436" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R435" t="s">
+        <v>702</v>
+      </c>
+      <c r="S435" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="436" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>660</v>
       </c>
@@ -19646,6 +22292,12 @@
       </c>
       <c r="N436" t="s">
         <v>692</v>
+      </c>
+      <c r="R436" t="s">
+        <v>702</v>
+      </c>
+      <c r="S436" t="s">
+        <v>705</v>
       </c>
     </row>
   </sheetData>

--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/house_model_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A540585-2526-9944-916C-8611AB216960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8C79C3-2CE8-1F4F-85E8-35399414900E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4225" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5067" uniqueCount="709">
   <si>
     <t>State</t>
   </si>
@@ -2637,8 +2637,8 @@
     <col min="1" max="1" width="18.1640625" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
     <col min="3" max="4" width="29.83203125" customWidth="1"/>
-    <col min="5" max="6" width="20.6640625" style="3" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="30.1640625" style="3" hidden="1" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="30.1640625" style="3" customWidth="1"/>
     <col min="8" max="8" width="25.33203125" customWidth="1"/>
     <col min="9" max="9" width="24.1640625" customWidth="1"/>
     <col min="10" max="10" width="13.6640625" hidden="1" customWidth="1"/>
@@ -2647,8 +2647,8 @@
     <col min="13" max="13" width="21" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="29.1640625" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="19.5" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="21.33203125" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="23.83203125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="21.33203125" customWidth="1"/>
+    <col min="17" max="17" width="23.83203125" customWidth="1"/>
     <col min="18" max="18" width="16.1640625" customWidth="1"/>
     <col min="19" max="19" width="29.6640625" customWidth="1"/>
     <col min="20" max="20" width="22" customWidth="1"/>
@@ -3030,6 +3030,9 @@
       <c r="N9" t="s">
         <v>691</v>
       </c>
+      <c r="O9" t="s">
+        <v>690</v>
+      </c>
       <c r="R9" t="s">
         <v>703</v>
       </c>
@@ -3073,6 +3076,12 @@
       <c r="N10" t="s">
         <v>691</v>
       </c>
+      <c r="O10" t="s">
+        <v>690</v>
+      </c>
+      <c r="P10" t="s">
+        <v>690</v>
+      </c>
       <c r="R10" t="s">
         <v>702</v>
       </c>
@@ -3116,6 +3125,12 @@
       <c r="N11" t="s">
         <v>689</v>
       </c>
+      <c r="O11" t="s">
+        <v>690</v>
+      </c>
+      <c r="P11" t="s">
+        <v>690</v>
+      </c>
       <c r="R11" t="s">
         <v>702</v>
       </c>
@@ -3159,6 +3174,12 @@
       <c r="N12" t="s">
         <v>690</v>
       </c>
+      <c r="O12" t="s">
+        <v>689</v>
+      </c>
+      <c r="P12" t="s">
+        <v>692</v>
+      </c>
       <c r="R12" t="s">
         <v>702</v>
       </c>
@@ -3202,6 +3223,12 @@
       <c r="N13" t="s">
         <v>689</v>
       </c>
+      <c r="O13" t="s">
+        <v>690</v>
+      </c>
+      <c r="P13" t="s">
+        <v>689</v>
+      </c>
       <c r="R13" t="s">
         <v>702</v>
       </c>
@@ -3245,6 +3272,12 @@
       <c r="N14" t="s">
         <v>691</v>
       </c>
+      <c r="O14" t="s">
+        <v>690</v>
+      </c>
+      <c r="P14" t="s">
+        <v>689</v>
+      </c>
       <c r="R14" t="s">
         <v>702</v>
       </c>
@@ -3288,6 +3321,12 @@
       <c r="N15" t="s">
         <v>691</v>
       </c>
+      <c r="O15" t="s">
+        <v>690</v>
+      </c>
+      <c r="P15" t="s">
+        <v>689</v>
+      </c>
       <c r="R15" t="s">
         <v>702</v>
       </c>
@@ -3331,6 +3370,12 @@
       <c r="N16" t="s">
         <v>690</v>
       </c>
+      <c r="O16" t="s">
+        <v>690</v>
+      </c>
+      <c r="P16" t="s">
+        <v>692</v>
+      </c>
       <c r="R16" t="s">
         <v>702</v>
       </c>
@@ -3374,6 +3419,12 @@
       <c r="N17" t="s">
         <v>691</v>
       </c>
+      <c r="O17" t="s">
+        <v>690</v>
+      </c>
+      <c r="P17" t="s">
+        <v>689</v>
+      </c>
       <c r="R17" t="s">
         <v>702</v>
       </c>
@@ -3417,6 +3468,12 @@
       <c r="N18" t="s">
         <v>691</v>
       </c>
+      <c r="O18" t="s">
+        <v>690</v>
+      </c>
+      <c r="P18" t="s">
+        <v>689</v>
+      </c>
       <c r="R18" t="s">
         <v>702</v>
       </c>
@@ -3466,6 +3523,12 @@
       <c r="N19" t="s">
         <v>692</v>
       </c>
+      <c r="O19" t="s">
+        <v>689</v>
+      </c>
+      <c r="P19" t="s">
+        <v>690</v>
+      </c>
       <c r="R19" t="s">
         <v>702</v>
       </c>
@@ -3515,6 +3578,12 @@
       <c r="N20" t="s">
         <v>691</v>
       </c>
+      <c r="O20" t="s">
+        <v>689</v>
+      </c>
+      <c r="P20" t="s">
+        <v>690</v>
+      </c>
       <c r="R20" t="s">
         <v>702</v>
       </c>
@@ -3564,6 +3633,12 @@
       <c r="N21" t="s">
         <v>691</v>
       </c>
+      <c r="O21" t="s">
+        <v>690</v>
+      </c>
+      <c r="P21" t="s">
+        <v>690</v>
+      </c>
       <c r="R21" t="s">
         <v>702</v>
       </c>
@@ -3613,6 +3688,12 @@
       <c r="N22" t="s">
         <v>691</v>
       </c>
+      <c r="O22" t="s">
+        <v>689</v>
+      </c>
+      <c r="P22" t="s">
+        <v>690</v>
+      </c>
       <c r="R22" t="s">
         <v>702</v>
       </c>
@@ -3656,6 +3737,12 @@
       <c r="N23" t="s">
         <v>691</v>
       </c>
+      <c r="O23" t="s">
+        <v>690</v>
+      </c>
+      <c r="P23" t="s">
+        <v>689</v>
+      </c>
       <c r="R23" t="s">
         <v>701</v>
       </c>
@@ -3699,6 +3786,12 @@
       <c r="N24" t="s">
         <v>691</v>
       </c>
+      <c r="O24" t="s">
+        <v>690</v>
+      </c>
+      <c r="P24" t="s">
+        <v>690</v>
+      </c>
       <c r="R24" t="s">
         <v>701</v>
       </c>
@@ -3742,6 +3835,12 @@
       <c r="N25" t="s">
         <v>691</v>
       </c>
+      <c r="O25" t="s">
+        <v>690</v>
+      </c>
+      <c r="P25" t="s">
+        <v>689</v>
+      </c>
       <c r="R25" t="s">
         <v>701</v>
       </c>
@@ -3785,6 +3884,12 @@
       <c r="N26" t="s">
         <v>689</v>
       </c>
+      <c r="O26" t="s">
+        <v>690</v>
+      </c>
+      <c r="P26" t="s">
+        <v>689</v>
+      </c>
       <c r="R26" t="s">
         <v>701</v>
       </c>
@@ -3828,6 +3933,12 @@
       <c r="N27" t="s">
         <v>689</v>
       </c>
+      <c r="O27" t="s">
+        <v>690</v>
+      </c>
+      <c r="P27" t="s">
+        <v>689</v>
+      </c>
       <c r="R27" t="s">
         <v>701</v>
       </c>
@@ -3871,6 +3982,12 @@
       <c r="N28" t="s">
         <v>689</v>
       </c>
+      <c r="O28" t="s">
+        <v>690</v>
+      </c>
+      <c r="P28" t="s">
+        <v>689</v>
+      </c>
       <c r="R28" t="s">
         <v>701</v>
       </c>
@@ -3914,6 +4031,12 @@
       <c r="N29" t="s">
         <v>690</v>
       </c>
+      <c r="O29" t="s">
+        <v>689</v>
+      </c>
+      <c r="P29" t="s">
+        <v>689</v>
+      </c>
       <c r="R29" t="s">
         <v>701</v>
       </c>
@@ -3957,6 +4080,12 @@
       <c r="N30" t="s">
         <v>690</v>
       </c>
+      <c r="O30" t="s">
+        <v>689</v>
+      </c>
+      <c r="P30" t="s">
+        <v>689</v>
+      </c>
       <c r="R30" t="s">
         <v>701</v>
       </c>
@@ -4000,6 +4129,12 @@
       <c r="N31" t="s">
         <v>690</v>
       </c>
+      <c r="O31" t="s">
+        <v>689</v>
+      </c>
+      <c r="P31" t="s">
+        <v>691</v>
+      </c>
       <c r="R31" t="s">
         <v>701</v>
       </c>
@@ -4043,6 +4178,12 @@
       <c r="N32" t="s">
         <v>689</v>
       </c>
+      <c r="O32" t="s">
+        <v>690</v>
+      </c>
+      <c r="P32" t="s">
+        <v>689</v>
+      </c>
       <c r="R32" t="s">
         <v>701</v>
       </c>
@@ -4086,6 +4227,12 @@
       <c r="N33" t="s">
         <v>690</v>
       </c>
+      <c r="O33" t="s">
+        <v>690</v>
+      </c>
+      <c r="P33" t="s">
+        <v>690</v>
+      </c>
       <c r="R33" t="s">
         <v>701</v>
       </c>
@@ -4129,6 +4276,12 @@
       <c r="N34" t="s">
         <v>690</v>
       </c>
+      <c r="O34" t="s">
+        <v>689</v>
+      </c>
+      <c r="P34" t="s">
+        <v>689</v>
+      </c>
       <c r="R34" t="s">
         <v>701</v>
       </c>
@@ -4172,6 +4325,12 @@
       <c r="N35" t="s">
         <v>690</v>
       </c>
+      <c r="O35" t="s">
+        <v>690</v>
+      </c>
+      <c r="P35" t="s">
+        <v>692</v>
+      </c>
       <c r="R35" t="s">
         <v>701</v>
       </c>
@@ -4215,6 +4374,12 @@
       <c r="N36" t="s">
         <v>690</v>
       </c>
+      <c r="O36" t="s">
+        <v>690</v>
+      </c>
+      <c r="P36" t="s">
+        <v>689</v>
+      </c>
       <c r="R36" t="s">
         <v>701</v>
       </c>
@@ -4258,6 +4423,12 @@
       <c r="N37" t="s">
         <v>690</v>
       </c>
+      <c r="O37" t="s">
+        <v>690</v>
+      </c>
+      <c r="P37" t="s">
+        <v>689</v>
+      </c>
       <c r="R37" t="s">
         <v>701</v>
       </c>
@@ -4301,6 +4472,12 @@
       <c r="N38" t="s">
         <v>689</v>
       </c>
+      <c r="O38" t="s">
+        <v>690</v>
+      </c>
+      <c r="P38" t="s">
+        <v>689</v>
+      </c>
       <c r="R38" t="s">
         <v>701</v>
       </c>
@@ -4344,6 +4521,12 @@
       <c r="N39" t="s">
         <v>690</v>
       </c>
+      <c r="O39" t="s">
+        <v>690</v>
+      </c>
+      <c r="P39" t="s">
+        <v>689</v>
+      </c>
       <c r="R39" t="s">
         <v>701</v>
       </c>
@@ -4387,6 +4570,12 @@
       <c r="N40" t="s">
         <v>690</v>
       </c>
+      <c r="O40" t="s">
+        <v>690</v>
+      </c>
+      <c r="P40" t="s">
+        <v>692</v>
+      </c>
       <c r="R40" t="s">
         <v>701</v>
       </c>
@@ -4430,6 +4619,12 @@
       <c r="N41" t="s">
         <v>689</v>
       </c>
+      <c r="O41" t="s">
+        <v>690</v>
+      </c>
+      <c r="P41" t="s">
+        <v>689</v>
+      </c>
       <c r="R41" t="s">
         <v>701</v>
       </c>
@@ -4473,6 +4668,12 @@
       <c r="N42" t="s">
         <v>689</v>
       </c>
+      <c r="O42" t="s">
+        <v>690</v>
+      </c>
+      <c r="P42" t="s">
+        <v>691</v>
+      </c>
       <c r="R42" t="s">
         <v>701</v>
       </c>
@@ -4516,6 +4717,12 @@
       <c r="N43" t="s">
         <v>690</v>
       </c>
+      <c r="O43" t="s">
+        <v>690</v>
+      </c>
+      <c r="P43" t="s">
+        <v>692</v>
+      </c>
       <c r="R43" t="s">
         <v>701</v>
       </c>
@@ -4559,6 +4766,12 @@
       <c r="N44" t="s">
         <v>690</v>
       </c>
+      <c r="O44" t="s">
+        <v>690</v>
+      </c>
+      <c r="P44" t="s">
+        <v>692</v>
+      </c>
       <c r="R44" t="s">
         <v>701</v>
       </c>
@@ -4602,6 +4815,12 @@
       <c r="N45" t="s">
         <v>690</v>
       </c>
+      <c r="O45" t="s">
+        <v>690</v>
+      </c>
+      <c r="P45" t="s">
+        <v>691</v>
+      </c>
       <c r="R45" t="s">
         <v>701</v>
       </c>
@@ -4645,6 +4864,12 @@
       <c r="N46" t="s">
         <v>689</v>
       </c>
+      <c r="O46" t="s">
+        <v>690</v>
+      </c>
+      <c r="P46" t="s">
+        <v>691</v>
+      </c>
       <c r="R46" t="s">
         <v>701</v>
       </c>
@@ -4688,6 +4913,12 @@
       <c r="N47" t="s">
         <v>690</v>
       </c>
+      <c r="O47" t="s">
+        <v>690</v>
+      </c>
+      <c r="P47" t="s">
+        <v>692</v>
+      </c>
       <c r="R47" t="s">
         <v>701</v>
       </c>
@@ -4731,6 +4962,12 @@
       <c r="N48" t="s">
         <v>689</v>
       </c>
+      <c r="O48" t="s">
+        <v>690</v>
+      </c>
+      <c r="P48" t="s">
+        <v>691</v>
+      </c>
       <c r="R48" t="s">
         <v>701</v>
       </c>
@@ -4774,6 +5011,12 @@
       <c r="N49" t="s">
         <v>690</v>
       </c>
+      <c r="O49" t="s">
+        <v>689</v>
+      </c>
+      <c r="P49" t="s">
+        <v>691</v>
+      </c>
       <c r="R49" t="s">
         <v>701</v>
       </c>
@@ -4817,6 +5060,12 @@
       <c r="N50" t="s">
         <v>690</v>
       </c>
+      <c r="O50" t="s">
+        <v>690</v>
+      </c>
+      <c r="P50" t="s">
+        <v>689</v>
+      </c>
       <c r="R50" t="s">
         <v>701</v>
       </c>
@@ -4860,6 +5109,12 @@
       <c r="N51" t="s">
         <v>690</v>
       </c>
+      <c r="O51" t="s">
+        <v>690</v>
+      </c>
+      <c r="P51" t="s">
+        <v>692</v>
+      </c>
       <c r="R51" t="s">
         <v>701</v>
       </c>
@@ -4903,6 +5158,12 @@
       <c r="N52" t="s">
         <v>689</v>
       </c>
+      <c r="O52" t="s">
+        <v>690</v>
+      </c>
+      <c r="P52" t="s">
+        <v>689</v>
+      </c>
       <c r="R52" t="s">
         <v>701</v>
       </c>
@@ -4946,6 +5207,12 @@
       <c r="N53" t="s">
         <v>690</v>
       </c>
+      <c r="O53" t="s">
+        <v>690</v>
+      </c>
+      <c r="P53" t="s">
+        <v>692</v>
+      </c>
       <c r="R53" t="s">
         <v>701</v>
       </c>
@@ -4989,6 +5256,12 @@
       <c r="N54" t="s">
         <v>689</v>
       </c>
+      <c r="O54" t="s">
+        <v>690</v>
+      </c>
+      <c r="P54" t="s">
+        <v>689</v>
+      </c>
       <c r="R54" t="s">
         <v>701</v>
       </c>
@@ -5032,6 +5305,12 @@
       <c r="N55" t="s">
         <v>690</v>
       </c>
+      <c r="O55" t="s">
+        <v>689</v>
+      </c>
+      <c r="P55" t="s">
+        <v>692</v>
+      </c>
       <c r="R55" t="s">
         <v>701</v>
       </c>
@@ -5075,6 +5354,12 @@
       <c r="N56" t="s">
         <v>690</v>
       </c>
+      <c r="O56" t="s">
+        <v>690</v>
+      </c>
+      <c r="P56" t="s">
+        <v>692</v>
+      </c>
       <c r="R56" t="s">
         <v>701</v>
       </c>
@@ -5118,6 +5403,12 @@
       <c r="N57" t="s">
         <v>690</v>
       </c>
+      <c r="O57" t="s">
+        <v>690</v>
+      </c>
+      <c r="P57" t="s">
+        <v>692</v>
+      </c>
       <c r="R57" t="s">
         <v>701</v>
       </c>
@@ -5161,6 +5452,12 @@
       <c r="N58" t="s">
         <v>689</v>
       </c>
+      <c r="O58" t="s">
+        <v>689</v>
+      </c>
+      <c r="P58" t="s">
+        <v>689</v>
+      </c>
       <c r="R58" t="s">
         <v>701</v>
       </c>
@@ -5204,6 +5501,12 @@
       <c r="N59" t="s">
         <v>690</v>
       </c>
+      <c r="O59" t="s">
+        <v>691</v>
+      </c>
+      <c r="P59" t="s">
+        <v>692</v>
+      </c>
       <c r="R59" t="s">
         <v>701</v>
       </c>
@@ -5247,6 +5550,12 @@
       <c r="N60" t="s">
         <v>690</v>
       </c>
+      <c r="O60" t="s">
+        <v>690</v>
+      </c>
+      <c r="P60" t="s">
+        <v>692</v>
+      </c>
       <c r="R60" t="s">
         <v>701</v>
       </c>
@@ -5290,6 +5599,12 @@
       <c r="N61" t="s">
         <v>690</v>
       </c>
+      <c r="O61" t="s">
+        <v>689</v>
+      </c>
+      <c r="P61" t="s">
+        <v>692</v>
+      </c>
       <c r="R61" t="s">
         <v>701</v>
       </c>
@@ -5333,6 +5648,12 @@
       <c r="N62" t="s">
         <v>689</v>
       </c>
+      <c r="O62" t="s">
+        <v>690</v>
+      </c>
+      <c r="P62" t="s">
+        <v>689</v>
+      </c>
       <c r="R62" t="s">
         <v>701</v>
       </c>
@@ -5376,6 +5697,12 @@
       <c r="N63" t="s">
         <v>690</v>
       </c>
+      <c r="O63" t="s">
+        <v>690</v>
+      </c>
+      <c r="P63" t="s">
+        <v>692</v>
+      </c>
       <c r="R63" t="s">
         <v>701</v>
       </c>
@@ -5419,6 +5746,12 @@
       <c r="N64" t="s">
         <v>689</v>
       </c>
+      <c r="O64" t="s">
+        <v>690</v>
+      </c>
+      <c r="P64" t="s">
+        <v>689</v>
+      </c>
       <c r="R64" t="s">
         <v>701</v>
       </c>
@@ -5462,6 +5795,12 @@
       <c r="N65" t="s">
         <v>690</v>
       </c>
+      <c r="O65" t="s">
+        <v>691</v>
+      </c>
+      <c r="P65" t="s">
+        <v>692</v>
+      </c>
       <c r="R65" t="s">
         <v>701</v>
       </c>
@@ -5505,6 +5844,12 @@
       <c r="N66" t="s">
         <v>690</v>
       </c>
+      <c r="O66" t="s">
+        <v>689</v>
+      </c>
+      <c r="P66" t="s">
+        <v>692</v>
+      </c>
       <c r="R66" t="s">
         <v>701</v>
       </c>
@@ -5548,6 +5893,12 @@
       <c r="N67" t="s">
         <v>690</v>
       </c>
+      <c r="O67" t="s">
+        <v>690</v>
+      </c>
+      <c r="P67" t="s">
+        <v>691</v>
+      </c>
       <c r="R67" t="s">
         <v>701</v>
       </c>
@@ -5591,6 +5942,12 @@
       <c r="N68" t="s">
         <v>690</v>
       </c>
+      <c r="O68" t="s">
+        <v>690</v>
+      </c>
+      <c r="P68" t="s">
+        <v>692</v>
+      </c>
       <c r="R68" t="s">
         <v>701</v>
       </c>
@@ -5634,6 +5991,12 @@
       <c r="N69" t="s">
         <v>689</v>
       </c>
+      <c r="O69" t="s">
+        <v>690</v>
+      </c>
+      <c r="P69" t="s">
+        <v>689</v>
+      </c>
       <c r="R69" t="s">
         <v>701</v>
       </c>
@@ -5677,6 +6040,12 @@
       <c r="N70" t="s">
         <v>689</v>
       </c>
+      <c r="O70" t="s">
+        <v>690</v>
+      </c>
+      <c r="P70" t="s">
+        <v>691</v>
+      </c>
       <c r="R70" t="s">
         <v>701</v>
       </c>
@@ -5720,6 +6089,12 @@
       <c r="N71" t="s">
         <v>689</v>
       </c>
+      <c r="O71" t="s">
+        <v>690</v>
+      </c>
+      <c r="P71" t="s">
+        <v>689</v>
+      </c>
       <c r="R71" t="s">
         <v>701</v>
       </c>
@@ -5763,6 +6138,12 @@
       <c r="N72" t="s">
         <v>689</v>
       </c>
+      <c r="O72" t="s">
+        <v>690</v>
+      </c>
+      <c r="P72" t="s">
+        <v>689</v>
+      </c>
       <c r="R72" t="s">
         <v>701</v>
       </c>
@@ -5806,6 +6187,12 @@
       <c r="N73" t="s">
         <v>689</v>
       </c>
+      <c r="O73" t="s">
+        <v>690</v>
+      </c>
+      <c r="P73" t="s">
+        <v>689</v>
+      </c>
       <c r="R73" t="s">
         <v>701</v>
       </c>
@@ -5849,6 +6236,12 @@
       <c r="N74" t="s">
         <v>690</v>
       </c>
+      <c r="O74" t="s">
+        <v>690</v>
+      </c>
+      <c r="P74" t="s">
+        <v>692</v>
+      </c>
       <c r="R74" t="s">
         <v>701</v>
       </c>
@@ -5892,6 +6285,12 @@
       <c r="N75" t="s">
         <v>689</v>
       </c>
+      <c r="O75" t="s">
+        <v>690</v>
+      </c>
+      <c r="P75" t="s">
+        <v>689</v>
+      </c>
       <c r="R75" t="s">
         <v>702</v>
       </c>
@@ -5935,6 +6334,12 @@
       <c r="N76" t="s">
         <v>692</v>
       </c>
+      <c r="O76" t="s">
+        <v>690</v>
+      </c>
+      <c r="P76" t="s">
+        <v>690</v>
+      </c>
       <c r="R76" t="s">
         <v>702</v>
       </c>
@@ -5978,6 +6383,12 @@
       <c r="N77" t="s">
         <v>691</v>
       </c>
+      <c r="O77" t="s">
+        <v>690</v>
+      </c>
+      <c r="P77" t="s">
+        <v>689</v>
+      </c>
       <c r="R77" t="s">
         <v>702</v>
       </c>
@@ -6021,6 +6432,12 @@
       <c r="N78" t="s">
         <v>692</v>
       </c>
+      <c r="O78" t="s">
+        <v>690</v>
+      </c>
+      <c r="P78" t="s">
+        <v>690</v>
+      </c>
       <c r="R78" t="s">
         <v>702</v>
       </c>
@@ -6064,6 +6481,12 @@
       <c r="N79" t="s">
         <v>691</v>
       </c>
+      <c r="O79" t="s">
+        <v>690</v>
+      </c>
+      <c r="P79" t="s">
+        <v>689</v>
+      </c>
       <c r="R79" t="s">
         <v>702</v>
       </c>
@@ -6107,6 +6530,12 @@
       <c r="N80" t="s">
         <v>689</v>
       </c>
+      <c r="O80" t="s">
+        <v>689</v>
+      </c>
+      <c r="P80" t="s">
+        <v>689</v>
+      </c>
       <c r="R80" t="s">
         <v>702</v>
       </c>
@@ -6150,6 +6579,12 @@
       <c r="N81" t="s">
         <v>692</v>
       </c>
+      <c r="O81" t="s">
+        <v>690</v>
+      </c>
+      <c r="P81" t="s">
+        <v>690</v>
+      </c>
       <c r="R81" t="s">
         <v>702</v>
       </c>
@@ -6193,6 +6628,12 @@
       <c r="N82" t="s">
         <v>689</v>
       </c>
+      <c r="O82" t="s">
+        <v>690</v>
+      </c>
+      <c r="P82" t="s">
+        <v>691</v>
+      </c>
       <c r="R82" t="s">
         <v>702</v>
       </c>
@@ -6236,6 +6677,12 @@
       <c r="N83" t="s">
         <v>689</v>
       </c>
+      <c r="O83" t="s">
+        <v>689</v>
+      </c>
+      <c r="P83" t="s">
+        <v>689</v>
+      </c>
       <c r="R83" t="s">
         <v>702</v>
       </c>
@@ -6279,6 +6726,12 @@
       <c r="N84" t="s">
         <v>692</v>
       </c>
+      <c r="O84" t="s">
+        <v>690</v>
+      </c>
+      <c r="P84" t="s">
+        <v>690</v>
+      </c>
       <c r="R84" t="s">
         <v>702</v>
       </c>
@@ -6322,6 +6775,12 @@
       <c r="N85" t="s">
         <v>691</v>
       </c>
+      <c r="O85" t="s">
+        <v>689</v>
+      </c>
+      <c r="P85" t="s">
+        <v>690</v>
+      </c>
       <c r="R85" t="s">
         <v>702</v>
       </c>
@@ -6365,6 +6824,12 @@
       <c r="N86" t="s">
         <v>689</v>
       </c>
+      <c r="O86" t="s">
+        <v>689</v>
+      </c>
+      <c r="P86" t="s">
+        <v>689</v>
+      </c>
       <c r="R86" t="s">
         <v>702</v>
       </c>
@@ -6408,6 +6873,12 @@
       <c r="N87" t="s">
         <v>691</v>
       </c>
+      <c r="O87" t="s">
+        <v>690</v>
+      </c>
+      <c r="P87" t="s">
+        <v>689</v>
+      </c>
       <c r="R87" t="s">
         <v>702</v>
       </c>
@@ -6451,6 +6922,12 @@
       <c r="N88" t="s">
         <v>691</v>
       </c>
+      <c r="O88" t="s">
+        <v>689</v>
+      </c>
+      <c r="P88" t="s">
+        <v>690</v>
+      </c>
       <c r="R88" t="s">
         <v>702</v>
       </c>
@@ -6495,6 +6972,12 @@
       <c r="N89" t="s">
         <v>691</v>
       </c>
+      <c r="O89" t="s">
+        <v>689</v>
+      </c>
+      <c r="P89" t="s">
+        <v>690</v>
+      </c>
       <c r="R89" t="s">
         <v>702</v>
       </c>
@@ -6539,6 +7022,12 @@
       <c r="N90" t="s">
         <v>691</v>
       </c>
+      <c r="O90" t="s">
+        <v>689</v>
+      </c>
+      <c r="P90" t="s">
+        <v>690</v>
+      </c>
       <c r="R90" t="s">
         <v>702</v>
       </c>
@@ -6583,6 +7072,12 @@
       <c r="N91" t="s">
         <v>691</v>
       </c>
+      <c r="O91" t="s">
+        <v>689</v>
+      </c>
+      <c r="P91" t="s">
+        <v>689</v>
+      </c>
       <c r="R91" t="s">
         <v>702</v>
       </c>
@@ -6627,6 +7122,12 @@
       <c r="N92" t="s">
         <v>689</v>
       </c>
+      <c r="O92" t="s">
+        <v>691</v>
+      </c>
+      <c r="P92" t="s">
+        <v>690</v>
+      </c>
       <c r="R92" t="s">
         <v>702</v>
       </c>
@@ -6671,6 +7172,12 @@
       <c r="N93" t="s">
         <v>691</v>
       </c>
+      <c r="O93" t="s">
+        <v>689</v>
+      </c>
+      <c r="P93" t="s">
+        <v>690</v>
+      </c>
       <c r="R93" t="s">
         <v>702</v>
       </c>
@@ -6715,6 +7222,12 @@
       <c r="N94" t="s">
         <v>691</v>
       </c>
+      <c r="O94" t="s">
+        <v>689</v>
+      </c>
+      <c r="P94" t="s">
+        <v>690</v>
+      </c>
       <c r="R94" t="s">
         <v>702</v>
       </c>
@@ -6759,6 +7272,12 @@
       <c r="N95" t="s">
         <v>691</v>
       </c>
+      <c r="O95" t="s">
+        <v>689</v>
+      </c>
+      <c r="P95" t="s">
+        <v>689</v>
+      </c>
       <c r="R95" t="s">
         <v>702</v>
       </c>
@@ -6803,6 +7322,12 @@
       <c r="N96" t="s">
         <v>691</v>
       </c>
+      <c r="O96" t="s">
+        <v>689</v>
+      </c>
+      <c r="P96" t="s">
+        <v>690</v>
+      </c>
       <c r="R96" t="s">
         <v>702</v>
       </c>
@@ -6847,6 +7372,12 @@
       <c r="N97" t="s">
         <v>689</v>
       </c>
+      <c r="O97" t="s">
+        <v>689</v>
+      </c>
+      <c r="P97" t="s">
+        <v>691</v>
+      </c>
       <c r="R97" t="s">
         <v>702</v>
       </c>
@@ -6891,6 +7422,12 @@
       <c r="N98" t="s">
         <v>690</v>
       </c>
+      <c r="O98" t="s">
+        <v>691</v>
+      </c>
+      <c r="P98" t="s">
+        <v>691</v>
+      </c>
       <c r="R98" t="s">
         <v>702</v>
       </c>
@@ -6935,6 +7472,12 @@
       <c r="N99" t="s">
         <v>691</v>
       </c>
+      <c r="O99" t="s">
+        <v>689</v>
+      </c>
+      <c r="P99" t="s">
+        <v>689</v>
+      </c>
       <c r="R99" t="s">
         <v>702</v>
       </c>
@@ -6979,6 +7522,12 @@
       <c r="N100" t="s">
         <v>689</v>
       </c>
+      <c r="O100" t="s">
+        <v>689</v>
+      </c>
+      <c r="P100" t="s">
+        <v>689</v>
+      </c>
       <c r="R100" t="s">
         <v>702</v>
       </c>
@@ -7023,6 +7572,12 @@
       <c r="N101" t="s">
         <v>692</v>
       </c>
+      <c r="O101" t="s">
+        <v>690</v>
+      </c>
+      <c r="P101" t="s">
+        <v>690</v>
+      </c>
       <c r="R101" t="s">
         <v>702</v>
       </c>
@@ -7067,6 +7622,12 @@
       <c r="N102" t="s">
         <v>689</v>
       </c>
+      <c r="O102" t="s">
+        <v>689</v>
+      </c>
+      <c r="P102" t="s">
+        <v>689</v>
+      </c>
       <c r="R102" t="s">
         <v>702</v>
       </c>
@@ -7111,6 +7672,12 @@
       <c r="N103" t="s">
         <v>691</v>
       </c>
+      <c r="O103" t="s">
+        <v>689</v>
+      </c>
+      <c r="P103" t="s">
+        <v>690</v>
+      </c>
       <c r="R103" t="s">
         <v>702</v>
       </c>
@@ -7155,6 +7722,12 @@
       <c r="N104" t="s">
         <v>691</v>
       </c>
+      <c r="O104" t="s">
+        <v>689</v>
+      </c>
+      <c r="P104" t="s">
+        <v>690</v>
+      </c>
       <c r="R104" t="s">
         <v>702</v>
       </c>
@@ -7199,6 +7772,12 @@
       <c r="N105" t="s">
         <v>692</v>
       </c>
+      <c r="O105" t="s">
+        <v>690</v>
+      </c>
+      <c r="P105" t="s">
+        <v>690</v>
+      </c>
       <c r="R105" t="s">
         <v>702</v>
       </c>
@@ -7243,6 +7822,12 @@
       <c r="N106" t="s">
         <v>689</v>
       </c>
+      <c r="O106" t="s">
+        <v>690</v>
+      </c>
+      <c r="P106" t="s">
+        <v>689</v>
+      </c>
       <c r="R106" t="s">
         <v>702</v>
       </c>
@@ -7287,6 +7872,12 @@
       <c r="N107" t="s">
         <v>691</v>
       </c>
+      <c r="O107" t="s">
+        <v>690</v>
+      </c>
+      <c r="P107" t="s">
+        <v>689</v>
+      </c>
       <c r="R107" t="s">
         <v>702</v>
       </c>
@@ -7331,6 +7922,12 @@
       <c r="N108" t="s">
         <v>690</v>
       </c>
+      <c r="O108" t="s">
+        <v>691</v>
+      </c>
+      <c r="P108" t="s">
+        <v>689</v>
+      </c>
       <c r="R108" t="s">
         <v>702</v>
       </c>
@@ -7375,6 +7972,12 @@
       <c r="N109" t="s">
         <v>691</v>
       </c>
+      <c r="O109" t="s">
+        <v>689</v>
+      </c>
+      <c r="P109" t="s">
+        <v>689</v>
+      </c>
       <c r="R109" t="s">
         <v>702</v>
       </c>
@@ -7419,6 +8022,12 @@
       <c r="N110" t="s">
         <v>689</v>
       </c>
+      <c r="O110" t="s">
+        <v>689</v>
+      </c>
+      <c r="P110" t="s">
+        <v>691</v>
+      </c>
       <c r="R110" t="s">
         <v>702</v>
       </c>
@@ -7463,6 +8072,12 @@
       <c r="N111" t="s">
         <v>689</v>
       </c>
+      <c r="O111" t="s">
+        <v>689</v>
+      </c>
+      <c r="P111" t="s">
+        <v>689</v>
+      </c>
       <c r="R111" t="s">
         <v>702</v>
       </c>
@@ -7507,6 +8122,12 @@
       <c r="N112" t="s">
         <v>690</v>
       </c>
+      <c r="O112" t="s">
+        <v>692</v>
+      </c>
+      <c r="P112" t="s">
+        <v>691</v>
+      </c>
       <c r="R112" t="s">
         <v>702</v>
       </c>
@@ -7551,6 +8172,12 @@
       <c r="N113" t="s">
         <v>689</v>
       </c>
+      <c r="O113" t="s">
+        <v>690</v>
+      </c>
+      <c r="P113" t="s">
+        <v>689</v>
+      </c>
       <c r="R113" t="s">
         <v>702</v>
       </c>
@@ -7595,6 +8222,12 @@
       <c r="N114" t="s">
         <v>690</v>
       </c>
+      <c r="O114" t="s">
+        <v>690</v>
+      </c>
+      <c r="P114" t="s">
+        <v>692</v>
+      </c>
       <c r="R114" t="s">
         <v>702</v>
       </c>
@@ -7639,6 +8272,12 @@
       <c r="N115" t="s">
         <v>690</v>
       </c>
+      <c r="O115" t="s">
+        <v>690</v>
+      </c>
+      <c r="P115" t="s">
+        <v>692</v>
+      </c>
       <c r="R115" t="s">
         <v>702</v>
       </c>
@@ -7683,6 +8322,12 @@
       <c r="N116" t="s">
         <v>690</v>
       </c>
+      <c r="O116" t="s">
+        <v>689</v>
+      </c>
+      <c r="P116" t="s">
+        <v>692</v>
+      </c>
       <c r="R116" t="s">
         <v>702</v>
       </c>
@@ -7726,6 +8371,12 @@
       <c r="N117" t="s">
         <v>689</v>
       </c>
+      <c r="O117" t="s">
+        <v>691</v>
+      </c>
+      <c r="P117" t="s">
+        <v>690</v>
+      </c>
       <c r="R117" t="s">
         <v>702</v>
       </c>
@@ -7775,6 +8426,12 @@
       <c r="N118" t="s">
         <v>690</v>
       </c>
+      <c r="O118" t="s">
+        <v>692</v>
+      </c>
+      <c r="P118" t="s">
+        <v>690</v>
+      </c>
       <c r="R118" t="s">
         <v>702</v>
       </c>
@@ -7824,6 +8481,12 @@
       <c r="N119" t="s">
         <v>691</v>
       </c>
+      <c r="O119" t="s">
+        <v>691</v>
+      </c>
+      <c r="P119" t="s">
+        <v>690</v>
+      </c>
       <c r="R119" t="s">
         <v>702</v>
       </c>
@@ -7873,6 +8536,12 @@
       <c r="N120" t="s">
         <v>690</v>
       </c>
+      <c r="O120" t="s">
+        <v>692</v>
+      </c>
+      <c r="P120" t="s">
+        <v>689</v>
+      </c>
       <c r="R120" t="s">
         <v>702</v>
       </c>
@@ -7922,6 +8591,12 @@
       <c r="N121" t="s">
         <v>690</v>
       </c>
+      <c r="O121" t="s">
+        <v>692</v>
+      </c>
+      <c r="P121" t="s">
+        <v>690</v>
+      </c>
       <c r="R121" t="s">
         <v>702</v>
       </c>
@@ -7968,6 +8643,12 @@
       <c r="N122" t="s">
         <v>690</v>
       </c>
+      <c r="O122" t="s">
+        <v>692</v>
+      </c>
+      <c r="P122" t="s">
+        <v>690</v>
+      </c>
       <c r="R122" t="s">
         <v>702</v>
       </c>
@@ -8014,6 +8695,12 @@
       <c r="N123" t="s">
         <v>691</v>
       </c>
+      <c r="O123" t="s">
+        <v>690</v>
+      </c>
+      <c r="P123" t="s">
+        <v>690</v>
+      </c>
       <c r="R123" t="s">
         <v>702</v>
       </c>
@@ -8063,6 +8750,12 @@
       <c r="N124" t="s">
         <v>689</v>
       </c>
+      <c r="O124" t="s">
+        <v>691</v>
+      </c>
+      <c r="P124" t="s">
+        <v>690</v>
+      </c>
       <c r="R124" t="s">
         <v>702</v>
       </c>
@@ -8112,6 +8805,12 @@
       <c r="N125" t="s">
         <v>691</v>
       </c>
+      <c r="O125" t="s">
+        <v>689</v>
+      </c>
+      <c r="P125" t="s">
+        <v>690</v>
+      </c>
       <c r="R125" t="s">
         <v>702</v>
       </c>
@@ -8158,6 +8857,12 @@
       <c r="N126" t="s">
         <v>691</v>
       </c>
+      <c r="O126" t="s">
+        <v>689</v>
+      </c>
+      <c r="P126" t="s">
+        <v>690</v>
+      </c>
       <c r="R126" t="s">
         <v>702</v>
       </c>
@@ -8204,6 +8909,12 @@
       <c r="N127" t="s">
         <v>691</v>
       </c>
+      <c r="O127" t="s">
+        <v>689</v>
+      </c>
+      <c r="P127" t="s">
+        <v>690</v>
+      </c>
       <c r="R127" t="s">
         <v>702</v>
       </c>
@@ -8250,6 +8961,12 @@
       <c r="N128" t="s">
         <v>689</v>
       </c>
+      <c r="O128" t="s">
+        <v>691</v>
+      </c>
+      <c r="P128" t="s">
+        <v>690</v>
+      </c>
       <c r="R128" t="s">
         <v>702</v>
       </c>
@@ -8299,6 +9016,12 @@
       <c r="N129" t="s">
         <v>690</v>
       </c>
+      <c r="O129" t="s">
+        <v>692</v>
+      </c>
+      <c r="P129" t="s">
+        <v>690</v>
+      </c>
       <c r="R129" t="s">
         <v>702</v>
       </c>
@@ -8348,6 +9071,12 @@
       <c r="N130" t="s">
         <v>691</v>
       </c>
+      <c r="O130" t="s">
+        <v>689</v>
+      </c>
+      <c r="P130" t="s">
+        <v>690</v>
+      </c>
       <c r="R130" t="s">
         <v>702</v>
       </c>
@@ -8391,6 +9120,12 @@
       <c r="N131" t="s">
         <v>690</v>
       </c>
+      <c r="O131" t="s">
+        <v>690</v>
+      </c>
+      <c r="P131" t="s">
+        <v>690</v>
+      </c>
       <c r="R131" t="s">
         <v>702</v>
       </c>
@@ -8434,6 +9169,12 @@
       <c r="N132" t="s">
         <v>690</v>
       </c>
+      <c r="O132" t="s">
+        <v>690</v>
+      </c>
+      <c r="P132" t="s">
+        <v>690</v>
+      </c>
       <c r="R132" t="s">
         <v>702</v>
       </c>
@@ -8483,6 +9224,12 @@
       <c r="N133" t="s">
         <v>692</v>
       </c>
+      <c r="O133" t="s">
+        <v>690</v>
+      </c>
+      <c r="P133" t="s">
+        <v>690</v>
+      </c>
       <c r="R133" t="s">
         <v>702</v>
       </c>
@@ -8532,6 +9279,12 @@
       <c r="N134" t="s">
         <v>692</v>
       </c>
+      <c r="O134" t="s">
+        <v>690</v>
+      </c>
+      <c r="P134" t="s">
+        <v>690</v>
+      </c>
       <c r="R134" t="s">
         <v>702</v>
       </c>
@@ -8581,6 +9334,12 @@
       <c r="N135" t="s">
         <v>690</v>
       </c>
+      <c r="O135" t="s">
+        <v>692</v>
+      </c>
+      <c r="P135" t="s">
+        <v>690</v>
+      </c>
       <c r="R135" t="s">
         <v>702</v>
       </c>
@@ -8630,6 +9389,12 @@
       <c r="N136" t="s">
         <v>690</v>
       </c>
+      <c r="O136" t="s">
+        <v>692</v>
+      </c>
+      <c r="P136" t="s">
+        <v>690</v>
+      </c>
       <c r="R136" t="s">
         <v>702</v>
       </c>
@@ -8679,6 +9444,12 @@
       <c r="N137" t="s">
         <v>690</v>
       </c>
+      <c r="O137" t="s">
+        <v>690</v>
+      </c>
+      <c r="P137" t="s">
+        <v>691</v>
+      </c>
       <c r="R137" t="s">
         <v>702</v>
       </c>
@@ -8728,6 +9499,12 @@
       <c r="N138" t="s">
         <v>690</v>
       </c>
+      <c r="O138" t="s">
+        <v>690</v>
+      </c>
+      <c r="P138" t="s">
+        <v>692</v>
+      </c>
       <c r="R138" t="s">
         <v>702</v>
       </c>
@@ -8777,6 +9554,12 @@
       <c r="N139" t="s">
         <v>691</v>
       </c>
+      <c r="O139" t="s">
+        <v>690</v>
+      </c>
+      <c r="P139" t="s">
+        <v>690</v>
+      </c>
       <c r="R139" t="s">
         <v>702</v>
       </c>
@@ -8826,6 +9609,12 @@
       <c r="N140" t="s">
         <v>691</v>
       </c>
+      <c r="O140" t="s">
+        <v>690</v>
+      </c>
+      <c r="P140" t="s">
+        <v>690</v>
+      </c>
       <c r="R140" t="s">
         <v>702</v>
       </c>
@@ -8875,6 +9664,12 @@
       <c r="N141" t="s">
         <v>690</v>
       </c>
+      <c r="O141" t="s">
+        <v>691</v>
+      </c>
+      <c r="P141" t="s">
+        <v>690</v>
+      </c>
       <c r="R141" t="s">
         <v>702</v>
       </c>
@@ -8924,6 +9719,12 @@
       <c r="N142" t="s">
         <v>689</v>
       </c>
+      <c r="O142" t="s">
+        <v>690</v>
+      </c>
+      <c r="P142" t="s">
+        <v>689</v>
+      </c>
       <c r="R142" t="s">
         <v>702</v>
       </c>
@@ -8973,6 +9774,12 @@
       <c r="N143" t="s">
         <v>691</v>
       </c>
+      <c r="O143" t="s">
+        <v>690</v>
+      </c>
+      <c r="P143" t="s">
+        <v>690</v>
+      </c>
       <c r="R143" t="s">
         <v>702</v>
       </c>
@@ -9022,6 +9829,12 @@
       <c r="N144" t="s">
         <v>691</v>
       </c>
+      <c r="O144" t="s">
+        <v>690</v>
+      </c>
+      <c r="P144" t="s">
+        <v>689</v>
+      </c>
       <c r="R144" t="s">
         <v>702</v>
       </c>
@@ -9071,6 +9884,12 @@
       <c r="N145" t="s">
         <v>691</v>
       </c>
+      <c r="O145" t="s">
+        <v>690</v>
+      </c>
+      <c r="P145" t="s">
+        <v>689</v>
+      </c>
       <c r="R145" t="s">
         <v>702</v>
       </c>
@@ -9120,6 +9939,12 @@
       <c r="N146" t="s">
         <v>692</v>
       </c>
+      <c r="O146" t="s">
+        <v>690</v>
+      </c>
+      <c r="P146" t="s">
+        <v>690</v>
+      </c>
       <c r="R146" t="s">
         <v>702</v>
       </c>
@@ -9169,6 +9994,12 @@
       <c r="N147" t="s">
         <v>691</v>
       </c>
+      <c r="O147" t="s">
+        <v>689</v>
+      </c>
+      <c r="P147" t="s">
+        <v>690</v>
+      </c>
       <c r="R147" t="s">
         <v>702</v>
       </c>
@@ -9218,6 +10049,12 @@
       <c r="N148" t="s">
         <v>691</v>
       </c>
+      <c r="O148" t="s">
+        <v>689</v>
+      </c>
+      <c r="P148" t="s">
+        <v>689</v>
+      </c>
       <c r="R148" t="s">
         <v>702</v>
       </c>
@@ -9267,6 +10104,12 @@
       <c r="N149" t="s">
         <v>692</v>
       </c>
+      <c r="O149" t="s">
+        <v>690</v>
+      </c>
+      <c r="P149" t="s">
+        <v>690</v>
+      </c>
       <c r="R149" t="s">
         <v>702</v>
       </c>
@@ -9316,6 +10159,12 @@
       <c r="N150" t="s">
         <v>692</v>
       </c>
+      <c r="O150" t="s">
+        <v>690</v>
+      </c>
+      <c r="P150" t="s">
+        <v>690</v>
+      </c>
       <c r="R150" t="s">
         <v>702</v>
       </c>
@@ -9365,6 +10214,12 @@
       <c r="N151" t="s">
         <v>691</v>
       </c>
+      <c r="O151" t="s">
+        <v>689</v>
+      </c>
+      <c r="P151" t="s">
+        <v>690</v>
+      </c>
       <c r="R151" t="s">
         <v>702</v>
       </c>
@@ -9414,6 +10269,12 @@
       <c r="N152" t="s">
         <v>692</v>
       </c>
+      <c r="O152" t="s">
+        <v>689</v>
+      </c>
+      <c r="P152" t="s">
+        <v>690</v>
+      </c>
       <c r="R152" t="s">
         <v>702</v>
       </c>
@@ -9463,6 +10324,12 @@
       <c r="N153" t="s">
         <v>692</v>
       </c>
+      <c r="O153" t="s">
+        <v>690</v>
+      </c>
+      <c r="P153" t="s">
+        <v>690</v>
+      </c>
       <c r="R153" t="s">
         <v>702</v>
       </c>
@@ -9512,6 +10379,12 @@
       <c r="N154" t="s">
         <v>692</v>
       </c>
+      <c r="O154" t="s">
+        <v>690</v>
+      </c>
+      <c r="P154" t="s">
+        <v>690</v>
+      </c>
       <c r="R154" t="s">
         <v>702</v>
       </c>
@@ -9561,6 +10434,12 @@
       <c r="N155" t="s">
         <v>692</v>
       </c>
+      <c r="O155" t="s">
+        <v>690</v>
+      </c>
+      <c r="P155" t="s">
+        <v>690</v>
+      </c>
       <c r="R155" t="s">
         <v>702</v>
       </c>
@@ -9610,6 +10489,12 @@
       <c r="N156" t="s">
         <v>692</v>
       </c>
+      <c r="O156" t="s">
+        <v>690</v>
+      </c>
+      <c r="P156" t="s">
+        <v>690</v>
+      </c>
       <c r="R156" t="s">
         <v>702</v>
       </c>
@@ -9659,6 +10544,12 @@
       <c r="N157" t="s">
         <v>692</v>
       </c>
+      <c r="O157" t="s">
+        <v>690</v>
+      </c>
+      <c r="P157" t="s">
+        <v>690</v>
+      </c>
       <c r="R157" t="s">
         <v>702</v>
       </c>
@@ -9708,6 +10599,12 @@
       <c r="N158" t="s">
         <v>689</v>
       </c>
+      <c r="O158" t="s">
+        <v>691</v>
+      </c>
+      <c r="P158" t="s">
+        <v>690</v>
+      </c>
       <c r="R158" t="s">
         <v>702</v>
       </c>
@@ -9757,6 +10654,12 @@
       <c r="N159" t="s">
         <v>692</v>
       </c>
+      <c r="O159" t="s">
+        <v>690</v>
+      </c>
+      <c r="P159" t="s">
+        <v>690</v>
+      </c>
       <c r="R159" t="s">
         <v>702</v>
       </c>
@@ -9806,6 +10709,12 @@
       <c r="N160" t="s">
         <v>692</v>
       </c>
+      <c r="O160" t="s">
+        <v>690</v>
+      </c>
+      <c r="P160" t="s">
+        <v>690</v>
+      </c>
       <c r="R160" t="s">
         <v>702</v>
       </c>
@@ -9849,6 +10758,12 @@
       <c r="N161" t="s">
         <v>692</v>
       </c>
+      <c r="O161" t="s">
+        <v>690</v>
+      </c>
+      <c r="P161" t="s">
+        <v>690</v>
+      </c>
       <c r="R161" t="s">
         <v>702</v>
       </c>
@@ -9892,6 +10807,12 @@
       <c r="N162" t="s">
         <v>692</v>
       </c>
+      <c r="O162" t="s">
+        <v>690</v>
+      </c>
+      <c r="P162" t="s">
+        <v>690</v>
+      </c>
       <c r="R162" t="s">
         <v>702</v>
       </c>
@@ -9935,6 +10856,12 @@
       <c r="N163" t="s">
         <v>692</v>
       </c>
+      <c r="O163" t="s">
+        <v>690</v>
+      </c>
+      <c r="P163" t="s">
+        <v>690</v>
+      </c>
       <c r="R163" t="s">
         <v>702</v>
       </c>
@@ -9978,6 +10905,12 @@
       <c r="N164" t="s">
         <v>692</v>
       </c>
+      <c r="O164" t="s">
+        <v>690</v>
+      </c>
+      <c r="P164" t="s">
+        <v>690</v>
+      </c>
       <c r="R164" t="s">
         <v>702</v>
       </c>
@@ -10021,6 +10954,12 @@
       <c r="N165" t="s">
         <v>692</v>
       </c>
+      <c r="O165" t="s">
+        <v>690</v>
+      </c>
+      <c r="P165" t="s">
+        <v>690</v>
+      </c>
       <c r="R165" t="s">
         <v>702</v>
       </c>
@@ -10064,6 +11003,12 @@
       <c r="N166" t="s">
         <v>691</v>
       </c>
+      <c r="O166" t="s">
+        <v>690</v>
+      </c>
+      <c r="P166" t="s">
+        <v>690</v>
+      </c>
       <c r="R166" t="s">
         <v>702</v>
       </c>
@@ -10107,6 +11052,12 @@
       <c r="N167" t="s">
         <v>692</v>
       </c>
+      <c r="O167" t="s">
+        <v>690</v>
+      </c>
+      <c r="P167" t="s">
+        <v>690</v>
+      </c>
       <c r="R167" t="s">
         <v>702</v>
       </c>
@@ -10150,6 +11101,12 @@
       <c r="N168" t="s">
         <v>691</v>
       </c>
+      <c r="O168" t="s">
+        <v>690</v>
+      </c>
+      <c r="P168" t="s">
+        <v>690</v>
+      </c>
       <c r="R168" t="s">
         <v>702</v>
       </c>
@@ -10199,6 +11156,12 @@
       <c r="N169" t="s">
         <v>692</v>
       </c>
+      <c r="O169" t="s">
+        <v>690</v>
+      </c>
+      <c r="P169" t="s">
+        <v>690</v>
+      </c>
       <c r="R169" t="s">
         <v>702</v>
       </c>
@@ -10248,6 +11211,12 @@
       <c r="N170" t="s">
         <v>692</v>
       </c>
+      <c r="O170" t="s">
+        <v>690</v>
+      </c>
+      <c r="P170" t="s">
+        <v>690</v>
+      </c>
       <c r="R170" t="s">
         <v>702</v>
       </c>
@@ -10297,6 +11266,12 @@
       <c r="N171" t="s">
         <v>691</v>
       </c>
+      <c r="O171" t="s">
+        <v>689</v>
+      </c>
+      <c r="P171" t="s">
+        <v>690</v>
+      </c>
       <c r="R171" t="s">
         <v>702</v>
       </c>
@@ -10346,6 +11321,12 @@
       <c r="N172" t="s">
         <v>692</v>
       </c>
+      <c r="O172" t="s">
+        <v>690</v>
+      </c>
+      <c r="P172" t="s">
+        <v>690</v>
+      </c>
       <c r="R172" t="s">
         <v>702</v>
       </c>
@@ -10395,6 +11376,12 @@
       <c r="N173" t="s">
         <v>692</v>
       </c>
+      <c r="O173" t="s">
+        <v>690</v>
+      </c>
+      <c r="P173" t="s">
+        <v>690</v>
+      </c>
       <c r="R173" t="s">
         <v>702</v>
       </c>
@@ -10444,6 +11431,12 @@
       <c r="N174" t="s">
         <v>692</v>
       </c>
+      <c r="O174" t="s">
+        <v>690</v>
+      </c>
+      <c r="P174" t="s">
+        <v>690</v>
+      </c>
       <c r="R174" t="s">
         <v>702</v>
       </c>
@@ -10715,6 +11708,12 @@
       <c r="N181" t="s">
         <v>692</v>
       </c>
+      <c r="O181" t="s">
+        <v>690</v>
+      </c>
+      <c r="P181" t="s">
+        <v>690</v>
+      </c>
       <c r="R181" t="s">
         <v>702</v>
       </c>
@@ -10758,6 +11757,12 @@
       <c r="N182" t="s">
         <v>692</v>
       </c>
+      <c r="O182" t="s">
+        <v>690</v>
+      </c>
+      <c r="P182" t="s">
+        <v>690</v>
+      </c>
       <c r="R182" t="s">
         <v>702</v>
       </c>
@@ -10801,6 +11806,12 @@
       <c r="N183" t="s">
         <v>691</v>
       </c>
+      <c r="O183" t="s">
+        <v>689</v>
+      </c>
+      <c r="P183" t="s">
+        <v>690</v>
+      </c>
       <c r="R183" t="s">
         <v>702</v>
       </c>
@@ -10844,6 +11855,12 @@
       <c r="N184" t="s">
         <v>691</v>
       </c>
+      <c r="O184" t="s">
+        <v>689</v>
+      </c>
+      <c r="P184" t="s">
+        <v>690</v>
+      </c>
       <c r="R184" t="s">
         <v>702</v>
       </c>
@@ -10887,6 +11904,12 @@
       <c r="N185" t="s">
         <v>689</v>
       </c>
+      <c r="O185" t="s">
+        <v>689</v>
+      </c>
+      <c r="P185" t="s">
+        <v>690</v>
+      </c>
       <c r="R185" t="s">
         <v>702</v>
       </c>
@@ -10930,6 +11953,12 @@
       <c r="N186" t="s">
         <v>690</v>
       </c>
+      <c r="O186" t="s">
+        <v>692</v>
+      </c>
+      <c r="P186" t="s">
+        <v>689</v>
+      </c>
       <c r="R186" t="s">
         <v>702</v>
       </c>
@@ -10973,6 +12002,12 @@
       <c r="N187" t="s">
         <v>689</v>
       </c>
+      <c r="O187" t="s">
+        <v>691</v>
+      </c>
+      <c r="P187" t="s">
+        <v>690</v>
+      </c>
       <c r="R187" t="s">
         <v>702</v>
       </c>
@@ -11016,6 +12051,12 @@
       <c r="N188" t="s">
         <v>691</v>
       </c>
+      <c r="O188" t="s">
+        <v>689</v>
+      </c>
+      <c r="P188" t="s">
+        <v>690</v>
+      </c>
       <c r="R188" t="s">
         <v>702</v>
       </c>
@@ -11059,6 +12100,12 @@
       <c r="N189" t="s">
         <v>690</v>
       </c>
+      <c r="O189" t="s">
+        <v>692</v>
+      </c>
+      <c r="P189" t="s">
+        <v>690</v>
+      </c>
       <c r="R189" t="s">
         <v>702</v>
       </c>
@@ -11102,6 +12149,12 @@
       <c r="N190" t="s">
         <v>689</v>
       </c>
+      <c r="O190" t="s">
+        <v>689</v>
+      </c>
+      <c r="P190" t="s">
+        <v>689</v>
+      </c>
       <c r="R190" t="s">
         <v>702</v>
       </c>
@@ -11145,6 +12198,12 @@
       <c r="N191" t="s">
         <v>691</v>
       </c>
+      <c r="O191" t="s">
+        <v>690</v>
+      </c>
+      <c r="P191" t="s">
+        <v>689</v>
+      </c>
       <c r="R191" t="s">
         <v>702</v>
       </c>
@@ -11188,6 +12247,12 @@
       <c r="N192" t="s">
         <v>691</v>
       </c>
+      <c r="O192" t="s">
+        <v>690</v>
+      </c>
+      <c r="P192" t="s">
+        <v>690</v>
+      </c>
       <c r="R192" t="s">
         <v>702</v>
       </c>
@@ -11231,6 +12296,12 @@
       <c r="N193" t="s">
         <v>691</v>
       </c>
+      <c r="O193" t="s">
+        <v>690</v>
+      </c>
+      <c r="P193" t="s">
+        <v>689</v>
+      </c>
       <c r="R193" t="s">
         <v>702</v>
       </c>
@@ -11274,6 +12345,12 @@
       <c r="N194" t="s">
         <v>692</v>
       </c>
+      <c r="O194" t="s">
+        <v>690</v>
+      </c>
+      <c r="P194" t="s">
+        <v>690</v>
+      </c>
       <c r="R194" t="s">
         <v>702</v>
       </c>
@@ -11317,6 +12394,12 @@
       <c r="N195" t="s">
         <v>691</v>
       </c>
+      <c r="O195" t="s">
+        <v>690</v>
+      </c>
+      <c r="P195" t="s">
+        <v>690</v>
+      </c>
       <c r="R195" t="s">
         <v>702</v>
       </c>
@@ -11360,6 +12443,12 @@
       <c r="N196" t="s">
         <v>692</v>
       </c>
+      <c r="O196" t="s">
+        <v>690</v>
+      </c>
+      <c r="P196" t="s">
+        <v>690</v>
+      </c>
       <c r="R196" t="s">
         <v>702</v>
       </c>
@@ -11403,6 +12492,12 @@
       <c r="N197" t="s">
         <v>690</v>
       </c>
+      <c r="O197" t="s">
+        <v>689</v>
+      </c>
+      <c r="P197" t="s">
+        <v>689</v>
+      </c>
       <c r="R197" t="s">
         <v>702</v>
       </c>
@@ -11446,6 +12541,12 @@
       <c r="N198" t="s">
         <v>691</v>
       </c>
+      <c r="O198" t="s">
+        <v>689</v>
+      </c>
+      <c r="P198" t="s">
+        <v>690</v>
+      </c>
       <c r="R198" t="s">
         <v>702</v>
       </c>
@@ -11489,6 +12590,12 @@
       <c r="N199" t="s">
         <v>692</v>
       </c>
+      <c r="O199" t="s">
+        <v>690</v>
+      </c>
+      <c r="P199" t="s">
+        <v>690</v>
+      </c>
       <c r="R199" t="s">
         <v>702</v>
       </c>
@@ -11532,6 +12639,12 @@
       <c r="N200" t="s">
         <v>692</v>
       </c>
+      <c r="O200" t="s">
+        <v>690</v>
+      </c>
+      <c r="P200" t="s">
+        <v>690</v>
+      </c>
       <c r="R200" t="s">
         <v>702</v>
       </c>
@@ -11575,6 +12688,12 @@
       <c r="N201" t="s">
         <v>692</v>
       </c>
+      <c r="O201" t="s">
+        <v>690</v>
+      </c>
+      <c r="P201" t="s">
+        <v>690</v>
+      </c>
       <c r="R201" t="s">
         <v>702</v>
       </c>
@@ -11618,6 +12737,12 @@
       <c r="N202" t="s">
         <v>691</v>
       </c>
+      <c r="O202" t="s">
+        <v>689</v>
+      </c>
+      <c r="P202" t="s">
+        <v>690</v>
+      </c>
       <c r="R202" t="s">
         <v>702</v>
       </c>
@@ -11661,6 +12786,12 @@
       <c r="N203" t="s">
         <v>692</v>
       </c>
+      <c r="O203" t="s">
+        <v>690</v>
+      </c>
+      <c r="P203" t="s">
+        <v>690</v>
+      </c>
       <c r="R203" t="s">
         <v>702</v>
       </c>
@@ -11704,6 +12835,12 @@
       <c r="N204" t="s">
         <v>692</v>
       </c>
+      <c r="O204" t="s">
+        <v>690</v>
+      </c>
+      <c r="P204" t="s">
+        <v>690</v>
+      </c>
       <c r="R204" t="s">
         <v>702</v>
       </c>
@@ -11747,6 +12884,12 @@
       <c r="N205" t="s">
         <v>691</v>
       </c>
+      <c r="O205" t="s">
+        <v>689</v>
+      </c>
+      <c r="P205" t="s">
+        <v>690</v>
+      </c>
       <c r="R205" t="s">
         <v>702</v>
       </c>
@@ -11790,6 +12933,12 @@
       <c r="N206" t="s">
         <v>692</v>
       </c>
+      <c r="O206" t="s">
+        <v>690</v>
+      </c>
+      <c r="P206" t="s">
+        <v>690</v>
+      </c>
       <c r="R206" t="s">
         <v>702</v>
       </c>
@@ -11833,6 +12982,12 @@
       <c r="N207" t="s">
         <v>692</v>
       </c>
+      <c r="O207" t="s">
+        <v>689</v>
+      </c>
+      <c r="P207" t="s">
+        <v>690</v>
+      </c>
       <c r="R207" t="s">
         <v>702</v>
       </c>
@@ -11876,6 +13031,12 @@
       <c r="N208" t="s">
         <v>692</v>
       </c>
+      <c r="O208" t="s">
+        <v>690</v>
+      </c>
+      <c r="P208" t="s">
+        <v>690</v>
+      </c>
       <c r="R208" t="s">
         <v>702</v>
       </c>
@@ -11919,6 +13080,12 @@
       <c r="N209" t="s">
         <v>691</v>
       </c>
+      <c r="O209" t="s">
+        <v>689</v>
+      </c>
+      <c r="P209" t="s">
+        <v>690</v>
+      </c>
       <c r="R209" t="s">
         <v>702</v>
       </c>
@@ -11962,6 +13129,12 @@
       <c r="N210" t="s">
         <v>691</v>
       </c>
+      <c r="O210" t="s">
+        <v>689</v>
+      </c>
+      <c r="P210" t="s">
+        <v>690</v>
+      </c>
       <c r="R210" t="s">
         <v>702</v>
       </c>
@@ -12005,6 +13178,12 @@
       <c r="N211" t="s">
         <v>689</v>
       </c>
+      <c r="O211" t="s">
+        <v>692</v>
+      </c>
+      <c r="P211" t="s">
+        <v>690</v>
+      </c>
       <c r="R211" t="s">
         <v>702</v>
       </c>
@@ -12048,6 +13227,12 @@
       <c r="N212" t="s">
         <v>690</v>
       </c>
+      <c r="O212" t="s">
+        <v>692</v>
+      </c>
+      <c r="P212" t="s">
+        <v>690</v>
+      </c>
       <c r="R212" t="s">
         <v>702</v>
       </c>
@@ -12091,6 +13276,12 @@
       <c r="N213" t="s">
         <v>692</v>
       </c>
+      <c r="O213" t="s">
+        <v>690</v>
+      </c>
+      <c r="P213" t="s">
+        <v>690</v>
+      </c>
       <c r="R213" t="s">
         <v>702</v>
       </c>
@@ -12134,6 +13325,12 @@
       <c r="N214" t="s">
         <v>692</v>
       </c>
+      <c r="O214" t="s">
+        <v>690</v>
+      </c>
+      <c r="P214" t="s">
+        <v>690</v>
+      </c>
       <c r="R214" t="s">
         <v>702</v>
       </c>
@@ -12177,6 +13374,12 @@
       <c r="N215" t="s">
         <v>691</v>
       </c>
+      <c r="O215" t="s">
+        <v>690</v>
+      </c>
+      <c r="P215" t="s">
+        <v>690</v>
+      </c>
       <c r="R215" t="s">
         <v>702</v>
       </c>
@@ -12220,6 +13423,12 @@
       <c r="N216" t="s">
         <v>691</v>
       </c>
+      <c r="O216" t="s">
+        <v>689</v>
+      </c>
+      <c r="P216" t="s">
+        <v>690</v>
+      </c>
       <c r="R216" t="s">
         <v>702</v>
       </c>
@@ -12263,6 +13472,12 @@
       <c r="N217" t="s">
         <v>691</v>
       </c>
+      <c r="O217" t="s">
+        <v>689</v>
+      </c>
+      <c r="P217" t="s">
+        <v>690</v>
+      </c>
       <c r="R217" t="s">
         <v>702</v>
       </c>
@@ -12306,6 +13521,12 @@
       <c r="N218" t="s">
         <v>692</v>
       </c>
+      <c r="O218" t="s">
+        <v>690</v>
+      </c>
+      <c r="P218" t="s">
+        <v>690</v>
+      </c>
       <c r="R218" t="s">
         <v>702</v>
       </c>
@@ -12349,6 +13570,12 @@
       <c r="N219" t="s">
         <v>692</v>
       </c>
+      <c r="O219" t="s">
+        <v>690</v>
+      </c>
+      <c r="P219" t="s">
+        <v>690</v>
+      </c>
       <c r="R219" t="s">
         <v>702</v>
       </c>
@@ -12392,6 +13619,12 @@
       <c r="N220" t="s">
         <v>692</v>
       </c>
+      <c r="O220" t="s">
+        <v>690</v>
+      </c>
+      <c r="P220" t="s">
+        <v>690</v>
+      </c>
       <c r="R220" t="s">
         <v>702</v>
       </c>
@@ -12441,6 +13674,12 @@
       <c r="N221" t="s">
         <v>691</v>
       </c>
+      <c r="O221" t="s">
+        <v>691</v>
+      </c>
+      <c r="P221" t="s">
+        <v>690</v>
+      </c>
       <c r="R221" t="s">
         <v>702</v>
       </c>
@@ -12490,6 +13729,12 @@
       <c r="N222" t="s">
         <v>690</v>
       </c>
+      <c r="O222" t="s">
+        <v>692</v>
+      </c>
+      <c r="P222" t="s">
+        <v>690</v>
+      </c>
       <c r="R222" t="s">
         <v>702</v>
       </c>
@@ -12539,6 +13784,12 @@
       <c r="N223" t="s">
         <v>691</v>
       </c>
+      <c r="O223" t="s">
+        <v>691</v>
+      </c>
+      <c r="P223" t="s">
+        <v>690</v>
+      </c>
       <c r="R223" t="s">
         <v>702</v>
       </c>
@@ -12588,6 +13839,12 @@
       <c r="N224" t="s">
         <v>691</v>
       </c>
+      <c r="O224" t="s">
+        <v>691</v>
+      </c>
+      <c r="P224" t="s">
+        <v>690</v>
+      </c>
       <c r="R224" t="s">
         <v>702</v>
       </c>
@@ -12631,6 +13888,12 @@
       <c r="N225" t="s">
         <v>690</v>
       </c>
+      <c r="O225" t="s">
+        <v>691</v>
+      </c>
+      <c r="P225" t="s">
+        <v>690</v>
+      </c>
       <c r="R225" t="s">
         <v>702</v>
       </c>
@@ -12674,6 +13937,12 @@
       <c r="N226" t="s">
         <v>692</v>
       </c>
+      <c r="O226" t="s">
+        <v>690</v>
+      </c>
+      <c r="P226" t="s">
+        <v>690</v>
+      </c>
       <c r="R226" t="s">
         <v>702</v>
       </c>
@@ -12717,6 +13986,12 @@
       <c r="N227" t="s">
         <v>692</v>
       </c>
+      <c r="O227" t="s">
+        <v>690</v>
+      </c>
+      <c r="P227" t="s">
+        <v>690</v>
+      </c>
       <c r="R227" t="s">
         <v>702</v>
       </c>
@@ -12760,6 +14035,12 @@
       <c r="N228" t="s">
         <v>692</v>
       </c>
+      <c r="O228" t="s">
+        <v>690</v>
+      </c>
+      <c r="P228" t="s">
+        <v>690</v>
+      </c>
       <c r="R228" t="s">
         <v>702</v>
       </c>
@@ -12803,6 +14084,12 @@
       <c r="N229" t="s">
         <v>691</v>
       </c>
+      <c r="O229" t="s">
+        <v>689</v>
+      </c>
+      <c r="P229" t="s">
+        <v>690</v>
+      </c>
       <c r="R229" t="s">
         <v>702</v>
       </c>
@@ -12846,6 +14133,12 @@
       <c r="N230" t="s">
         <v>692</v>
       </c>
+      <c r="O230" t="s">
+        <v>690</v>
+      </c>
+      <c r="P230" t="s">
+        <v>690</v>
+      </c>
       <c r="R230" t="s">
         <v>702</v>
       </c>
@@ -12889,6 +14182,12 @@
       <c r="N231" t="s">
         <v>692</v>
       </c>
+      <c r="O231" t="s">
+        <v>690</v>
+      </c>
+      <c r="P231" t="s">
+        <v>690</v>
+      </c>
       <c r="R231" t="s">
         <v>702</v>
       </c>
@@ -12932,6 +14231,12 @@
       <c r="N232" t="s">
         <v>692</v>
       </c>
+      <c r="O232" t="s">
+        <v>690</v>
+      </c>
+      <c r="P232" t="s">
+        <v>690</v>
+      </c>
       <c r="R232" t="s">
         <v>702</v>
       </c>
@@ -12975,6 +14280,12 @@
       <c r="N233" t="s">
         <v>692</v>
       </c>
+      <c r="O233" t="s">
+        <v>690</v>
+      </c>
+      <c r="P233" t="s">
+        <v>690</v>
+      </c>
       <c r="R233" t="s">
         <v>702</v>
       </c>
@@ -13018,6 +14329,12 @@
       <c r="N234" t="s">
         <v>692</v>
       </c>
+      <c r="O234" t="s">
+        <v>690</v>
+      </c>
+      <c r="P234" t="s">
+        <v>690</v>
+      </c>
       <c r="R234" t="s">
         <v>702</v>
       </c>
@@ -13067,6 +14384,12 @@
       <c r="N235" t="s">
         <v>692</v>
       </c>
+      <c r="O235" t="s">
+        <v>690</v>
+      </c>
+      <c r="P235" t="s">
+        <v>690</v>
+      </c>
       <c r="R235" t="s">
         <v>702</v>
       </c>
@@ -13116,6 +14439,12 @@
       <c r="N236" t="s">
         <v>691</v>
       </c>
+      <c r="O236" t="s">
+        <v>689</v>
+      </c>
+      <c r="P236" t="s">
+        <v>690</v>
+      </c>
       <c r="R236" t="s">
         <v>702</v>
       </c>
@@ -13165,6 +14494,12 @@
       <c r="N237" t="s">
         <v>692</v>
       </c>
+      <c r="O237" t="s">
+        <v>690</v>
+      </c>
+      <c r="P237" t="s">
+        <v>690</v>
+      </c>
       <c r="R237" t="s">
         <v>702</v>
       </c>
@@ -13208,6 +14543,12 @@
       <c r="N238" t="s">
         <v>690</v>
       </c>
+      <c r="O238" t="s">
+        <v>689</v>
+      </c>
+      <c r="P238" t="s">
+        <v>691</v>
+      </c>
       <c r="R238" t="s">
         <v>702</v>
       </c>
@@ -13251,6 +14592,12 @@
       <c r="N239" t="s">
         <v>691</v>
       </c>
+      <c r="O239" t="s">
+        <v>689</v>
+      </c>
+      <c r="P239" t="s">
+        <v>689</v>
+      </c>
       <c r="R239" t="s">
         <v>702</v>
       </c>
@@ -13294,6 +14641,12 @@
       <c r="N240" t="s">
         <v>689</v>
       </c>
+      <c r="O240" t="s">
+        <v>689</v>
+      </c>
+      <c r="P240" t="s">
+        <v>689</v>
+      </c>
       <c r="R240" t="s">
         <v>702</v>
       </c>
@@ -13337,6 +14690,12 @@
       <c r="N241" t="s">
         <v>690</v>
       </c>
+      <c r="O241" t="s">
+        <v>689</v>
+      </c>
+      <c r="P241" t="s">
+        <v>691</v>
+      </c>
       <c r="R241" t="s">
         <v>702</v>
       </c>
@@ -13380,6 +14739,12 @@
       <c r="N242" t="s">
         <v>692</v>
       </c>
+      <c r="O242" t="s">
+        <v>690</v>
+      </c>
+      <c r="P242" t="s">
+        <v>690</v>
+      </c>
       <c r="R242" t="s">
         <v>702</v>
       </c>
@@ -13423,6 +14788,12 @@
       <c r="N243" t="s">
         <v>692</v>
       </c>
+      <c r="O243" t="s">
+        <v>690</v>
+      </c>
+      <c r="P243" t="s">
+        <v>690</v>
+      </c>
       <c r="R243" t="s">
         <v>702</v>
       </c>
@@ -13466,6 +14837,12 @@
       <c r="N244" t="s">
         <v>691</v>
       </c>
+      <c r="O244" t="s">
+        <v>689</v>
+      </c>
+      <c r="P244" t="s">
+        <v>690</v>
+      </c>
       <c r="R244" t="s">
         <v>702</v>
       </c>
@@ -13509,6 +14886,12 @@
       <c r="N245" t="s">
         <v>691</v>
       </c>
+      <c r="O245" t="s">
+        <v>689</v>
+      </c>
+      <c r="P245" t="s">
+        <v>690</v>
+      </c>
       <c r="R245" t="s">
         <v>702</v>
       </c>
@@ -13552,6 +14935,12 @@
       <c r="N246" t="s">
         <v>691</v>
       </c>
+      <c r="O246" t="s">
+        <v>689</v>
+      </c>
+      <c r="P246" t="s">
+        <v>690</v>
+      </c>
       <c r="R246" t="s">
         <v>702</v>
       </c>
@@ -13595,6 +14984,12 @@
       <c r="N247" t="s">
         <v>692</v>
       </c>
+      <c r="O247" t="s">
+        <v>690</v>
+      </c>
+      <c r="P247" t="s">
+        <v>690</v>
+      </c>
       <c r="R247" t="s">
         <v>702</v>
       </c>
@@ -13638,6 +15033,12 @@
       <c r="N248" t="s">
         <v>691</v>
       </c>
+      <c r="O248" t="s">
+        <v>690</v>
+      </c>
+      <c r="P248" t="s">
+        <v>690</v>
+      </c>
       <c r="R248" t="s">
         <v>702</v>
       </c>
@@ -13681,6 +15082,12 @@
       <c r="N249" t="s">
         <v>690</v>
       </c>
+      <c r="O249" t="s">
+        <v>689</v>
+      </c>
+      <c r="P249" t="s">
+        <v>689</v>
+      </c>
       <c r="R249" t="s">
         <v>702</v>
       </c>
@@ -13724,6 +15131,12 @@
       <c r="N250" t="s">
         <v>691</v>
       </c>
+      <c r="O250" t="s">
+        <v>690</v>
+      </c>
+      <c r="P250" t="s">
+        <v>690</v>
+      </c>
       <c r="R250" t="s">
         <v>702</v>
       </c>
@@ -13767,6 +15180,12 @@
       <c r="N251" t="s">
         <v>690</v>
       </c>
+      <c r="O251" t="s">
+        <v>689</v>
+      </c>
+      <c r="P251" t="s">
+        <v>691</v>
+      </c>
       <c r="R251" t="s">
         <v>702</v>
       </c>
@@ -13810,6 +15229,12 @@
       <c r="N252" t="s">
         <v>690</v>
       </c>
+      <c r="O252" t="s">
+        <v>689</v>
+      </c>
+      <c r="P252" t="s">
+        <v>691</v>
+      </c>
       <c r="R252" t="s">
         <v>702</v>
       </c>
@@ -13853,6 +15278,12 @@
       <c r="N253" t="s">
         <v>690</v>
       </c>
+      <c r="O253" t="s">
+        <v>692</v>
+      </c>
+      <c r="P253" t="s">
+        <v>689</v>
+      </c>
       <c r="R253" t="s">
         <v>702</v>
       </c>
@@ -13896,6 +15327,12 @@
       <c r="N254" t="s">
         <v>691</v>
       </c>
+      <c r="O254" t="s">
+        <v>690</v>
+      </c>
+      <c r="P254" t="s">
+        <v>689</v>
+      </c>
       <c r="R254" t="s">
         <v>702</v>
       </c>
@@ -13939,6 +15376,12 @@
       <c r="N255" t="s">
         <v>690</v>
       </c>
+      <c r="O255" t="s">
+        <v>689</v>
+      </c>
+      <c r="P255" t="s">
+        <v>689</v>
+      </c>
       <c r="R255" t="s">
         <v>702</v>
       </c>
@@ -13982,6 +15425,12 @@
       <c r="N256" t="s">
         <v>689</v>
       </c>
+      <c r="O256" t="s">
+        <v>690</v>
+      </c>
+      <c r="P256" t="s">
+        <v>691</v>
+      </c>
       <c r="R256" t="s">
         <v>702</v>
       </c>
@@ -14025,6 +15474,12 @@
       <c r="N257" t="s">
         <v>690</v>
       </c>
+      <c r="O257" t="s">
+        <v>690</v>
+      </c>
+      <c r="P257" t="s">
+        <v>692</v>
+      </c>
       <c r="R257" t="s">
         <v>702</v>
       </c>
@@ -14068,6 +15523,12 @@
       <c r="N258" t="s">
         <v>690</v>
       </c>
+      <c r="O258" t="s">
+        <v>690</v>
+      </c>
+      <c r="P258" t="s">
+        <v>691</v>
+      </c>
       <c r="R258" t="s">
         <v>702</v>
       </c>
@@ -14111,6 +15572,12 @@
       <c r="N259" t="s">
         <v>691</v>
       </c>
+      <c r="O259" t="s">
+        <v>690</v>
+      </c>
+      <c r="P259" t="s">
+        <v>690</v>
+      </c>
       <c r="R259" t="s">
         <v>702</v>
       </c>
@@ -14154,6 +15621,12 @@
       <c r="N260" t="s">
         <v>689</v>
       </c>
+      <c r="O260" t="s">
+        <v>689</v>
+      </c>
+      <c r="P260" t="s">
+        <v>689</v>
+      </c>
       <c r="R260" t="s">
         <v>702</v>
       </c>
@@ -14197,6 +15670,12 @@
       <c r="N261" t="s">
         <v>689</v>
       </c>
+      <c r="O261" t="s">
+        <v>690</v>
+      </c>
+      <c r="P261" t="s">
+        <v>690</v>
+      </c>
       <c r="R261" t="s">
         <v>702</v>
       </c>
@@ -14240,6 +15719,12 @@
       <c r="N262" t="s">
         <v>689</v>
       </c>
+      <c r="O262" t="s">
+        <v>689</v>
+      </c>
+      <c r="P262" t="s">
+        <v>689</v>
+      </c>
       <c r="R262" t="s">
         <v>702</v>
       </c>
@@ -14283,6 +15768,12 @@
       <c r="N263" t="s">
         <v>690</v>
       </c>
+      <c r="O263" t="s">
+        <v>692</v>
+      </c>
+      <c r="P263" t="s">
+        <v>689</v>
+      </c>
       <c r="R263" t="s">
         <v>702</v>
       </c>
@@ -14326,6 +15817,12 @@
       <c r="N264" t="s">
         <v>690</v>
       </c>
+      <c r="O264" t="s">
+        <v>690</v>
+      </c>
+      <c r="P264" t="s">
+        <v>689</v>
+      </c>
       <c r="R264" t="s">
         <v>702</v>
       </c>
@@ -14369,6 +15866,12 @@
       <c r="N265" t="s">
         <v>690</v>
       </c>
+      <c r="O265" t="s">
+        <v>689</v>
+      </c>
+      <c r="P265" t="s">
+        <v>691</v>
+      </c>
       <c r="R265" t="s">
         <v>702</v>
       </c>
@@ -14412,6 +15915,12 @@
       <c r="N266" t="s">
         <v>690</v>
       </c>
+      <c r="O266" t="s">
+        <v>692</v>
+      </c>
+      <c r="P266" t="s">
+        <v>689</v>
+      </c>
       <c r="R266" t="s">
         <v>702</v>
       </c>
@@ -14455,6 +15964,12 @@
       <c r="N267" t="s">
         <v>690</v>
       </c>
+      <c r="O267" t="s">
+        <v>692</v>
+      </c>
+      <c r="P267" t="s">
+        <v>690</v>
+      </c>
       <c r="R267" t="s">
         <v>702</v>
       </c>
@@ -14498,6 +16013,12 @@
       <c r="N268" t="s">
         <v>689</v>
       </c>
+      <c r="O268" t="s">
+        <v>690</v>
+      </c>
+      <c r="P268" t="s">
+        <v>689</v>
+      </c>
       <c r="R268" t="s">
         <v>702</v>
       </c>
@@ -14541,6 +16062,12 @@
       <c r="N269" t="s">
         <v>689</v>
       </c>
+      <c r="O269" t="s">
+        <v>690</v>
+      </c>
+      <c r="P269" t="s">
+        <v>689</v>
+      </c>
       <c r="R269" t="s">
         <v>702</v>
       </c>
@@ -14584,6 +16111,12 @@
       <c r="N270" t="s">
         <v>691</v>
       </c>
+      <c r="O270" t="s">
+        <v>690</v>
+      </c>
+      <c r="P270" t="s">
+        <v>690</v>
+      </c>
       <c r="R270" t="s">
         <v>702</v>
       </c>
@@ -14627,6 +16160,12 @@
       <c r="N271" t="s">
         <v>690</v>
       </c>
+      <c r="O271" t="s">
+        <v>691</v>
+      </c>
+      <c r="P271" t="s">
+        <v>692</v>
+      </c>
       <c r="R271" t="s">
         <v>702</v>
       </c>
@@ -14670,6 +16209,12 @@
       <c r="N272" t="s">
         <v>690</v>
       </c>
+      <c r="O272" t="s">
+        <v>689</v>
+      </c>
+      <c r="P272" t="s">
+        <v>692</v>
+      </c>
       <c r="R272" t="s">
         <v>702</v>
       </c>
@@ -14713,6 +16258,12 @@
       <c r="N273" t="s">
         <v>690</v>
       </c>
+      <c r="O273" t="s">
+        <v>691</v>
+      </c>
+      <c r="P273" t="s">
+        <v>692</v>
+      </c>
       <c r="R273" t="s">
         <v>702</v>
       </c>
@@ -14756,6 +16307,12 @@
       <c r="N274" t="s">
         <v>690</v>
       </c>
+      <c r="O274" t="s">
+        <v>691</v>
+      </c>
+      <c r="P274" t="s">
+        <v>689</v>
+      </c>
       <c r="R274" t="s">
         <v>702</v>
       </c>
@@ -14799,6 +16356,12 @@
       <c r="N275" t="s">
         <v>691</v>
       </c>
+      <c r="O275" t="s">
+        <v>690</v>
+      </c>
+      <c r="P275" t="s">
+        <v>689</v>
+      </c>
       <c r="R275" t="s">
         <v>702</v>
       </c>
@@ -14842,6 +16405,12 @@
       <c r="N276" t="s">
         <v>691</v>
       </c>
+      <c r="O276" t="s">
+        <v>690</v>
+      </c>
+      <c r="P276" t="s">
+        <v>689</v>
+      </c>
       <c r="R276" t="s">
         <v>702</v>
       </c>
@@ -14885,6 +16454,12 @@
       <c r="N277" t="s">
         <v>692</v>
       </c>
+      <c r="O277" t="s">
+        <v>690</v>
+      </c>
+      <c r="P277" t="s">
+        <v>690</v>
+      </c>
       <c r="R277" t="s">
         <v>702</v>
       </c>
@@ -14929,6 +16504,12 @@
       <c r="N278" t="s">
         <v>691</v>
       </c>
+      <c r="O278" t="s">
+        <v>689</v>
+      </c>
+      <c r="P278" t="s">
+        <v>690</v>
+      </c>
       <c r="R278" t="s">
         <v>702</v>
       </c>
@@ -14972,6 +16553,12 @@
       <c r="N279" t="s">
         <v>692</v>
       </c>
+      <c r="O279" t="s">
+        <v>690</v>
+      </c>
+      <c r="P279" t="s">
+        <v>690</v>
+      </c>
       <c r="R279" t="s">
         <v>702</v>
       </c>
@@ -15015,6 +16602,12 @@
       <c r="N280" t="s">
         <v>692</v>
       </c>
+      <c r="O280" t="s">
+        <v>690</v>
+      </c>
+      <c r="P280" t="s">
+        <v>690</v>
+      </c>
       <c r="R280" t="s">
         <v>702</v>
       </c>
@@ -15058,6 +16651,12 @@
       <c r="N281" t="s">
         <v>692</v>
       </c>
+      <c r="O281" t="s">
+        <v>690</v>
+      </c>
+      <c r="P281" t="s">
+        <v>690</v>
+      </c>
       <c r="R281" t="s">
         <v>702</v>
       </c>
@@ -15101,6 +16700,12 @@
       <c r="N282" t="s">
         <v>692</v>
       </c>
+      <c r="O282" t="s">
+        <v>690</v>
+      </c>
+      <c r="P282" t="s">
+        <v>690</v>
+      </c>
       <c r="R282" t="s">
         <v>702</v>
       </c>
@@ -15144,6 +16749,12 @@
       <c r="N283" t="s">
         <v>691</v>
       </c>
+      <c r="O283" t="s">
+        <v>689</v>
+      </c>
+      <c r="P283" t="s">
+        <v>690</v>
+      </c>
       <c r="R283" t="s">
         <v>702</v>
       </c>
@@ -15187,6 +16798,12 @@
       <c r="N284" t="s">
         <v>691</v>
       </c>
+      <c r="O284" t="s">
+        <v>689</v>
+      </c>
+      <c r="P284" t="s">
+        <v>690</v>
+      </c>
       <c r="R284" t="s">
         <v>702</v>
       </c>
@@ -15236,6 +16853,12 @@
       <c r="N285" t="s">
         <v>689</v>
       </c>
+      <c r="O285" t="s">
+        <v>691</v>
+      </c>
+      <c r="P285" t="s">
+        <v>690</v>
+      </c>
       <c r="R285" t="s">
         <v>702</v>
       </c>
@@ -15285,6 +16908,12 @@
       <c r="N286" t="s">
         <v>689</v>
       </c>
+      <c r="O286" t="s">
+        <v>689</v>
+      </c>
+      <c r="P286" t="s">
+        <v>690</v>
+      </c>
       <c r="R286" t="s">
         <v>702</v>
       </c>
@@ -15334,6 +16963,12 @@
       <c r="N287" t="s">
         <v>689</v>
       </c>
+      <c r="O287" t="s">
+        <v>691</v>
+      </c>
+      <c r="P287" t="s">
+        <v>690</v>
+      </c>
       <c r="R287" t="s">
         <v>702</v>
       </c>
@@ -15383,6 +17018,12 @@
       <c r="N288" t="s">
         <v>689</v>
       </c>
+      <c r="O288" t="s">
+        <v>689</v>
+      </c>
+      <c r="P288" t="s">
+        <v>690</v>
+      </c>
       <c r="R288" t="s">
         <v>702</v>
       </c>
@@ -15432,6 +17073,12 @@
       <c r="N289" t="s">
         <v>691</v>
       </c>
+      <c r="O289" t="s">
+        <v>689</v>
+      </c>
+      <c r="P289" t="s">
+        <v>690</v>
+      </c>
       <c r="R289" t="s">
         <v>702</v>
       </c>
@@ -15481,6 +17128,12 @@
       <c r="N290" t="s">
         <v>691</v>
       </c>
+      <c r="O290" t="s">
+        <v>689</v>
+      </c>
+      <c r="P290" t="s">
+        <v>690</v>
+      </c>
       <c r="R290" t="s">
         <v>702</v>
       </c>
@@ -15530,6 +17183,12 @@
       <c r="N291" t="s">
         <v>691</v>
       </c>
+      <c r="O291" t="s">
+        <v>689</v>
+      </c>
+      <c r="P291" t="s">
+        <v>690</v>
+      </c>
       <c r="R291" t="s">
         <v>702</v>
       </c>
@@ -15579,6 +17238,12 @@
       <c r="N292" t="s">
         <v>691</v>
       </c>
+      <c r="O292" t="s">
+        <v>689</v>
+      </c>
+      <c r="P292" t="s">
+        <v>690</v>
+      </c>
       <c r="R292" t="s">
         <v>702</v>
       </c>
@@ -15628,6 +17293,12 @@
       <c r="N293" t="s">
         <v>691</v>
       </c>
+      <c r="O293" t="s">
+        <v>689</v>
+      </c>
+      <c r="P293" t="s">
+        <v>690</v>
+      </c>
       <c r="R293" t="s">
         <v>702</v>
       </c>
@@ -15677,6 +17348,12 @@
       <c r="N294" t="s">
         <v>691</v>
       </c>
+      <c r="O294" t="s">
+        <v>689</v>
+      </c>
+      <c r="P294" t="s">
+        <v>690</v>
+      </c>
       <c r="R294" t="s">
         <v>702</v>
       </c>
@@ -15726,6 +17403,12 @@
       <c r="N295" t="s">
         <v>692</v>
       </c>
+      <c r="O295" t="s">
+        <v>690</v>
+      </c>
+      <c r="P295" t="s">
+        <v>690</v>
+      </c>
       <c r="R295" t="s">
         <v>702</v>
       </c>
@@ -15775,6 +17458,12 @@
       <c r="N296" t="s">
         <v>690</v>
       </c>
+      <c r="O296" t="s">
+        <v>691</v>
+      </c>
+      <c r="P296" t="s">
+        <v>689</v>
+      </c>
       <c r="R296" t="s">
         <v>702</v>
       </c>
@@ -15824,6 +17513,12 @@
       <c r="N297" t="s">
         <v>691</v>
       </c>
+      <c r="O297" t="s">
+        <v>689</v>
+      </c>
+      <c r="P297" t="s">
+        <v>690</v>
+      </c>
       <c r="R297" t="s">
         <v>702</v>
       </c>
@@ -15873,6 +17568,12 @@
       <c r="N298" t="s">
         <v>691</v>
       </c>
+      <c r="O298" t="s">
+        <v>689</v>
+      </c>
+      <c r="P298" t="s">
+        <v>690</v>
+      </c>
       <c r="R298" t="s">
         <v>702</v>
       </c>
@@ -15916,6 +17617,12 @@
       <c r="N299" t="s">
         <v>692</v>
       </c>
+      <c r="O299" t="s">
+        <v>690</v>
+      </c>
+      <c r="P299" t="s">
+        <v>690</v>
+      </c>
       <c r="R299" t="s">
         <v>702</v>
       </c>
@@ -15965,6 +17672,12 @@
       <c r="N300" t="s">
         <v>691</v>
       </c>
+      <c r="O300" t="s">
+        <v>689</v>
+      </c>
+      <c r="P300" t="s">
+        <v>690</v>
+      </c>
       <c r="R300" t="s">
         <v>702</v>
       </c>
@@ -16014,6 +17727,12 @@
       <c r="N301" t="s">
         <v>692</v>
       </c>
+      <c r="O301" t="s">
+        <v>690</v>
+      </c>
+      <c r="P301" t="s">
+        <v>690</v>
+      </c>
       <c r="R301" t="s">
         <v>702</v>
       </c>
@@ -16063,6 +17782,12 @@
       <c r="N302" t="s">
         <v>689</v>
       </c>
+      <c r="O302" t="s">
+        <v>689</v>
+      </c>
+      <c r="P302" t="s">
+        <v>690</v>
+      </c>
       <c r="R302" t="s">
         <v>702</v>
       </c>
@@ -16112,6 +17837,12 @@
       <c r="N303" t="s">
         <v>692</v>
       </c>
+      <c r="O303" t="s">
+        <v>690</v>
+      </c>
+      <c r="P303" t="s">
+        <v>690</v>
+      </c>
       <c r="R303" t="s">
         <v>702</v>
       </c>
@@ -16161,6 +17892,12 @@
       <c r="N304" t="s">
         <v>692</v>
       </c>
+      <c r="O304" t="s">
+        <v>690</v>
+      </c>
+      <c r="P304" t="s">
+        <v>690</v>
+      </c>
       <c r="R304" t="s">
         <v>702</v>
       </c>
@@ -16210,6 +17947,12 @@
       <c r="N305" t="s">
         <v>692</v>
       </c>
+      <c r="O305" t="s">
+        <v>690</v>
+      </c>
+      <c r="P305" t="s">
+        <v>690</v>
+      </c>
       <c r="R305" t="s">
         <v>702</v>
       </c>
@@ -16259,6 +18002,12 @@
       <c r="N306" t="s">
         <v>692</v>
       </c>
+      <c r="O306" t="s">
+        <v>690</v>
+      </c>
+      <c r="P306" t="s">
+        <v>690</v>
+      </c>
       <c r="R306" t="s">
         <v>702</v>
       </c>
@@ -16308,6 +18057,12 @@
       <c r="N307" t="s">
         <v>692</v>
       </c>
+      <c r="O307" t="s">
+        <v>689</v>
+      </c>
+      <c r="P307" t="s">
+        <v>690</v>
+      </c>
       <c r="R307" t="s">
         <v>702</v>
       </c>
@@ -16357,6 +18112,12 @@
       <c r="N308" t="s">
         <v>692</v>
       </c>
+      <c r="O308" t="s">
+        <v>689</v>
+      </c>
+      <c r="P308" t="s">
+        <v>690</v>
+      </c>
       <c r="R308" t="s">
         <v>702</v>
       </c>
@@ -16406,6 +18167,12 @@
       <c r="N309" t="s">
         <v>691</v>
       </c>
+      <c r="O309" t="s">
+        <v>689</v>
+      </c>
+      <c r="P309" t="s">
+        <v>690</v>
+      </c>
       <c r="R309" t="s">
         <v>702</v>
       </c>
@@ -16455,6 +18222,12 @@
       <c r="N310" t="s">
         <v>690</v>
       </c>
+      <c r="O310" t="s">
+        <v>691</v>
+      </c>
+      <c r="P310" t="s">
+        <v>690</v>
+      </c>
       <c r="R310" t="s">
         <v>702</v>
       </c>
@@ -16504,6 +18277,12 @@
       <c r="N311" t="s">
         <v>692</v>
       </c>
+      <c r="O311" t="s">
+        <v>690</v>
+      </c>
+      <c r="P311" t="s">
+        <v>690</v>
+      </c>
       <c r="R311" t="s">
         <v>702</v>
       </c>
@@ -16553,6 +18332,12 @@
       <c r="N312" t="s">
         <v>692</v>
       </c>
+      <c r="O312" t="s">
+        <v>689</v>
+      </c>
+      <c r="P312" t="s">
+        <v>690</v>
+      </c>
       <c r="R312" t="s">
         <v>702</v>
       </c>
@@ -16602,6 +18387,12 @@
       <c r="N313" t="s">
         <v>692</v>
       </c>
+      <c r="O313" t="s">
+        <v>690</v>
+      </c>
+      <c r="P313" t="s">
+        <v>690</v>
+      </c>
       <c r="R313" t="s">
         <v>702</v>
       </c>
@@ -16651,6 +18442,12 @@
       <c r="N314" t="s">
         <v>692</v>
       </c>
+      <c r="O314" t="s">
+        <v>689</v>
+      </c>
+      <c r="P314" t="s">
+        <v>690</v>
+      </c>
       <c r="R314" t="s">
         <v>702</v>
       </c>
@@ -16694,6 +18491,12 @@
       <c r="N315" t="s">
         <v>689</v>
       </c>
+      <c r="O315" t="s">
+        <v>689</v>
+      </c>
+      <c r="P315" t="s">
+        <v>690</v>
+      </c>
       <c r="R315" t="s">
         <v>702</v>
       </c>
@@ -16737,6 +18540,12 @@
       <c r="N316" t="s">
         <v>691</v>
       </c>
+      <c r="O316" t="s">
+        <v>690</v>
+      </c>
+      <c r="P316" t="s">
+        <v>690</v>
+      </c>
       <c r="R316" t="s">
         <v>702</v>
       </c>
@@ -16780,6 +18589,12 @@
       <c r="N317" t="s">
         <v>691</v>
       </c>
+      <c r="O317" t="s">
+        <v>690</v>
+      </c>
+      <c r="P317" t="s">
+        <v>689</v>
+      </c>
       <c r="R317" t="s">
         <v>702</v>
       </c>
@@ -16823,6 +18638,12 @@
       <c r="N318" t="s">
         <v>691</v>
       </c>
+      <c r="O318" t="s">
+        <v>690</v>
+      </c>
+      <c r="P318" t="s">
+        <v>690</v>
+      </c>
       <c r="R318" t="s">
         <v>702</v>
       </c>
@@ -16866,6 +18687,12 @@
       <c r="N319" t="s">
         <v>691</v>
       </c>
+      <c r="O319" t="s">
+        <v>689</v>
+      </c>
+      <c r="P319" t="s">
+        <v>690</v>
+      </c>
       <c r="R319" t="s">
         <v>702</v>
       </c>
@@ -16915,6 +18742,12 @@
       <c r="N320" t="s">
         <v>691</v>
       </c>
+      <c r="O320" t="s">
+        <v>690</v>
+      </c>
+      <c r="P320" t="s">
+        <v>690</v>
+      </c>
       <c r="R320" t="s">
         <v>702</v>
       </c>
@@ -16964,6 +18797,12 @@
       <c r="N321" t="s">
         <v>692</v>
       </c>
+      <c r="O321" t="s">
+        <v>690</v>
+      </c>
+      <c r="P321" t="s">
+        <v>690</v>
+      </c>
       <c r="R321" t="s">
         <v>702</v>
       </c>
@@ -17013,6 +18852,12 @@
       <c r="N322" t="s">
         <v>691</v>
       </c>
+      <c r="O322" t="s">
+        <v>690</v>
+      </c>
+      <c r="P322" t="s">
+        <v>690</v>
+      </c>
       <c r="R322" t="s">
         <v>702</v>
       </c>
@@ -17062,6 +18907,12 @@
       <c r="N323" t="s">
         <v>692</v>
       </c>
+      <c r="O323" t="s">
+        <v>690</v>
+      </c>
+      <c r="P323" t="s">
+        <v>690</v>
+      </c>
       <c r="R323" t="s">
         <v>702</v>
       </c>
@@ -17111,6 +18962,12 @@
       <c r="N324" t="s">
         <v>692</v>
       </c>
+      <c r="O324" t="s">
+        <v>690</v>
+      </c>
+      <c r="P324" t="s">
+        <v>690</v>
+      </c>
       <c r="R324" t="s">
         <v>702</v>
       </c>
@@ -17160,6 +19017,12 @@
       <c r="N325" t="s">
         <v>691</v>
       </c>
+      <c r="O325" t="s">
+        <v>690</v>
+      </c>
+      <c r="P325" t="s">
+        <v>689</v>
+      </c>
       <c r="R325" t="s">
         <v>702</v>
       </c>
@@ -17209,6 +19072,12 @@
       <c r="N326" t="s">
         <v>692</v>
       </c>
+      <c r="O326" t="s">
+        <v>690</v>
+      </c>
+      <c r="P326" t="s">
+        <v>690</v>
+      </c>
       <c r="R326" t="s">
         <v>702</v>
       </c>
@@ -17258,6 +19127,12 @@
       <c r="N327" t="s">
         <v>690</v>
       </c>
+      <c r="O327" t="s">
+        <v>691</v>
+      </c>
+      <c r="P327" t="s">
+        <v>689</v>
+      </c>
       <c r="R327" t="s">
         <v>702</v>
       </c>
@@ -17289,7 +19164,7 @@
         <f t="shared" si="5"/>
         <v>85.7</v>
       </c>
-      <c r="H328" s="4" t="s">
+      <c r="H328" s="6" t="s">
         <v>436</v>
       </c>
       <c r="I328" t="s">
@@ -17305,6 +19180,12 @@
         <v>691</v>
       </c>
       <c r="N328" t="s">
+        <v>690</v>
+      </c>
+      <c r="O328" t="s">
+        <v>692</v>
+      </c>
+      <c r="P328" t="s">
         <v>690</v>
       </c>
       <c r="R328" t="s">
@@ -17356,6 +19237,12 @@
       <c r="N329" t="s">
         <v>692</v>
       </c>
+      <c r="O329" t="s">
+        <v>690</v>
+      </c>
+      <c r="P329" t="s">
+        <v>690</v>
+      </c>
       <c r="R329" t="s">
         <v>702</v>
       </c>
@@ -17405,6 +19292,12 @@
       <c r="N330" t="s">
         <v>691</v>
       </c>
+      <c r="O330" t="s">
+        <v>690</v>
+      </c>
+      <c r="P330" t="s">
+        <v>690</v>
+      </c>
       <c r="R330" t="s">
         <v>702</v>
       </c>
@@ -17454,6 +19347,12 @@
       <c r="N331" t="s">
         <v>691</v>
       </c>
+      <c r="O331" t="s">
+        <v>690</v>
+      </c>
+      <c r="P331" t="s">
+        <v>690</v>
+      </c>
       <c r="R331" t="s">
         <v>702</v>
       </c>
@@ -17503,6 +19402,12 @@
       <c r="N332" t="s">
         <v>691</v>
       </c>
+      <c r="O332" t="s">
+        <v>690</v>
+      </c>
+      <c r="P332" t="s">
+        <v>689</v>
+      </c>
       <c r="R332" t="s">
         <v>702</v>
       </c>
@@ -17552,6 +19457,12 @@
       <c r="N333" t="s">
         <v>692</v>
       </c>
+      <c r="O333" t="s">
+        <v>690</v>
+      </c>
+      <c r="P333" t="s">
+        <v>690</v>
+      </c>
       <c r="R333" t="s">
         <v>702</v>
       </c>
@@ -17601,6 +19512,12 @@
       <c r="N334" t="s">
         <v>692</v>
       </c>
+      <c r="O334" t="s">
+        <v>690</v>
+      </c>
+      <c r="P334" t="s">
+        <v>690</v>
+      </c>
       <c r="R334" t="s">
         <v>702</v>
       </c>
@@ -17650,6 +19567,12 @@
       <c r="N335" t="s">
         <v>691</v>
       </c>
+      <c r="O335" t="s">
+        <v>689</v>
+      </c>
+      <c r="P335" t="s">
+        <v>690</v>
+      </c>
       <c r="R335" t="s">
         <v>702</v>
       </c>
@@ -17699,6 +19622,12 @@
       <c r="N336" t="s">
         <v>692</v>
       </c>
+      <c r="O336" t="s">
+        <v>690</v>
+      </c>
+      <c r="P336" t="s">
+        <v>690</v>
+      </c>
       <c r="R336" t="s">
         <v>702</v>
       </c>
@@ -17748,6 +19677,12 @@
       <c r="N337" t="s">
         <v>691</v>
       </c>
+      <c r="O337" t="s">
+        <v>689</v>
+      </c>
+      <c r="P337" t="s">
+        <v>690</v>
+      </c>
       <c r="R337" t="s">
         <v>702</v>
       </c>
@@ -17797,6 +19732,12 @@
       <c r="N338" t="s">
         <v>692</v>
       </c>
+      <c r="O338" t="s">
+        <v>690</v>
+      </c>
+      <c r="P338" t="s">
+        <v>690</v>
+      </c>
       <c r="R338" t="s">
         <v>702</v>
       </c>
@@ -17846,6 +19787,12 @@
       <c r="N339" t="s">
         <v>692</v>
       </c>
+      <c r="O339" t="s">
+        <v>690</v>
+      </c>
+      <c r="P339" t="s">
+        <v>690</v>
+      </c>
       <c r="R339" t="s">
         <v>702</v>
       </c>
@@ -17895,6 +19842,12 @@
       <c r="N340" t="s">
         <v>692</v>
       </c>
+      <c r="O340" t="s">
+        <v>690</v>
+      </c>
+      <c r="P340" t="s">
+        <v>690</v>
+      </c>
       <c r="R340" t="s">
         <v>702</v>
       </c>
@@ -17944,6 +19897,12 @@
       <c r="N341" t="s">
         <v>692</v>
       </c>
+      <c r="O341" t="s">
+        <v>690</v>
+      </c>
+      <c r="P341" t="s">
+        <v>690</v>
+      </c>
       <c r="R341" t="s">
         <v>702</v>
       </c>
@@ -17993,6 +19952,12 @@
       <c r="N342" t="s">
         <v>692</v>
       </c>
+      <c r="O342" t="s">
+        <v>690</v>
+      </c>
+      <c r="P342" t="s">
+        <v>690</v>
+      </c>
       <c r="R342" t="s">
         <v>702</v>
       </c>
@@ -18036,6 +20001,12 @@
       <c r="N343" t="s">
         <v>691</v>
       </c>
+      <c r="O343" t="s">
+        <v>689</v>
+      </c>
+      <c r="P343" t="s">
+        <v>689</v>
+      </c>
       <c r="R343" t="s">
         <v>702</v>
       </c>
@@ -18079,6 +20050,12 @@
       <c r="N344" t="s">
         <v>692</v>
       </c>
+      <c r="O344" t="s">
+        <v>690</v>
+      </c>
+      <c r="P344" t="s">
+        <v>690</v>
+      </c>
       <c r="R344" t="s">
         <v>702</v>
       </c>
@@ -18122,6 +20099,12 @@
       <c r="N345" t="s">
         <v>691</v>
       </c>
+      <c r="O345" t="s">
+        <v>689</v>
+      </c>
+      <c r="P345" t="s">
+        <v>690</v>
+      </c>
       <c r="R345" t="s">
         <v>702</v>
       </c>
@@ -18165,6 +20148,12 @@
       <c r="N346" t="s">
         <v>691</v>
       </c>
+      <c r="O346" t="s">
+        <v>691</v>
+      </c>
+      <c r="P346" t="s">
+        <v>690</v>
+      </c>
       <c r="R346" t="s">
         <v>702</v>
       </c>
@@ -18208,6 +20197,12 @@
       <c r="N347" t="s">
         <v>691</v>
       </c>
+      <c r="O347" t="s">
+        <v>689</v>
+      </c>
+      <c r="P347" t="s">
+        <v>690</v>
+      </c>
       <c r="R347" t="s">
         <v>702</v>
       </c>
@@ -18251,6 +20246,12 @@
       <c r="N348" t="s">
         <v>691</v>
       </c>
+      <c r="O348" t="s">
+        <v>689</v>
+      </c>
+      <c r="P348" t="s">
+        <v>690</v>
+      </c>
       <c r="R348" t="s">
         <v>702</v>
       </c>
@@ -18294,6 +20295,12 @@
       <c r="N349" t="s">
         <v>691</v>
       </c>
+      <c r="O349" t="s">
+        <v>689</v>
+      </c>
+      <c r="P349" t="s">
+        <v>690</v>
+      </c>
       <c r="R349" t="s">
         <v>702</v>
       </c>
@@ -18337,6 +20344,12 @@
       <c r="N350" t="s">
         <v>690</v>
       </c>
+      <c r="O350" t="s">
+        <v>692</v>
+      </c>
+      <c r="P350" t="s">
+        <v>690</v>
+      </c>
       <c r="R350" t="s">
         <v>702</v>
       </c>
@@ -18380,6 +20393,12 @@
       <c r="N351" t="s">
         <v>691</v>
       </c>
+      <c r="O351" t="s">
+        <v>691</v>
+      </c>
+      <c r="P351" t="s">
+        <v>690</v>
+      </c>
       <c r="R351" t="s">
         <v>702</v>
       </c>
@@ -18423,6 +20442,12 @@
       <c r="N352" t="s">
         <v>692</v>
       </c>
+      <c r="O352" t="s">
+        <v>690</v>
+      </c>
+      <c r="P352" t="s">
+        <v>690</v>
+      </c>
       <c r="R352" t="s">
         <v>702</v>
       </c>
@@ -18467,6 +20492,12 @@
       <c r="N353" t="s">
         <v>692</v>
       </c>
+      <c r="O353" t="s">
+        <v>690</v>
+      </c>
+      <c r="P353" t="s">
+        <v>690</v>
+      </c>
       <c r="R353" t="s">
         <v>702</v>
       </c>
@@ -18511,6 +20542,12 @@
       <c r="N354" t="s">
         <v>692</v>
       </c>
+      <c r="O354" t="s">
+        <v>690</v>
+      </c>
+      <c r="P354" t="s">
+        <v>690</v>
+      </c>
       <c r="R354" t="s">
         <v>702</v>
       </c>
@@ -18555,6 +20592,12 @@
       <c r="N355" t="s">
         <v>692</v>
       </c>
+      <c r="O355" t="s">
+        <v>689</v>
+      </c>
+      <c r="P355" t="s">
+        <v>690</v>
+      </c>
       <c r="R355" t="s">
         <v>702</v>
       </c>
@@ -18599,6 +20642,12 @@
       <c r="N356" t="s">
         <v>691</v>
       </c>
+      <c r="O356" t="s">
+        <v>689</v>
+      </c>
+      <c r="P356" t="s">
+        <v>690</v>
+      </c>
       <c r="R356" t="s">
         <v>702</v>
       </c>
@@ -18643,6 +20692,12 @@
       <c r="N357" t="s">
         <v>691</v>
       </c>
+      <c r="O357" t="s">
+        <v>691</v>
+      </c>
+      <c r="P357" t="s">
+        <v>690</v>
+      </c>
       <c r="R357" t="s">
         <v>702</v>
       </c>
@@ -18687,6 +20742,12 @@
       <c r="N358" t="s">
         <v>692</v>
       </c>
+      <c r="O358" t="s">
+        <v>689</v>
+      </c>
+      <c r="P358" t="s">
+        <v>690</v>
+      </c>
       <c r="R358" t="s">
         <v>702</v>
       </c>
@@ -18731,6 +20792,12 @@
       <c r="N359" t="s">
         <v>691</v>
       </c>
+      <c r="O359" t="s">
+        <v>689</v>
+      </c>
+      <c r="P359" t="s">
+        <v>690</v>
+      </c>
       <c r="R359" t="s">
         <v>702</v>
       </c>
@@ -18775,6 +20842,12 @@
       <c r="N360" t="s">
         <v>691</v>
       </c>
+      <c r="O360" t="s">
+        <v>691</v>
+      </c>
+      <c r="P360" t="s">
+        <v>690</v>
+      </c>
       <c r="R360" t="s">
         <v>702</v>
       </c>
@@ -18819,6 +20892,12 @@
       <c r="N361" t="s">
         <v>689</v>
       </c>
+      <c r="O361" t="s">
+        <v>691</v>
+      </c>
+      <c r="P361" t="s">
+        <v>690</v>
+      </c>
       <c r="R361" t="s">
         <v>702</v>
       </c>
@@ -18868,6 +20947,12 @@
       <c r="N362" t="s">
         <v>691</v>
       </c>
+      <c r="O362" t="s">
+        <v>689</v>
+      </c>
+      <c r="P362" t="s">
+        <v>690</v>
+      </c>
       <c r="R362" t="s">
         <v>702</v>
       </c>
@@ -18917,6 +21002,12 @@
       <c r="N363" t="s">
         <v>689</v>
       </c>
+      <c r="O363" t="s">
+        <v>689</v>
+      </c>
+      <c r="P363" t="s">
+        <v>689</v>
+      </c>
       <c r="R363" t="s">
         <v>702</v>
       </c>
@@ -18966,6 +21057,12 @@
       <c r="N364" t="s">
         <v>689</v>
       </c>
+      <c r="O364" t="s">
+        <v>689</v>
+      </c>
+      <c r="P364" t="s">
+        <v>689</v>
+      </c>
       <c r="R364" t="s">
         <v>702</v>
       </c>
@@ -19015,6 +21112,12 @@
       <c r="N365" t="s">
         <v>689</v>
       </c>
+      <c r="O365" t="s">
+        <v>690</v>
+      </c>
+      <c r="P365" t="s">
+        <v>690</v>
+      </c>
       <c r="R365" t="s">
         <v>702</v>
       </c>
@@ -19064,6 +21167,12 @@
       <c r="N366" t="s">
         <v>689</v>
       </c>
+      <c r="O366" t="s">
+        <v>689</v>
+      </c>
+      <c r="P366" t="s">
+        <v>689</v>
+      </c>
       <c r="R366" t="s">
         <v>702</v>
       </c>
@@ -19113,6 +21222,12 @@
       <c r="N367" t="s">
         <v>689</v>
       </c>
+      <c r="O367" t="s">
+        <v>689</v>
+      </c>
+      <c r="P367" t="s">
+        <v>689</v>
+      </c>
       <c r="R367" t="s">
         <v>702</v>
       </c>
@@ -19162,6 +21277,12 @@
       <c r="N368" t="s">
         <v>690</v>
       </c>
+      <c r="O368" t="s">
+        <v>689</v>
+      </c>
+      <c r="P368" t="s">
+        <v>691</v>
+      </c>
       <c r="R368" t="s">
         <v>702</v>
       </c>
@@ -19211,6 +21332,12 @@
       <c r="N369" t="s">
         <v>690</v>
       </c>
+      <c r="O369" t="s">
+        <v>689</v>
+      </c>
+      <c r="P369" t="s">
+        <v>691</v>
+      </c>
       <c r="R369" t="s">
         <v>702</v>
       </c>
@@ -19260,6 +21387,12 @@
       <c r="N370" t="s">
         <v>690</v>
       </c>
+      <c r="O370" t="s">
+        <v>689</v>
+      </c>
+      <c r="P370" t="s">
+        <v>692</v>
+      </c>
       <c r="R370" t="s">
         <v>702</v>
       </c>
@@ -19309,6 +21442,12 @@
       <c r="N371" t="s">
         <v>689</v>
       </c>
+      <c r="O371" t="s">
+        <v>690</v>
+      </c>
+      <c r="P371" t="s">
+        <v>689</v>
+      </c>
       <c r="R371" t="s">
         <v>702</v>
       </c>
@@ -19358,6 +21497,12 @@
       <c r="N372" t="s">
         <v>689</v>
       </c>
+      <c r="O372" t="s">
+        <v>690</v>
+      </c>
+      <c r="P372" t="s">
+        <v>691</v>
+      </c>
       <c r="R372" t="s">
         <v>702</v>
       </c>
@@ -19407,6 +21552,12 @@
       <c r="N373" t="s">
         <v>689</v>
       </c>
+      <c r="O373" t="s">
+        <v>690</v>
+      </c>
+      <c r="P373" t="s">
+        <v>689</v>
+      </c>
       <c r="R373" t="s">
         <v>702</v>
       </c>
@@ -19456,6 +21607,12 @@
       <c r="N374" t="s">
         <v>689</v>
       </c>
+      <c r="O374" t="s">
+        <v>690</v>
+      </c>
+      <c r="P374" t="s">
+        <v>689</v>
+      </c>
       <c r="R374" t="s">
         <v>702</v>
       </c>
@@ -19502,6 +21659,12 @@
       <c r="N375" t="s">
         <v>689</v>
       </c>
+      <c r="O375" t="s">
+        <v>689</v>
+      </c>
+      <c r="P375" t="s">
+        <v>689</v>
+      </c>
       <c r="R375" t="s">
         <v>702</v>
       </c>
@@ -19551,6 +21714,12 @@
       <c r="N376" t="s">
         <v>690</v>
       </c>
+      <c r="O376" t="s">
+        <v>690</v>
+      </c>
+      <c r="P376" t="s">
+        <v>692</v>
+      </c>
       <c r="R376" t="s">
         <v>702</v>
       </c>
@@ -19600,6 +21769,12 @@
       <c r="N377" t="s">
         <v>690</v>
       </c>
+      <c r="O377" t="s">
+        <v>690</v>
+      </c>
+      <c r="P377" t="s">
+        <v>692</v>
+      </c>
       <c r="R377" t="s">
         <v>702</v>
       </c>
@@ -19650,6 +21825,12 @@
       <c r="N378" t="s">
         <v>689</v>
       </c>
+      <c r="O378" t="s">
+        <v>689</v>
+      </c>
+      <c r="P378" t="s">
+        <v>689</v>
+      </c>
       <c r="R378" t="s">
         <v>702</v>
       </c>
@@ -19699,6 +21880,12 @@
       <c r="N379" t="s">
         <v>690</v>
       </c>
+      <c r="O379" t="s">
+        <v>691</v>
+      </c>
+      <c r="P379" t="s">
+        <v>691</v>
+      </c>
       <c r="R379" t="s">
         <v>702</v>
       </c>
@@ -19748,6 +21935,12 @@
       <c r="N380" t="s">
         <v>689</v>
       </c>
+      <c r="O380" t="s">
+        <v>690</v>
+      </c>
+      <c r="P380" t="s">
+        <v>691</v>
+      </c>
       <c r="R380" t="s">
         <v>702</v>
       </c>
@@ -19797,6 +21990,12 @@
       <c r="N381" t="s">
         <v>690</v>
       </c>
+      <c r="O381" t="s">
+        <v>689</v>
+      </c>
+      <c r="P381" t="s">
+        <v>692</v>
+      </c>
       <c r="R381" t="s">
         <v>702</v>
       </c>
@@ -19846,6 +22045,12 @@
       <c r="N382" t="s">
         <v>689</v>
       </c>
+      <c r="O382" t="s">
+        <v>690</v>
+      </c>
+      <c r="P382" t="s">
+        <v>691</v>
+      </c>
       <c r="R382" t="s">
         <v>702</v>
       </c>
@@ -19895,6 +22100,12 @@
       <c r="N383" t="s">
         <v>689</v>
       </c>
+      <c r="O383" t="s">
+        <v>689</v>
+      </c>
+      <c r="P383" t="s">
+        <v>689</v>
+      </c>
       <c r="R383" t="s">
         <v>702</v>
       </c>
@@ -19944,6 +22155,12 @@
       <c r="N384" t="s">
         <v>690</v>
       </c>
+      <c r="O384" t="s">
+        <v>690</v>
+      </c>
+      <c r="P384" t="s">
+        <v>692</v>
+      </c>
       <c r="R384" t="s">
         <v>702</v>
       </c>
@@ -19993,6 +22210,12 @@
       <c r="N385" t="s">
         <v>691</v>
       </c>
+      <c r="O385" t="s">
+        <v>690</v>
+      </c>
+      <c r="P385" t="s">
+        <v>689</v>
+      </c>
       <c r="R385" t="s">
         <v>702</v>
       </c>
@@ -20042,6 +22265,12 @@
       <c r="N386" t="s">
         <v>689</v>
       </c>
+      <c r="O386" t="s">
+        <v>689</v>
+      </c>
+      <c r="P386" t="s">
+        <v>689</v>
+      </c>
       <c r="R386" t="s">
         <v>702</v>
       </c>
@@ -20091,6 +22320,12 @@
       <c r="N387" t="s">
         <v>689</v>
       </c>
+      <c r="O387" t="s">
+        <v>689</v>
+      </c>
+      <c r="P387" t="s">
+        <v>689</v>
+      </c>
       <c r="R387" t="s">
         <v>702</v>
       </c>
@@ -20140,6 +22375,12 @@
       <c r="N388" t="s">
         <v>689</v>
       </c>
+      <c r="O388" t="s">
+        <v>690</v>
+      </c>
+      <c r="P388" t="s">
+        <v>691</v>
+      </c>
       <c r="R388" t="s">
         <v>702</v>
       </c>
@@ -20189,6 +22430,12 @@
       <c r="N389" t="s">
         <v>690</v>
       </c>
+      <c r="O389" t="s">
+        <v>690</v>
+      </c>
+      <c r="P389" t="s">
+        <v>692</v>
+      </c>
       <c r="R389" t="s">
         <v>702</v>
       </c>
@@ -20238,6 +22485,12 @@
       <c r="N390" t="s">
         <v>690</v>
       </c>
+      <c r="O390" t="s">
+        <v>691</v>
+      </c>
+      <c r="P390" t="s">
+        <v>692</v>
+      </c>
       <c r="R390" t="s">
         <v>702</v>
       </c>
@@ -20287,6 +22540,12 @@
       <c r="N391" t="s">
         <v>690</v>
       </c>
+      <c r="O391" t="s">
+        <v>692</v>
+      </c>
+      <c r="P391" t="s">
+        <v>691</v>
+      </c>
       <c r="R391" t="s">
         <v>702</v>
       </c>
@@ -20336,6 +22595,12 @@
       <c r="N392" t="s">
         <v>689</v>
       </c>
+      <c r="O392" t="s">
+        <v>689</v>
+      </c>
+      <c r="P392" t="s">
+        <v>689</v>
+      </c>
       <c r="R392" t="s">
         <v>702</v>
       </c>
@@ -20385,6 +22650,12 @@
       <c r="N393" t="s">
         <v>689</v>
       </c>
+      <c r="O393" t="s">
+        <v>689</v>
+      </c>
+      <c r="P393" t="s">
+        <v>689</v>
+      </c>
       <c r="R393" t="s">
         <v>702</v>
       </c>
@@ -20434,6 +22705,12 @@
       <c r="N394" t="s">
         <v>690</v>
       </c>
+      <c r="O394" t="s">
+        <v>689</v>
+      </c>
+      <c r="P394" t="s">
+        <v>692</v>
+      </c>
       <c r="R394" t="s">
         <v>702</v>
       </c>
@@ -20483,6 +22760,12 @@
       <c r="N395" t="s">
         <v>690</v>
       </c>
+      <c r="O395" t="s">
+        <v>690</v>
+      </c>
+      <c r="P395" t="s">
+        <v>692</v>
+      </c>
       <c r="R395" t="s">
         <v>702</v>
       </c>
@@ -20532,6 +22815,12 @@
       <c r="N396" t="s">
         <v>690</v>
       </c>
+      <c r="O396" t="s">
+        <v>690</v>
+      </c>
+      <c r="P396" t="s">
+        <v>692</v>
+      </c>
       <c r="R396" t="s">
         <v>702</v>
       </c>
@@ -20581,6 +22870,12 @@
       <c r="N397" t="s">
         <v>689</v>
       </c>
+      <c r="O397" t="s">
+        <v>689</v>
+      </c>
+      <c r="P397" t="s">
+        <v>689</v>
+      </c>
       <c r="R397" t="s">
         <v>702</v>
       </c>
@@ -20630,6 +22925,12 @@
       <c r="N398" t="s">
         <v>689</v>
       </c>
+      <c r="O398" t="s">
+        <v>690</v>
+      </c>
+      <c r="P398" t="s">
+        <v>691</v>
+      </c>
       <c r="R398" t="s">
         <v>702</v>
       </c>
@@ -20679,6 +22980,12 @@
       <c r="N399" t="s">
         <v>689</v>
       </c>
+      <c r="O399" t="s">
+        <v>689</v>
+      </c>
+      <c r="P399" t="s">
+        <v>689</v>
+      </c>
       <c r="R399" t="s">
         <v>702</v>
       </c>
@@ -20722,6 +23029,12 @@
       <c r="N400" t="s">
         <v>691</v>
       </c>
+      <c r="O400" t="s">
+        <v>690</v>
+      </c>
+      <c r="P400" t="s">
+        <v>689</v>
+      </c>
       <c r="R400" t="s">
         <v>702</v>
       </c>
@@ -20765,6 +23078,12 @@
       <c r="N401" t="s">
         <v>692</v>
       </c>
+      <c r="O401" t="s">
+        <v>690</v>
+      </c>
+      <c r="P401" t="s">
+        <v>690</v>
+      </c>
       <c r="R401" t="s">
         <v>702</v>
       </c>
@@ -20808,6 +23127,12 @@
       <c r="N402" t="s">
         <v>692</v>
       </c>
+      <c r="O402" t="s">
+        <v>690</v>
+      </c>
+      <c r="P402" t="s">
+        <v>690</v>
+      </c>
       <c r="R402" t="s">
         <v>702</v>
       </c>
@@ -20851,6 +23176,12 @@
       <c r="N403" t="s">
         <v>692</v>
       </c>
+      <c r="O403" t="s">
+        <v>690</v>
+      </c>
+      <c r="P403" t="s">
+        <v>690</v>
+      </c>
       <c r="R403" t="s">
         <v>702</v>
       </c>
@@ -20894,6 +23225,12 @@
       <c r="N404" t="s">
         <v>692</v>
       </c>
+      <c r="O404" t="s">
+        <v>690</v>
+      </c>
+      <c r="P404" t="s">
+        <v>690</v>
+      </c>
       <c r="R404" t="s">
         <v>702</v>
       </c>
@@ -20938,6 +23275,12 @@
       <c r="N405" t="s">
         <v>691</v>
       </c>
+      <c r="O405" t="s">
+        <v>689</v>
+      </c>
+      <c r="P405" t="s">
+        <v>690</v>
+      </c>
       <c r="R405" t="s">
         <v>702</v>
       </c>
@@ -20982,6 +23325,12 @@
       <c r="N406" t="s">
         <v>691</v>
       </c>
+      <c r="O406" t="s">
+        <v>689</v>
+      </c>
+      <c r="P406" t="s">
+        <v>690</v>
+      </c>
       <c r="R406" t="s">
         <v>702</v>
       </c>
@@ -21026,6 +23375,12 @@
       <c r="N407" t="s">
         <v>690</v>
       </c>
+      <c r="O407" t="s">
+        <v>692</v>
+      </c>
+      <c r="P407" t="s">
+        <v>690</v>
+      </c>
       <c r="R407" t="s">
         <v>702</v>
       </c>
@@ -21070,6 +23425,12 @@
       <c r="N408" t="s">
         <v>689</v>
       </c>
+      <c r="O408" t="s">
+        <v>691</v>
+      </c>
+      <c r="P408" t="s">
+        <v>690</v>
+      </c>
       <c r="R408" t="s">
         <v>702</v>
       </c>
@@ -21114,6 +23475,12 @@
       <c r="N409" t="s">
         <v>691</v>
       </c>
+      <c r="O409" t="s">
+        <v>689</v>
+      </c>
+      <c r="P409" t="s">
+        <v>690</v>
+      </c>
       <c r="R409" t="s">
         <v>702</v>
       </c>
@@ -21158,6 +23525,12 @@
       <c r="N410" t="s">
         <v>691</v>
       </c>
+      <c r="O410" t="s">
+        <v>690</v>
+      </c>
+      <c r="P410" t="s">
+        <v>690</v>
+      </c>
       <c r="R410" t="s">
         <v>702</v>
       </c>
@@ -21202,6 +23575,12 @@
       <c r="N411" t="s">
         <v>689</v>
       </c>
+      <c r="O411" t="s">
+        <v>689</v>
+      </c>
+      <c r="P411" t="s">
+        <v>689</v>
+      </c>
       <c r="R411" t="s">
         <v>702</v>
       </c>
@@ -21246,6 +23625,12 @@
       <c r="N412" t="s">
         <v>689</v>
       </c>
+      <c r="O412" t="s">
+        <v>689</v>
+      </c>
+      <c r="P412" t="s">
+        <v>689</v>
+      </c>
       <c r="R412" t="s">
         <v>702</v>
       </c>
@@ -21290,6 +23675,12 @@
       <c r="N413" t="s">
         <v>692</v>
       </c>
+      <c r="O413" t="s">
+        <v>690</v>
+      </c>
+      <c r="P413" t="s">
+        <v>690</v>
+      </c>
       <c r="R413" t="s">
         <v>702</v>
       </c>
@@ -21334,6 +23725,12 @@
       <c r="N414" t="s">
         <v>689</v>
       </c>
+      <c r="O414" t="s">
+        <v>690</v>
+      </c>
+      <c r="P414" t="s">
+        <v>689</v>
+      </c>
       <c r="R414" t="s">
         <v>702</v>
       </c>
@@ -21378,6 +23775,12 @@
       <c r="N415" t="s">
         <v>689</v>
       </c>
+      <c r="O415" t="s">
+        <v>690</v>
+      </c>
+      <c r="P415" t="s">
+        <v>690</v>
+      </c>
       <c r="R415" t="s">
         <v>702</v>
       </c>
@@ -21421,6 +23824,12 @@
       <c r="N416" t="s">
         <v>689</v>
       </c>
+      <c r="O416" t="s">
+        <v>690</v>
+      </c>
+      <c r="P416" t="s">
+        <v>690</v>
+      </c>
       <c r="R416" t="s">
         <v>701</v>
       </c>
@@ -21464,6 +23873,12 @@
       <c r="N417" t="s">
         <v>691</v>
       </c>
+      <c r="O417" t="s">
+        <v>690</v>
+      </c>
+      <c r="P417" t="s">
+        <v>690</v>
+      </c>
       <c r="R417" t="s">
         <v>701</v>
       </c>
@@ -21507,6 +23922,12 @@
       <c r="N418" t="s">
         <v>692</v>
       </c>
+      <c r="O418" t="s">
+        <v>690</v>
+      </c>
+      <c r="P418" t="s">
+        <v>690</v>
+      </c>
       <c r="R418" t="s">
         <v>701</v>
       </c>
@@ -21550,6 +23971,12 @@
       <c r="N419" t="s">
         <v>689</v>
       </c>
+      <c r="O419" t="s">
+        <v>690</v>
+      </c>
+      <c r="P419" t="s">
+        <v>691</v>
+      </c>
       <c r="R419" t="s">
         <v>701</v>
       </c>
@@ -21593,6 +24020,12 @@
       <c r="N420" t="s">
         <v>692</v>
       </c>
+      <c r="O420" t="s">
+        <v>690</v>
+      </c>
+      <c r="P420" t="s">
+        <v>690</v>
+      </c>
       <c r="R420" t="s">
         <v>701</v>
       </c>
@@ -21636,6 +24069,12 @@
       <c r="N421" t="s">
         <v>691</v>
       </c>
+      <c r="O421" t="s">
+        <v>690</v>
+      </c>
+      <c r="P421" t="s">
+        <v>690</v>
+      </c>
       <c r="R421" t="s">
         <v>701</v>
       </c>
@@ -21679,6 +24118,12 @@
       <c r="N422" t="s">
         <v>691</v>
       </c>
+      <c r="O422" t="s">
+        <v>690</v>
+      </c>
+      <c r="P422" t="s">
+        <v>690</v>
+      </c>
       <c r="R422" t="s">
         <v>701</v>
       </c>
@@ -21722,6 +24167,12 @@
       <c r="N423" t="s">
         <v>691</v>
       </c>
+      <c r="O423" t="s">
+        <v>690</v>
+      </c>
+      <c r="P423" t="s">
+        <v>690</v>
+      </c>
       <c r="R423" t="s">
         <v>701</v>
       </c>
@@ -21765,6 +24216,12 @@
       <c r="N424" t="s">
         <v>690</v>
       </c>
+      <c r="O424" t="s">
+        <v>689</v>
+      </c>
+      <c r="P424" t="s">
+        <v>690</v>
+      </c>
       <c r="R424" t="s">
         <v>701</v>
       </c>
@@ -21808,6 +24265,12 @@
       <c r="N425" t="s">
         <v>691</v>
       </c>
+      <c r="O425" t="s">
+        <v>690</v>
+      </c>
+      <c r="P425" t="s">
+        <v>690</v>
+      </c>
       <c r="R425" t="s">
         <v>701</v>
       </c>
@@ -21857,6 +24320,12 @@
       <c r="N426" t="s">
         <v>692</v>
       </c>
+      <c r="O426" t="s">
+        <v>690</v>
+      </c>
+      <c r="P426" t="s">
+        <v>690</v>
+      </c>
       <c r="R426" t="s">
         <v>702</v>
       </c>
@@ -21906,6 +24375,12 @@
       <c r="N427" t="s">
         <v>692</v>
       </c>
+      <c r="O427" t="s">
+        <v>690</v>
+      </c>
+      <c r="P427" t="s">
+        <v>690</v>
+      </c>
       <c r="R427" t="s">
         <v>702</v>
       </c>
@@ -21949,6 +24424,12 @@
       <c r="N428" t="s">
         <v>692</v>
       </c>
+      <c r="O428" t="s">
+        <v>690</v>
+      </c>
+      <c r="P428" t="s">
+        <v>690</v>
+      </c>
       <c r="R428" t="s">
         <v>702</v>
       </c>
@@ -21992,6 +24473,12 @@
       <c r="N429" t="s">
         <v>692</v>
       </c>
+      <c r="O429" t="s">
+        <v>690</v>
+      </c>
+      <c r="P429" t="s">
+        <v>690</v>
+      </c>
       <c r="R429" t="s">
         <v>702</v>
       </c>
@@ -22035,6 +24522,12 @@
       <c r="N430" t="s">
         <v>692</v>
       </c>
+      <c r="O430" t="s">
+        <v>690</v>
+      </c>
+      <c r="P430" t="s">
+        <v>690</v>
+      </c>
       <c r="R430" t="s">
         <v>702</v>
       </c>
@@ -22078,6 +24571,12 @@
       <c r="N431" t="s">
         <v>689</v>
       </c>
+      <c r="O431" t="s">
+        <v>691</v>
+      </c>
+      <c r="P431" t="s">
+        <v>689</v>
+      </c>
       <c r="R431" t="s">
         <v>702</v>
       </c>
@@ -22121,6 +24620,12 @@
       <c r="N432" t="s">
         <v>692</v>
       </c>
+      <c r="O432" t="s">
+        <v>690</v>
+      </c>
+      <c r="P432" t="s">
+        <v>690</v>
+      </c>
       <c r="R432" t="s">
         <v>702</v>
       </c>
@@ -22164,6 +24669,12 @@
       <c r="N433" t="s">
         <v>692</v>
       </c>
+      <c r="O433" t="s">
+        <v>690</v>
+      </c>
+      <c r="P433" t="s">
+        <v>690</v>
+      </c>
       <c r="R433" t="s">
         <v>702</v>
       </c>
@@ -22207,6 +24718,12 @@
       <c r="N434" t="s">
         <v>692</v>
       </c>
+      <c r="O434" t="s">
+        <v>690</v>
+      </c>
+      <c r="P434" t="s">
+        <v>690</v>
+      </c>
       <c r="R434" t="s">
         <v>702</v>
       </c>
@@ -22250,6 +24767,12 @@
       <c r="N435" t="s">
         <v>692</v>
       </c>
+      <c r="O435" t="s">
+        <v>690</v>
+      </c>
+      <c r="P435" t="s">
+        <v>690</v>
+      </c>
       <c r="R435" t="s">
         <v>702</v>
       </c>
@@ -22292,6 +24815,9 @@
       </c>
       <c r="N436" t="s">
         <v>692</v>
+      </c>
+      <c r="P436" t="s">
+        <v>690</v>
       </c>
       <c r="R436" t="s">
         <v>702</v>

--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/house_model_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8C79C3-2CE8-1F4F-85E8-35399414900E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6073063-6FB4-D646-A1F2-882E3885D360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5067" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5100" uniqueCount="730">
   <si>
     <t>State</t>
   </si>
@@ -2200,6 +2200,69 @@
   </si>
   <si>
     <t>Election System Notes</t>
+  </si>
+  <si>
+    <t>Galdo, Damon</t>
+  </si>
+  <si>
+    <t>Mullock, Zach</t>
+  </si>
+  <si>
+    <t>McGuire, Michael</t>
+  </si>
+  <si>
+    <t>Peace, Rachel</t>
+  </si>
+  <si>
+    <t>Kirrane, Sean</t>
+  </si>
+  <si>
+    <t>Herzig, Hillary</t>
+  </si>
+  <si>
+    <t>Bennett, Rebecca</t>
+  </si>
+  <si>
+    <t>Bucco, Carmen</t>
+  </si>
+  <si>
+    <t>Mejia, Analilia</t>
+  </si>
+  <si>
+    <t>Hathaway, Joe</t>
+  </si>
+  <si>
+    <t>Hamawy, Adam</t>
+  </si>
+  <si>
+    <t>Mele, Gregg</t>
+  </si>
+  <si>
+    <t>Bohannon, Christina</t>
+  </si>
+  <si>
+    <t>Miller-Meeks, Mariannette</t>
+  </si>
+  <si>
+    <t>James, Lindsay</t>
+  </si>
+  <si>
+    <t>Mitchell, Joe</t>
+  </si>
+  <si>
+    <t>Trone Garriott, Sarah</t>
+  </si>
+  <si>
+    <t>McGowan, Chris</t>
+  </si>
+  <si>
+    <t>Flint, Aaron</t>
+  </si>
+  <si>
+    <t>Gronli, Nicole</t>
+  </si>
+  <si>
+    <t>Jackley, Marty</t>
   </si>
 </sst>
 </file>
@@ -10746,6 +10809,12 @@
         <f t="shared" si="2"/>
         <v>-9.9999999999999645E-2</v>
       </c>
+      <c r="H161" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="I161" s="6" t="s">
+        <v>722</v>
+      </c>
       <c r="J161" t="s">
         <v>666</v>
       </c>
@@ -10795,6 +10864,12 @@
         <f t="shared" si="2"/>
         <v>-1.5999999999999996</v>
       </c>
+      <c r="H162" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="I162" s="4" t="s">
+        <v>724</v>
+      </c>
       <c r="J162" t="s">
         <v>666</v>
       </c>
@@ -10844,6 +10919,12 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
+      <c r="H163" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="I163" s="6" t="s">
+        <v>216</v>
+      </c>
       <c r="J163" t="s">
         <v>666</v>
       </c>
@@ -10893,6 +10974,9 @@
         <f t="shared" si="2"/>
         <v>-23.1</v>
       </c>
+      <c r="I164" s="4" t="s">
+        <v>726</v>
+      </c>
       <c r="J164" t="s">
         <v>666</v>
       </c>
@@ -14268,6 +14352,9 @@
         <f t="shared" si="3"/>
         <v>-3.0999999999999996</v>
       </c>
+      <c r="I233" s="4" t="s">
+        <v>727</v>
+      </c>
       <c r="J233" t="s">
         <v>668</v>
       </c>
@@ -14317,6 +14404,9 @@
         <f t="shared" si="3"/>
         <v>-21.1</v>
       </c>
+      <c r="I234" s="4" t="s">
+        <v>298</v>
+      </c>
       <c r="J234" t="s">
         <v>668</v>
       </c>
@@ -14825,6 +14915,12 @@
         <f t="shared" si="3"/>
         <v>27.1</v>
       </c>
+      <c r="H244" t="s">
+        <v>312</v>
+      </c>
+      <c r="I244" s="4" t="s">
+        <v>709</v>
+      </c>
       <c r="J244" t="s">
         <v>678</v>
       </c>
@@ -14874,6 +14970,12 @@
         <f t="shared" si="3"/>
         <v>-4.1999999999999993</v>
       </c>
+      <c r="H245" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="I245" t="s">
+        <v>313</v>
+      </c>
       <c r="J245" t="s">
         <v>678</v>
       </c>
@@ -14923,6 +15025,12 @@
         <f t="shared" si="3"/>
         <v>16.8</v>
       </c>
+      <c r="H246" t="s">
+        <v>314</v>
+      </c>
+      <c r="I246" s="4" t="s">
+        <v>711</v>
+      </c>
       <c r="J246" t="s">
         <v>678</v>
       </c>
@@ -14972,6 +15080,12 @@
         <f t="shared" si="3"/>
         <v>-21.700000000000003</v>
       </c>
+      <c r="H247" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="I247" t="s">
+        <v>315</v>
+      </c>
       <c r="J247" t="s">
         <v>678</v>
       </c>
@@ -15021,6 +15135,12 @@
         <f t="shared" si="3"/>
         <v>10.200000000000001</v>
       </c>
+      <c r="H248" t="s">
+        <v>316</v>
+      </c>
+      <c r="I248" s="4" t="s">
+        <v>713</v>
+      </c>
       <c r="J248" t="s">
         <v>678</v>
       </c>
@@ -15070,6 +15190,12 @@
         <f t="shared" si="3"/>
         <v>14.8</v>
       </c>
+      <c r="H249" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="I249" s="4" t="s">
+        <v>714</v>
+      </c>
       <c r="J249" t="s">
         <v>678</v>
       </c>
@@ -15119,6 +15245,12 @@
         <f t="shared" si="3"/>
         <v>7.2</v>
       </c>
+      <c r="H250" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="I250" t="s">
+        <v>318</v>
+      </c>
       <c r="J250" t="s">
         <v>678</v>
       </c>
@@ -15168,6 +15300,9 @@
         <f t="shared" si="3"/>
         <v>32.6</v>
       </c>
+      <c r="H251" t="s">
+        <v>319</v>
+      </c>
       <c r="J251" t="s">
         <v>678</v>
       </c>
@@ -15217,6 +15352,9 @@
         <f t="shared" si="3"/>
         <v>7.3000000000000007</v>
       </c>
+      <c r="H252" t="s">
+        <v>320</v>
+      </c>
       <c r="J252" t="s">
         <v>678</v>
       </c>
@@ -15266,6 +15404,12 @@
         <f t="shared" si="3"/>
         <v>59.199999999999996</v>
       </c>
+      <c r="H253" t="s">
+        <v>321</v>
+      </c>
+      <c r="I253" s="4" t="s">
+        <v>716</v>
+      </c>
       <c r="J253" t="s">
         <v>678</v>
       </c>
@@ -15315,6 +15459,12 @@
         <f t="shared" si="3"/>
         <v>17.100000000000001</v>
       </c>
+      <c r="H254" t="s">
+        <v>717</v>
+      </c>
+      <c r="I254" s="4" t="s">
+        <v>718</v>
+      </c>
       <c r="J254" t="s">
         <v>678</v>
       </c>
@@ -15364,6 +15514,12 @@
         <f t="shared" si="3"/>
         <v>32.299999999999997</v>
       </c>
+      <c r="H255" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="I255" s="4" t="s">
+        <v>720</v>
+      </c>
       <c r="J255" t="s">
         <v>678</v>
       </c>
@@ -20429,6 +20585,12 @@
       <c r="G352" s="3">
         <f t="shared" si="5"/>
         <v>-20.799999999999997</v>
+      </c>
+      <c r="H352" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="I352" s="4" t="s">
+        <v>729</v>
       </c>
       <c r="J352" t="s">
         <v>681</v>

--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/house_model_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC91D060-7D5A-4945-8EC5-AA0DFCC90D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9664176A-026D-7640-9579-1BD60C2EC363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5178" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5182" uniqueCount="771">
   <si>
     <t>State</t>
   </si>
@@ -2374,6 +2374,18 @@
   </si>
   <si>
     <t>Miller, Brian</t>
+  </si>
+  <si>
+    <t>Forstag, Sam</t>
+  </si>
+  <si>
+    <t>Lincoln, Kevin</t>
+  </si>
+  <si>
+    <t>Gallucci, Sam</t>
+  </si>
+  <si>
+    <t>Kirkland, Kyle</t>
   </si>
 </sst>
 </file>
@@ -4538,6 +4550,9 @@
       <c r="H35" t="s">
         <v>46</v>
       </c>
+      <c r="I35" s="4" t="s">
+        <v>768</v>
+      </c>
       <c r="K35" t="s">
         <v>668</v>
       </c>
@@ -4966,6 +4981,9 @@
       <c r="H43" t="s">
         <v>54</v>
       </c>
+      <c r="I43" s="4" t="s">
+        <v>770</v>
+      </c>
       <c r="K43" t="s">
         <v>668</v>
       </c>
@@ -4988,7 +5006,7 @@
         <v>700</v>
       </c>
       <c r="T43" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.2">
@@ -5230,6 +5248,9 @@
       <c r="H48" s="4" t="s">
         <v>737</v>
       </c>
+      <c r="I48" s="4" t="s">
+        <v>769</v>
+      </c>
       <c r="K48" t="s">
         <v>668</v>
       </c>
@@ -5252,7 +5273,7 @@
         <v>700</v>
       </c>
       <c r="T48" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.2">
@@ -14739,6 +14760,9 @@
         <f t="shared" si="3"/>
         <v>-3.0999999999999996</v>
       </c>
+      <c r="H233" s="4" t="s">
+        <v>767</v>
+      </c>
       <c r="I233" s="4" t="s">
         <v>726</v>
       </c>
@@ -14765,7 +14789,7 @@
         <v>701</v>
       </c>
       <c r="T233" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="234" spans="1:20" x14ac:dyDescent="0.2">

--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/house_model_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9664176A-026D-7640-9579-1BD60C2EC363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32669FF5-F00D-FD48-8777-A783A96FA398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5182" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5183" uniqueCount="772">
   <si>
     <t>State</t>
   </si>
@@ -2386,6 +2386,9 @@
   </si>
   <si>
     <t>Kirkland, Kyle</t>
+  </si>
+  <si>
+    <t>Kurdian, Armen</t>
   </si>
 </sst>
 </file>
@@ -6486,6 +6489,9 @@
       <c r="H71" t="s">
         <v>81</v>
       </c>
+      <c r="I71" s="4" t="s">
+        <v>771</v>
+      </c>
       <c r="K71" t="s">
         <v>668</v>
       </c>
@@ -6508,7 +6514,7 @@
         <v>700</v>
       </c>
       <c r="T71" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.2">

--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/house_model_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AE04AB-1482-984E-BF7F-4BF0BEC9ED14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A44C07-6115-4541-B5C1-0B9C36F78032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5182" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5183" uniqueCount="773">
   <si>
     <t>State</t>
   </si>
@@ -2389,6 +2389,9 @@
   </si>
   <si>
     <t>uncontested</t>
+  </si>
+  <si>
+    <t>Vargas, Stephanie</t>
   </si>
 </sst>
 </file>
@@ -5631,6 +5634,9 @@
       <c r="H55" t="s">
         <v>66</v>
       </c>
+      <c r="I55" s="4" t="s">
+        <v>772</v>
+      </c>
       <c r="K55" t="s">
         <v>667</v>
       </c>
@@ -5653,7 +5659,7 @@
         <v>699</v>
       </c>
       <c r="T55" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.2">

--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/house_model_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A44C07-6115-4541-B5C1-0B9C36F78032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9275FCE5-5565-5148-8BD8-87F235C9B411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5183" uniqueCount="773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5186" uniqueCount="775">
   <si>
     <t>State</t>
   </si>
@@ -2392,6 +2392,12 @@
   </si>
   <si>
     <t>Vargas, Stephanie</t>
+  </si>
+  <si>
+    <t>Males, John</t>
+  </si>
+  <si>
+    <t>Hodge, Tessa</t>
   </si>
 </sst>
 </file>
@@ -4234,6 +4240,9 @@
         <f t="shared" si="0"/>
         <v>21.200000000000003</v>
       </c>
+      <c r="H29" t="s">
+        <v>40</v>
+      </c>
       <c r="K29" t="s">
         <v>667</v>
       </c>
@@ -5091,6 +5100,9 @@
         <f t="shared" si="0"/>
         <v>-10.9</v>
       </c>
+      <c r="H45" s="4" t="s">
+        <v>774</v>
+      </c>
       <c r="I45" t="s">
         <v>56</v>
       </c>
@@ -5116,7 +5128,7 @@
         <v>699</v>
       </c>
       <c r="T45" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.2">
@@ -5202,6 +5214,9 @@
       <c r="H47" t="s">
         <v>58</v>
       </c>
+      <c r="I47" s="4" t="s">
+        <v>773</v>
+      </c>
       <c r="K47" t="s">
         <v>667</v>
       </c>
@@ -5224,7 +5239,7 @@
         <v>699</v>
       </c>
       <c r="T47" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.2">

--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/house_model_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9275FCE5-5565-5148-8BD8-87F235C9B411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F15540-9198-0146-B0C5-5300E0757A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5186" uniqueCount="775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5188" uniqueCount="777">
   <si>
     <t>State</t>
   </si>
@@ -2398,6 +2398,12 @@
   </si>
   <si>
     <t>Hodge, Tessa</t>
+  </si>
+  <si>
+    <t>Vo, Chuong</t>
+  </si>
+  <si>
+    <t>Tandon, Ritesh</t>
   </si>
 </sst>
 </file>
@@ -4779,6 +4785,9 @@
       <c r="H39" t="s">
         <v>50</v>
       </c>
+      <c r="I39" s="4" t="s">
+        <v>776</v>
+      </c>
       <c r="K39" t="s">
         <v>667</v>
       </c>
@@ -4801,7 +4810,7 @@
         <v>699</v>
       </c>
       <c r="T39" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.2">
@@ -6292,6 +6301,9 @@
       <c r="H67" t="s">
         <v>77</v>
       </c>
+      <c r="I67" s="4" t="s">
+        <v>775</v>
+      </c>
       <c r="K67" t="s">
         <v>667</v>
       </c>
@@ -6314,7 +6326,7 @@
         <v>699</v>
       </c>
       <c r="T67" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.2">

--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/house_model_python/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/Desktop - Ben’s MacBook Air/house_model_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F15540-9198-0146-B0C5-5300E0757A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9AD5E4-A0A7-CA4B-BD2B-352BB6CFB6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5188" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5228" uniqueCount="808">
   <si>
     <t>State</t>
   </si>
@@ -2404,6 +2404,99 @@
   </si>
   <si>
     <t>Tandon, Ritesh</t>
+  </si>
+  <si>
+    <t>Pino, Rosie</t>
+  </si>
+  <si>
+    <t>Fedorchak, Julie</t>
+  </si>
+  <si>
+    <t>Hammer, Trygve</t>
+  </si>
+  <si>
+    <t>Littau, Robin</t>
+  </si>
+  <si>
+    <t>Pan, Richard</t>
+  </si>
+  <si>
+    <t>Vang, Mai</t>
+  </si>
+  <si>
+    <t>Recile, Rudy</t>
+  </si>
+  <si>
+    <t>Villegas, Randy</t>
+  </si>
+  <si>
+    <t>Duenas, Angelica</t>
+  </si>
+  <si>
+    <t>Meyers, Scott</t>
+  </si>
+  <si>
+    <t>Gonzales-Torres, Angela</t>
+  </si>
+  <si>
+    <t>Brignano, Houston</t>
+  </si>
+  <si>
+    <t>Mota, Samantha</t>
+  </si>
+  <si>
+    <t>Kim, Young</t>
+  </si>
+  <si>
+    <t>R_vs_R</t>
+  </si>
+  <si>
+    <t>Burley, Brian</t>
+  </si>
+  <si>
+    <t>Bartie, Thurmond</t>
+  </si>
+  <si>
+    <t>Biggs, Sherri</t>
+  </si>
+  <si>
+    <t>Lehmacher, Eunice</t>
+  </si>
+  <si>
+    <t>McClain, Courtney</t>
+  </si>
+  <si>
+    <t>Dittmer, Mallory</t>
+  </si>
+  <si>
+    <t>Climer, Wes</t>
+  </si>
+  <si>
+    <t>Peterson, John</t>
+  </si>
+  <si>
+    <t>Vincent, John</t>
+  </si>
+  <si>
+    <t>Buck, Carrie</t>
+  </si>
+  <si>
+    <t>Flippo, David</t>
+  </si>
+  <si>
+    <t>Benitez-Thompson, Teresa</t>
+  </si>
+  <si>
+    <t>O'Donnell, Marty</t>
+  </si>
+  <si>
+    <t>Whipple, Cody</t>
+  </si>
+  <si>
+    <t>Russell, Ronald</t>
+  </si>
+  <si>
+    <t>LePage, Paul</t>
   </si>
 </sst>
 </file>
@@ -2839,15 +2932,15 @@
     <col min="7" max="7" width="30.1640625" style="3" customWidth="1"/>
     <col min="8" max="8" width="23.33203125" customWidth="1"/>
     <col min="9" max="10" width="24.1640625" customWidth="1"/>
-    <col min="11" max="11" width="13.6640625" customWidth="1"/>
-    <col min="12" max="12" width="18.6640625" customWidth="1"/>
-    <col min="13" max="13" width="28" customWidth="1"/>
-    <col min="14" max="14" width="21" customWidth="1"/>
-    <col min="15" max="15" width="29.1640625" customWidth="1"/>
-    <col min="16" max="16" width="19.5" customWidth="1"/>
-    <col min="17" max="17" width="21.33203125" customWidth="1"/>
-    <col min="18" max="18" width="23.83203125" customWidth="1"/>
-    <col min="19" max="19" width="16.1640625" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="18.6640625" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="28" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="21" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="29.1640625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="19.5" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="21.33203125" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="23.83203125" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="16.1640625" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="29.6640625" customWidth="1"/>
     <col min="21" max="21" width="22" customWidth="1"/>
     <col min="22" max="22" width="21.1640625" customWidth="1"/>
@@ -3985,6 +4078,9 @@
       <c r="H24" s="4" t="s">
         <v>37</v>
       </c>
+      <c r="I24" t="s">
+        <v>780</v>
+      </c>
       <c r="K24" t="s">
         <v>667</v>
       </c>
@@ -4197,6 +4293,12 @@
         <f t="shared" si="0"/>
         <v>16.700000000000003</v>
       </c>
+      <c r="H28" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="I28" t="s">
+        <v>744</v>
+      </c>
       <c r="K28" t="s">
         <v>667</v>
       </c>
@@ -4219,7 +4321,7 @@
         <v>699</v>
       </c>
       <c r="T28" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.2">
@@ -4249,6 +4351,9 @@
       <c r="H29" t="s">
         <v>40</v>
       </c>
+      <c r="J29" s="4" t="s">
+        <v>782</v>
+      </c>
       <c r="K29" t="s">
         <v>667</v>
       </c>
@@ -4271,7 +4376,7 @@
         <v>699</v>
       </c>
       <c r="T29" t="s">
-        <v>703</v>
+        <v>728</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.2">
@@ -4301,6 +4406,9 @@
       <c r="H30" t="s">
         <v>41</v>
       </c>
+      <c r="I30" s="4" t="s">
+        <v>783</v>
+      </c>
       <c r="K30" t="s">
         <v>667</v>
       </c>
@@ -4323,7 +4431,7 @@
         <v>699</v>
       </c>
       <c r="T30" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.2">
@@ -4596,7 +4704,7 @@
         <v>699</v>
       </c>
       <c r="T35" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.2">
@@ -4865,7 +4973,7 @@
         <v>699</v>
       </c>
       <c r="T40" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.2">
@@ -5057,6 +5165,9 @@
         <f t="shared" si="0"/>
         <v>6.6000000000000005</v>
       </c>
+      <c r="H44" s="4" t="s">
+        <v>784</v>
+      </c>
       <c r="I44" t="s">
         <v>55</v>
       </c>
@@ -5082,7 +5193,7 @@
         <v>699</v>
       </c>
       <c r="T44" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.2">
@@ -5444,6 +5555,9 @@
       <c r="H51" t="s">
         <v>62</v>
       </c>
+      <c r="J51" s="4" t="s">
+        <v>785</v>
+      </c>
       <c r="K51" t="s">
         <v>667</v>
       </c>
@@ -5466,7 +5580,7 @@
         <v>699</v>
       </c>
       <c r="T51" t="s">
-        <v>703</v>
+        <v>728</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.2">
@@ -5496,6 +5610,9 @@
       <c r="H52" t="s">
         <v>63</v>
       </c>
+      <c r="I52" s="4" t="s">
+        <v>786</v>
+      </c>
       <c r="K52" t="s">
         <v>667</v>
       </c>
@@ -5518,7 +5635,7 @@
         <v>699</v>
       </c>
       <c r="T52" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.2">
@@ -5710,6 +5827,12 @@
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
+      <c r="H56" t="s">
+        <v>67</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>787</v>
+      </c>
       <c r="K56" t="s">
         <v>667</v>
       </c>
@@ -5732,7 +5855,7 @@
         <v>699</v>
       </c>
       <c r="T56" t="s">
-        <v>703</v>
+        <v>728</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.2">
@@ -5818,6 +5941,9 @@
       <c r="H58" t="s">
         <v>69</v>
       </c>
+      <c r="I58" s="4" t="s">
+        <v>788</v>
+      </c>
       <c r="K58" t="s">
         <v>667</v>
       </c>
@@ -5840,7 +5966,7 @@
         <v>699</v>
       </c>
       <c r="T58" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.2">
@@ -5870,6 +5996,9 @@
       <c r="H59" t="s">
         <v>70</v>
       </c>
+      <c r="J59" s="4" t="s">
+        <v>789</v>
+      </c>
       <c r="K59" t="s">
         <v>667</v>
       </c>
@@ -5892,7 +6021,7 @@
         <v>699</v>
       </c>
       <c r="T59" t="s">
-        <v>703</v>
+        <v>728</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.2">
@@ -6034,6 +6163,9 @@
       <c r="I62" s="6" t="s">
         <v>758</v>
       </c>
+      <c r="J62" t="s">
+        <v>790</v>
+      </c>
       <c r="K62" t="s">
         <v>667</v>
       </c>
@@ -6056,7 +6188,7 @@
         <v>699</v>
       </c>
       <c r="T62" t="s">
-        <v>703</v>
+        <v>791</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.2">
@@ -6141,6 +6273,9 @@
       <c r="H64" t="s">
         <v>74</v>
       </c>
+      <c r="I64" s="4" t="s">
+        <v>792</v>
+      </c>
       <c r="K64" t="s">
         <v>667</v>
       </c>
@@ -6163,7 +6298,7 @@
         <v>699</v>
       </c>
       <c r="T64" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.2">
@@ -6271,7 +6406,7 @@
         <v>699</v>
       </c>
       <c r="T66" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.2">
@@ -6381,7 +6516,7 @@
         <v>699</v>
       </c>
       <c r="T68" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.2">
@@ -12226,6 +12361,12 @@
         <f t="shared" si="2"/>
         <v>30.200000000000003</v>
       </c>
+      <c r="H181" t="s">
+        <v>241</v>
+      </c>
+      <c r="I181" s="4" t="s">
+        <v>806</v>
+      </c>
       <c r="K181" t="s">
         <v>663</v>
       </c>
@@ -12275,6 +12416,9 @@
         <f t="shared" si="2"/>
         <v>-1.0999999999999996</v>
       </c>
+      <c r="I182" s="4" t="s">
+        <v>807</v>
+      </c>
       <c r="K182" t="s">
         <v>663</v>
       </c>
@@ -15077,6 +15221,12 @@
         <f t="shared" si="3"/>
         <v>10.7</v>
       </c>
+      <c r="H238" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="I238" s="4" t="s">
+        <v>801</v>
+      </c>
       <c r="K238" t="s">
         <v>666</v>
       </c>
@@ -15126,6 +15276,12 @@
         <f t="shared" si="3"/>
         <v>-5.6</v>
       </c>
+      <c r="H239" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="I239" s="4" t="s">
+        <v>802</v>
+      </c>
       <c r="K239" t="s">
         <v>666</v>
       </c>
@@ -15175,6 +15331,12 @@
         <f t="shared" si="3"/>
         <v>7.7</v>
       </c>
+      <c r="H240" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="I240" s="4" t="s">
+        <v>804</v>
+      </c>
       <c r="K240" t="s">
         <v>666</v>
       </c>
@@ -15224,6 +15386,12 @@
         <f t="shared" si="3"/>
         <v>11.2</v>
       </c>
+      <c r="H241" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="I241" s="4" t="s">
+        <v>805</v>
+      </c>
       <c r="K241" t="s">
         <v>666</v>
       </c>
@@ -15815,6 +15983,9 @@
       <c r="H252" t="s">
         <v>319</v>
       </c>
+      <c r="I252" s="4" t="s">
+        <v>777</v>
+      </c>
       <c r="K252" t="s">
         <v>676</v>
       </c>
@@ -18228,6 +18399,12 @@
         <f t="shared" si="4"/>
         <v>-28.4</v>
       </c>
+      <c r="H299" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="I299" t="s">
+        <v>778</v>
+      </c>
       <c r="K299" t="s">
         <v>679</v>
       </c>
@@ -20790,6 +20967,9 @@
         <f t="shared" si="5"/>
         <v>-5.6</v>
       </c>
+      <c r="I346" t="s">
+        <v>467</v>
+      </c>
       <c r="K346" t="s">
         <v>677</v>
       </c>
@@ -20839,6 +21019,12 @@
         <f t="shared" si="5"/>
         <v>-34.6</v>
       </c>
+      <c r="H347" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="I347" t="s">
+        <v>794</v>
+      </c>
       <c r="K347" t="s">
         <v>677</v>
       </c>
@@ -20888,6 +21074,12 @@
         <f t="shared" si="5"/>
         <v>-15.200000000000003</v>
       </c>
+      <c r="H348" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="I348" t="s">
+        <v>469</v>
+      </c>
       <c r="K348" t="s">
         <v>677</v>
       </c>
@@ -20937,6 +21129,12 @@
         <f t="shared" si="5"/>
         <v>-14.4</v>
       </c>
+      <c r="H349" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="I349" s="4" t="s">
+        <v>798</v>
+      </c>
       <c r="K349" t="s">
         <v>677</v>
       </c>
@@ -20986,6 +21184,12 @@
         <f t="shared" si="5"/>
         <v>31.200000000000003</v>
       </c>
+      <c r="H350" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="I350" s="4" t="s">
+        <v>799</v>
+      </c>
       <c r="K350" t="s">
         <v>677</v>
       </c>
@@ -21035,6 +21239,12 @@
         <f t="shared" si="5"/>
         <v>-18</v>
       </c>
+      <c r="H351" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="I351" t="s">
+        <v>472</v>
+      </c>
       <c r="K351" t="s">
         <v>677</v>
       </c>
@@ -22309,6 +22519,9 @@
       <c r="G375" s="3">
         <f t="shared" si="5"/>
         <v>-15.799999999999997</v>
+      </c>
+      <c r="H375" s="4" t="s">
+        <v>793</v>
       </c>
       <c r="I375" t="s">
         <v>513</v>

--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/Desktop - Ben’s MacBook Air/house_model_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9AD5E4-A0A7-CA4B-BD2B-352BB6CFB6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7186D49D-8394-1048-92BA-4B9524FE486A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5228" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5231" uniqueCount="811">
   <si>
     <t>State</t>
   </si>
@@ -2497,6 +2497,15 @@
   </si>
   <si>
     <t>LePage, Paul</t>
+  </si>
+  <si>
+    <t>Hernandez, Melissa</t>
+  </si>
+  <si>
+    <t>Morales, Cristian</t>
+  </si>
+  <si>
+    <t>Frese, Jeff</t>
   </si>
 </sst>
 </file>
@@ -4517,6 +4526,9 @@
       <c r="H32" t="s">
         <v>43</v>
       </c>
+      <c r="I32" s="4" t="s">
+        <v>810</v>
+      </c>
       <c r="K32" t="s">
         <v>667</v>
       </c>
@@ -4539,7 +4551,7 @@
         <v>699</v>
       </c>
       <c r="T32" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.2">
@@ -4734,6 +4746,9 @@
       <c r="H36" s="4" t="s">
         <v>750</v>
       </c>
+      <c r="J36" s="4" t="s">
+        <v>808</v>
+      </c>
       <c r="K36" t="s">
         <v>667</v>
       </c>
@@ -4756,7 +4771,7 @@
         <v>699</v>
       </c>
       <c r="T36" t="s">
-        <v>703</v>
+        <v>728</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.2">
@@ -6328,6 +6343,9 @@
       <c r="H65" t="s">
         <v>75</v>
       </c>
+      <c r="I65" s="4" t="s">
+        <v>809</v>
+      </c>
       <c r="K65" t="s">
         <v>667</v>
       </c>
@@ -6350,7 +6368,7 @@
         <v>699</v>
       </c>
       <c r="T65" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.2">
@@ -15953,7 +15971,7 @@
         <v>700</v>
       </c>
       <c r="T251" t="s">
-        <v>703</v>
+        <v>771</v>
       </c>
     </row>
     <row r="252" spans="1:20" x14ac:dyDescent="0.2">

--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/Desktop - Ben’s MacBook Air/house_model_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7186D49D-8394-1048-92BA-4B9524FE486A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC72F5D-FD50-0746-B296-9AD90F2E6958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5231" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5233" uniqueCount="813">
   <si>
     <t>State</t>
   </si>
@@ -2506,6 +2506,12 @@
   </si>
   <si>
     <t>Frese, Jeff</t>
+  </si>
+  <si>
+    <t>Jones, Eric</t>
+  </si>
+  <si>
+    <t>Soule, Peter</t>
   </si>
 </sst>
 </file>
@@ -4198,6 +4204,9 @@
       <c r="H26" s="6" t="s">
         <v>38</v>
       </c>
+      <c r="J26" s="4" t="s">
+        <v>811</v>
+      </c>
       <c r="K26" t="s">
         <v>667</v>
       </c>
@@ -4220,7 +4229,7 @@
         <v>699</v>
       </c>
       <c r="T26" t="s">
-        <v>703</v>
+        <v>728</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.2">
@@ -4856,6 +4865,9 @@
       <c r="H38" t="s">
         <v>49</v>
       </c>
+      <c r="I38" s="4" t="s">
+        <v>812</v>
+      </c>
       <c r="K38" t="s">
         <v>667</v>
       </c>
@@ -4878,7 +4890,7 @@
         <v>699</v>
       </c>
       <c r="T38" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.2">

--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/Desktop - Ben’s MacBook Air/house_model_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC72F5D-FD50-0746-B296-9AD90F2E6958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFB83BC-D5E4-E643-A459-12D3225096A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5233" uniqueCount="813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5246" uniqueCount="822">
   <si>
     <t>State</t>
   </si>
@@ -2512,6 +2512,33 @@
   </si>
   <si>
     <t>Soule, Peter</t>
+  </si>
+  <si>
+    <t>Cowan, John</t>
+  </si>
+  <si>
+    <t>Kozycki, Tony</t>
+  </si>
+  <si>
+    <t>Croisant, John</t>
+  </si>
+  <si>
+    <t>Wade, Brandon</t>
+  </si>
+  <si>
+    <t>Smith, Ceretta</t>
+  </si>
+  <si>
+    <t>Sneed, Andrew</t>
+  </si>
+  <si>
+    <t>Byrd, Suzie</t>
+  </si>
+  <si>
+    <t>Hollowell, Amanda</t>
+  </si>
+  <si>
+    <t>Jacob, Mitchell</t>
   </si>
 </sst>
 </file>
@@ -3043,15 +3070,16 @@
         <v>694</v>
       </c>
       <c r="E2" s="3">
-        <v>-55.1</v>
+        <f>31.2-67.5</f>
+        <v>-36.299999999999997</v>
       </c>
       <c r="F2" s="3">
-        <f>24.2-74.5</f>
-        <v>-50.3</v>
+        <f>34.4-64.6</f>
+        <v>-30.199999999999996</v>
       </c>
       <c r="G2" s="3">
-        <f t="shared" ref="G2:G65" si="0">E2+6.9+1.5</f>
-        <v>-46.7</v>
+        <f t="shared" ref="G2:G8" si="0">E2+6.9+1.5</f>
+        <v>-27.9</v>
       </c>
       <c r="K2" t="s">
         <v>674</v>
@@ -3080,15 +3108,16 @@
         <v>695</v>
       </c>
       <c r="E3" s="3">
-        <v>8.1999999999999993</v>
+        <f>40.8-58.1</f>
+        <v>-17.300000000000004</v>
       </c>
       <c r="F3" s="3">
-        <f>55.6-43.2</f>
-        <v>12.399999999999999</v>
+        <f>43.5-55.3</f>
+        <v>-11.799999999999997</v>
       </c>
       <c r="G3" s="3">
         <f t="shared" si="0"/>
-        <v>16.600000000000001</v>
+        <v>-8.9000000000000039</v>
       </c>
       <c r="K3" t="s">
         <v>674</v>
@@ -3117,15 +3146,16 @@
         <v>694</v>
       </c>
       <c r="E4" s="3">
-        <v>-46.5</v>
+        <f>26.5-72.4</f>
+        <v>-45.900000000000006</v>
       </c>
       <c r="F4" s="3">
-        <f>28.9-69.8</f>
-        <v>-40.9</v>
+        <f>29.3-69.4</f>
+        <v>-40.100000000000009</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" si="0"/>
-        <v>-38.1</v>
+        <v>-37.500000000000007</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>11</v>
@@ -3160,15 +3190,16 @@
         <v>694</v>
       </c>
       <c r="E5" s="3">
-        <v>-67.099999999999994</v>
+        <f>15.6-83.4</f>
+        <v>-67.800000000000011</v>
       </c>
       <c r="F5" s="3">
-        <f>18.4-80.4</f>
-        <v>-62.000000000000007</v>
+        <f>17.6-81.3</f>
+        <v>-63.699999999999996</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" si="0"/>
-        <v>-58.699999999999996</v>
+        <v>-59.400000000000013</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>13</v>
@@ -3203,15 +3234,22 @@
         <v>694</v>
       </c>
       <c r="E6" s="3">
-        <v>-29.8</v>
+        <f>34.6-63.6</f>
+        <v>-29</v>
       </c>
       <c r="F6" s="3">
-        <f>35.5-62.5</f>
-        <v>-27</v>
+        <f>35.4-62.5</f>
+        <v>-27.1</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
-        <v>-21.4</v>
+        <v>-20.6</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="I6" t="s">
+        <v>14</v>
       </c>
       <c r="K6" t="s">
         <v>674</v>
@@ -3240,18 +3278,16 @@
         <v>694</v>
       </c>
       <c r="E7" s="3">
-        <v>-38.799999999999997</v>
+        <f>31.6-66.6</f>
+        <v>-34.999999999999993</v>
       </c>
       <c r="F7" s="3">
-        <f>30.2-68.2</f>
-        <v>-38</v>
+        <f>31.8-66.4</f>
+        <v>-34.600000000000009</v>
       </c>
       <c r="G7" s="3">
         <f t="shared" si="0"/>
-        <v>-30.4</v>
-      </c>
-      <c r="I7" t="s">
-        <v>14</v>
+        <v>-26.599999999999994</v>
       </c>
       <c r="K7" t="s">
         <v>674</v>
@@ -3280,15 +3316,16 @@
         <v>695</v>
       </c>
       <c r="E8" s="3">
-        <v>23.9</v>
+        <f>61.9-37.1</f>
+        <v>24.799999999999997</v>
       </c>
       <c r="F8" s="3">
-        <f>63.9-34.9</f>
-        <v>29</v>
+        <f>64.7-34.4</f>
+        <v>30.300000000000004</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
-        <v>32.299999999999997</v>
+        <v>33.199999999999996</v>
       </c>
       <c r="K8" t="s">
         <v>674</v>
@@ -3324,7 +3361,7 @@
         <v>-10</v>
       </c>
       <c r="G9" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G2:G65" si="1">E9+6.9+1.5</f>
         <v>-4.6999999999999993</v>
       </c>
       <c r="K9" t="s">
@@ -3370,7 +3407,7 @@
         <v>1.5</v>
       </c>
       <c r="G10" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.3000000000000007</v>
       </c>
       <c r="K10" t="s">
@@ -3419,7 +3456,7 @@
         <v>-7.9000000000000057</v>
       </c>
       <c r="G11" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-6.5</v>
       </c>
       <c r="K11" t="s">
@@ -3468,7 +3505,7 @@
         <v>50.6</v>
       </c>
       <c r="G12" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="K12" t="s">
@@ -3517,7 +3554,7 @@
         <v>10.300000000000004</v>
       </c>
       <c r="G13" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15.7</v>
       </c>
       <c r="K13" t="s">
@@ -3566,7 +3603,7 @@
         <v>-16.399999999999999</v>
       </c>
       <c r="G14" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-11.499999999999998</v>
       </c>
       <c r="K14" t="s">
@@ -3615,7 +3652,7 @@
         <v>9.9999999999994316E-2</v>
       </c>
       <c r="G15" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.7</v>
       </c>
       <c r="K15" t="s">
@@ -3664,7 +3701,7 @@
         <v>32.699999999999996</v>
       </c>
       <c r="G16" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30.5</v>
       </c>
       <c r="K16" t="s">
@@ -3713,7 +3750,7 @@
         <v>-13.600000000000001</v>
       </c>
       <c r="G17" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-7.9</v>
       </c>
       <c r="K17" t="s">
@@ -3762,7 +3799,7 @@
         <v>-25.800000000000004</v>
       </c>
       <c r="G18" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-22.6</v>
       </c>
       <c r="K18" t="s">
@@ -3811,7 +3848,7 @@
         <v>-40.9</v>
       </c>
       <c r="G19" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-36.9</v>
       </c>
       <c r="H19" s="4" t="s">
@@ -3866,7 +3903,7 @@
         <v>-13.100000000000001</v>
       </c>
       <c r="G20" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-7.1999999999999993</v>
       </c>
       <c r="H20" s="4" t="s">
@@ -3921,7 +3958,7 @@
         <v>-23.400000000000006</v>
       </c>
       <c r="G21" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-16.5</v>
       </c>
       <c r="H21" s="4" t="s">
@@ -3976,7 +4013,7 @@
         <v>-35.200000000000003</v>
       </c>
       <c r="G22" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-31.5</v>
       </c>
       <c r="H22" s="4" t="s">
@@ -4031,7 +4068,7 @@
         <v>17.800000000000004</v>
       </c>
       <c r="G23" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20.6</v>
       </c>
       <c r="H23" s="4" t="s">
@@ -4087,7 +4124,7 @@
         <v>28.4</v>
       </c>
       <c r="G24" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>33</v>
       </c>
       <c r="H24" s="4" t="s">
@@ -4142,7 +4179,7 @@
         <v>14</v>
       </c>
       <c r="G25" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18.5</v>
       </c>
       <c r="H25" s="6" t="s">
@@ -4198,7 +4235,7 @@
         <v>21.1</v>
       </c>
       <c r="G26" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>22.9</v>
       </c>
       <c r="H26" s="6" t="s">
@@ -4253,7 +4290,7 @@
         <v>-14.5</v>
       </c>
       <c r="G27" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-12.200000000000001</v>
       </c>
       <c r="H27" s="4" t="s">
@@ -4308,7 +4345,7 @@
         <v>12.600000000000001</v>
       </c>
       <c r="G28" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16.700000000000003</v>
       </c>
       <c r="H28" s="4" t="s">
@@ -4363,7 +4400,7 @@
         <v>19.600000000000001</v>
       </c>
       <c r="G29" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>21.200000000000003</v>
       </c>
       <c r="H29" t="s">
@@ -4418,7 +4455,7 @@
         <v>42.6</v>
       </c>
       <c r="G30" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>42.4</v>
       </c>
       <c r="H30" t="s">
@@ -4473,7 +4510,7 @@
         <v>26.200000000000003</v>
       </c>
       <c r="G31" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>19.8</v>
       </c>
       <c r="H31" t="s">
@@ -4529,7 +4566,7 @@
         <v>38.6</v>
       </c>
       <c r="G32" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>41.9</v>
       </c>
       <c r="H32" t="s">
@@ -4584,7 +4621,7 @@
         <v>74.599999999999994</v>
       </c>
       <c r="G33" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>76.100000000000009</v>
       </c>
       <c r="H33" s="4" t="s">
@@ -4639,7 +4676,7 @@
         <v>80.7</v>
       </c>
       <c r="G34" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>82.2</v>
       </c>
       <c r="H34" t="s">
@@ -4694,7 +4731,7 @@
         <v>17.700000000000003</v>
       </c>
       <c r="G35" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="H35" t="s">
@@ -4749,7 +4786,7 @@
         <v>45.5</v>
       </c>
       <c r="G36" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>43.1</v>
       </c>
       <c r="H36" s="4" t="s">
@@ -4804,7 +4841,7 @@
         <v>57.300000000000004</v>
       </c>
       <c r="G37" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>56.199999999999996</v>
       </c>
       <c r="H37" t="s">
@@ -4859,7 +4896,7 @@
         <v>52.8</v>
       </c>
       <c r="G38" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>56.5</v>
       </c>
       <c r="H38" t="s">
@@ -4914,7 +4951,7 @@
         <v>48.199999999999996</v>
       </c>
       <c r="G39" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>47.3</v>
       </c>
       <c r="H39" t="s">
@@ -4969,7 +5006,7 @@
         <v>42.699999999999996</v>
       </c>
       <c r="G40" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>36.799999999999997</v>
       </c>
       <c r="H40" t="s">
@@ -5024,7 +5061,7 @@
         <v>39.6</v>
       </c>
       <c r="G41" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>42.699999999999996</v>
       </c>
       <c r="H41" t="s">
@@ -5079,7 +5116,7 @@
         <v>-26.200000000000003</v>
       </c>
       <c r="G42" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-23.800000000000004</v>
       </c>
       <c r="H42" s="4" t="s">
@@ -5134,7 +5171,7 @@
         <v>21.1</v>
       </c>
       <c r="G43" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14.4</v>
       </c>
       <c r="H43" t="s">
@@ -5189,7 +5226,7 @@
         <v>17</v>
       </c>
       <c r="G44" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.6000000000000005</v>
       </c>
       <c r="H44" s="4" t="s">
@@ -5244,7 +5281,7 @@
         <v>-12.100000000000001</v>
       </c>
       <c r="G45" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-10.9</v>
       </c>
       <c r="H45" s="4" t="s">
@@ -5299,7 +5336,7 @@
         <v>29</v>
       </c>
       <c r="G46" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>33.299999999999997</v>
       </c>
       <c r="H46" t="s">
@@ -5355,7 +5392,7 @@
         <v>16.5</v>
       </c>
       <c r="G47" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14.2</v>
       </c>
       <c r="H47" t="s">
@@ -5410,7 +5447,7 @@
         <v>22.400000000000006</v>
       </c>
       <c r="G48" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>23.6</v>
       </c>
       <c r="H48" s="4" t="s">
@@ -5465,7 +5502,7 @@
         <v>19.600000000000001</v>
       </c>
       <c r="G49" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18.100000000000001</v>
       </c>
       <c r="H49" t="s">
@@ -5521,7 +5558,7 @@
         <v>32.700000000000003</v>
       </c>
       <c r="G50" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>33.6</v>
       </c>
       <c r="H50" t="s">
@@ -5576,7 +5613,7 @@
         <v>49.900000000000006</v>
       </c>
       <c r="G51" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
       <c r="H51" t="s">
@@ -5631,7 +5668,7 @@
         <v>44.999999999999993</v>
       </c>
       <c r="G52" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>48.3</v>
       </c>
       <c r="H52" t="s">
@@ -5686,7 +5723,7 @@
         <v>25.1</v>
       </c>
       <c r="G53" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20.6</v>
       </c>
       <c r="H53" t="s">
@@ -5741,7 +5778,7 @@
         <v>33.700000000000003</v>
       </c>
       <c r="G54" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>33.4</v>
       </c>
       <c r="H54" t="s">
@@ -5796,7 +5833,7 @@
         <v>25.9</v>
       </c>
       <c r="G55" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18.200000000000003</v>
       </c>
       <c r="H55" t="s">
@@ -5851,7 +5888,7 @@
         <v>64.2</v>
       </c>
       <c r="G56" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>59</v>
       </c>
       <c r="H56" t="s">
@@ -5906,7 +5943,7 @@
         <v>23.5</v>
       </c>
       <c r="G57" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16.100000000000001</v>
       </c>
       <c r="H57" t="s">
@@ -5962,7 +5999,7 @@
         <v>44.1</v>
       </c>
       <c r="G58" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>47.4</v>
       </c>
       <c r="H58" t="s">
@@ -6017,7 +6054,7 @@
         <v>73.3</v>
       </c>
       <c r="G59" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>68.8</v>
       </c>
       <c r="H59" t="s">
@@ -6072,7 +6109,7 @@
         <v>28</v>
       </c>
       <c r="G60" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20.700000000000003</v>
       </c>
       <c r="H60" s="4" t="s">
@@ -6128,7 +6165,7 @@
         <v>26</v>
       </c>
       <c r="G61" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>17.899999999999999</v>
       </c>
       <c r="H61" t="s">
@@ -6184,7 +6221,7 @@
         <v>-7.6999999999999957</v>
       </c>
       <c r="G62" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-3.7999999999999989</v>
       </c>
       <c r="I62" s="6" t="s">
@@ -6239,7 +6276,7 @@
         <v>25.799999999999997</v>
       </c>
       <c r="G63" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>22.5</v>
       </c>
       <c r="H63" t="s">
@@ -6294,7 +6331,7 @@
         <v>19.700000000000003</v>
       </c>
       <c r="G64" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>21.5</v>
       </c>
       <c r="H64" t="s">
@@ -6349,7 +6386,7 @@
         <v>63.8</v>
       </c>
       <c r="G65" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>57.3</v>
       </c>
       <c r="H65" t="s">
@@ -6404,7 +6441,7 @@
         <v>53.100000000000009</v>
       </c>
       <c r="G66" s="3">
-        <f t="shared" ref="G66:G129" si="1">E66+6.9+1.5</f>
+        <f t="shared" ref="G66:G129" si="2">E66+6.9+1.5</f>
         <v>43.5</v>
       </c>
       <c r="H66" t="s">
@@ -6460,7 +6497,7 @@
         <v>10.100000000000001</v>
       </c>
       <c r="G67" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12.3</v>
       </c>
       <c r="H67" t="s">
@@ -6515,7 +6552,7 @@
         <v>28.200000000000003</v>
       </c>
       <c r="G68" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24.5</v>
       </c>
       <c r="H68" t="s">
@@ -6570,7 +6607,7 @@
         <v>16.100000000000001</v>
       </c>
       <c r="G69" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>18.399999999999999</v>
       </c>
       <c r="H69" t="s">
@@ -6625,7 +6662,7 @@
         <v>7.2000000000000028</v>
       </c>
       <c r="G70" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11.8</v>
       </c>
       <c r="H70" s="4" t="s">
@@ -6681,7 +6718,7 @@
         <v>15.200000000000003</v>
       </c>
       <c r="G71" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20.5</v>
       </c>
       <c r="H71" t="s">
@@ -6736,7 +6773,7 @@
         <v>21.099999999999994</v>
       </c>
       <c r="G72" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>26.6</v>
       </c>
       <c r="H72" t="s">
@@ -6791,7 +6828,7 @@
         <v>22.9</v>
       </c>
       <c r="G73" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>26.6</v>
       </c>
       <c r="H73" t="s">
@@ -6846,7 +6883,7 @@
         <v>33.299999999999997</v>
       </c>
       <c r="G74" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>25.9</v>
       </c>
       <c r="H74" t="s">
@@ -6901,7 +6938,7 @@
         <v>61.3</v>
       </c>
       <c r="G75" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>64.3</v>
       </c>
       <c r="K75" t="s">
@@ -6950,7 +6987,7 @@
         <v>39.900000000000006</v>
       </c>
       <c r="G76" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>48.199999999999996</v>
       </c>
       <c r="K76" t="s">
@@ -6999,7 +7036,7 @@
         <v>-8.1999999999999957</v>
       </c>
       <c r="G77" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.2999999999999989</v>
       </c>
       <c r="K77" t="s">
@@ -7048,7 +7085,7 @@
         <v>-18.5</v>
       </c>
       <c r="G78" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-9.9</v>
       </c>
       <c r="K78" t="s">
@@ -7097,7 +7134,7 @@
         <v>-10.100000000000001</v>
       </c>
       <c r="G79" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-0.69999999999999929</v>
       </c>
       <c r="K79" t="s">
@@ -7146,7 +7183,7 @@
         <v>23.800000000000004</v>
       </c>
       <c r="G80" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>28.200000000000003</v>
       </c>
       <c r="K80" t="s">
@@ -7195,7 +7232,7 @@
         <v>14.200000000000003</v>
       </c>
       <c r="G81" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>23.4</v>
       </c>
       <c r="K81" t="s">
@@ -7244,7 +7281,7 @@
         <v>4.5</v>
       </c>
       <c r="G82" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.6000000000000005</v>
       </c>
       <c r="K82" t="s">
@@ -7293,7 +7330,7 @@
         <v>28.099999999999994</v>
       </c>
       <c r="G83" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>31.299999999999997</v>
       </c>
       <c r="K83" t="s">
@@ -7342,7 +7379,7 @@
         <v>11.5</v>
       </c>
       <c r="G84" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16.100000000000001</v>
       </c>
       <c r="K84" t="s">
@@ -7391,7 +7428,7 @@
         <v>19.700000000000003</v>
       </c>
       <c r="G85" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>22.5</v>
       </c>
       <c r="K85" t="s">
@@ -7440,7 +7477,7 @@
         <v>31.200000000000003</v>
       </c>
       <c r="G86" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>31.799999999999997</v>
       </c>
       <c r="K86" t="s">
@@ -7489,7 +7526,7 @@
         <v>10.700000000000003</v>
       </c>
       <c r="G87" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="K87" t="s">
@@ -7538,7 +7575,7 @@
         <v>14.700000000000003</v>
       </c>
       <c r="G88" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>23.1</v>
       </c>
       <c r="K88" t="s">
@@ -7588,7 +7625,7 @@
         <v>-32.199999999999996</v>
       </c>
       <c r="G89" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-28.500000000000007</v>
       </c>
       <c r="K89" t="s">
@@ -7638,7 +7675,7 @@
         <v>-10.899999999999999</v>
       </c>
       <c r="G90" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-9.6</v>
       </c>
       <c r="K90" t="s">
@@ -7688,7 +7725,7 @@
         <v>-14</v>
       </c>
       <c r="G91" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-12.499999999999998</v>
       </c>
       <c r="K91" t="s">
@@ -7738,7 +7775,7 @@
         <v>-6.7000000000000028</v>
       </c>
       <c r="G92" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-3.4000000000000039</v>
       </c>
       <c r="K92" t="s">
@@ -7788,7 +7825,7 @@
         <v>-15.700000000000003</v>
       </c>
       <c r="G93" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-12.999999999999998</v>
       </c>
       <c r="K93" t="s">
@@ -7838,7 +7875,7 @@
         <v>-23.599999999999994</v>
       </c>
       <c r="G94" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-21.6</v>
       </c>
       <c r="K94" t="s">
@@ -7888,7 +7925,7 @@
         <v>-5.5</v>
       </c>
       <c r="G95" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-3.9999999999999982</v>
       </c>
       <c r="K95" t="s">
@@ -7938,7 +7975,7 @@
         <v>-10.700000000000003</v>
       </c>
       <c r="G96" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.699999999999994</v>
       </c>
       <c r="K96" t="s">
@@ -7988,7 +8025,7 @@
         <v>-6.7999999999999972</v>
       </c>
       <c r="G97" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-9.3000000000000025</v>
       </c>
       <c r="K97" t="s">
@@ -8038,7 +8075,7 @@
         <v>32.9</v>
       </c>
       <c r="G98" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>32.299999999999997</v>
       </c>
       <c r="K98" t="s">
@@ -8088,7 +8125,7 @@
         <v>-9.5999999999999943</v>
       </c>
       <c r="G99" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.3000000000000025</v>
       </c>
       <c r="K99" t="s">
@@ -8138,7 +8175,7 @@
         <v>-5.8000000000000043</v>
       </c>
       <c r="G100" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-6.8999999999999968</v>
       </c>
       <c r="K100" t="s">
@@ -8188,7 +8225,7 @@
         <v>-7.8000000000000043</v>
       </c>
       <c r="G101" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-5.3999999999999968</v>
       </c>
       <c r="K101" t="s">
@@ -8238,7 +8275,7 @@
         <v>-2.8000000000000043</v>
       </c>
       <c r="G102" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-2.0999999999999996</v>
       </c>
       <c r="K102" t="s">
@@ -8288,7 +8325,7 @@
         <v>-10.600000000000001</v>
       </c>
       <c r="G103" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-11.400000000000004</v>
       </c>
       <c r="K103" t="s">
@@ -8338,7 +8375,7 @@
         <v>-5.519999999999996</v>
       </c>
       <c r="G104" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-5.2000000000000011</v>
       </c>
       <c r="K104" t="s">
@@ -8388,7 +8425,7 @@
         <v>-13.899999999999999</v>
       </c>
       <c r="G105" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-13.6</v>
       </c>
       <c r="K105" t="s">
@@ -8438,7 +8475,7 @@
         <v>-10.100000000000001</v>
       </c>
       <c r="G106" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-8.4999999999999982</v>
       </c>
       <c r="K106" t="s">
@@ -8488,7 +8525,7 @@
         <v>-22</v>
       </c>
       <c r="G107" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-22.600000000000009</v>
       </c>
       <c r="K107" t="s">
@@ -8538,7 +8575,7 @@
         <v>48.2</v>
       </c>
       <c r="G108" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>45.400000000000006</v>
       </c>
       <c r="K108" t="s">
@@ -8588,7 +8625,7 @@
         <v>-8.7999999999999972</v>
       </c>
       <c r="G109" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.8000000000000025</v>
       </c>
       <c r="K109" t="s">
@@ -8638,7 +8675,7 @@
         <v>2.2000000000000028</v>
       </c>
       <c r="G110" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-2.0999999999999996</v>
       </c>
       <c r="K110" t="s">
@@ -8688,7 +8725,7 @@
         <v>26.6</v>
       </c>
       <c r="G111" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>22.199999999999996</v>
       </c>
       <c r="K111" t="s">
@@ -8738,7 +8775,7 @@
         <v>56.4</v>
       </c>
       <c r="G112" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>47</v>
       </c>
       <c r="K112" t="s">
@@ -8788,7 +8825,7 @@
         <v>5.1000000000000014</v>
       </c>
       <c r="G113" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-0.80000000000000249</v>
       </c>
       <c r="K113" t="s">
@@ -8838,7 +8875,7 @@
         <v>-1.1000000000000014</v>
       </c>
       <c r="G114" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-9.9000000000000039</v>
       </c>
       <c r="K114" t="s">
@@ -8888,7 +8925,7 @@
         <v>-0.20000000000000284</v>
       </c>
       <c r="G115" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-6.1</v>
       </c>
       <c r="K115" t="s">
@@ -8938,7 +8975,7 @@
         <v>-6.6000000000000014</v>
       </c>
       <c r="G116" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-17.000000000000007</v>
       </c>
       <c r="K116" t="s">
@@ -8987,8 +9024,11 @@
         <v>-13.399999999999999</v>
       </c>
       <c r="G117" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.2999999999999989</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>820</v>
       </c>
       <c r="K117" t="s">
         <v>677</v>
@@ -9012,7 +9052,7 @@
         <v>700</v>
       </c>
       <c r="T117" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="118" spans="1:20" x14ac:dyDescent="0.2">
@@ -9036,7 +9076,7 @@
         <v>10.300000000000004</v>
       </c>
       <c r="G118" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15.9</v>
       </c>
       <c r="H118" t="s">
@@ -9092,7 +9132,7 @@
         <v>-30.100000000000009</v>
       </c>
       <c r="G119" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-22.6</v>
       </c>
       <c r="H119" s="4" t="s">
@@ -9147,7 +9187,7 @@
         <v>57.699999999999996</v>
       </c>
       <c r="G120" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>60.6</v>
       </c>
       <c r="H120" t="s">
@@ -9203,7 +9243,7 @@
         <v>72.8</v>
       </c>
       <c r="G121" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>80.5</v>
       </c>
       <c r="H121" t="s">
@@ -9259,7 +9299,7 @@
         <v>49.5</v>
       </c>
       <c r="G122" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>58.4</v>
       </c>
       <c r="H122" t="s">
@@ -9311,8 +9351,11 @@
         <v>-19.199999999999996</v>
       </c>
       <c r="G123" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-12.700000000000001</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>814</v>
       </c>
       <c r="I123" s="6" t="s">
         <v>136</v>
@@ -9364,7 +9407,7 @@
         <v>-27.599999999999994</v>
       </c>
       <c r="G124" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-22.9</v>
       </c>
       <c r="H124" s="4" t="s">
@@ -9420,7 +9463,7 @@
         <v>-32.299999999999997</v>
       </c>
       <c r="G125" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-26.5</v>
       </c>
       <c r="H125" s="4" t="s">
@@ -9476,7 +9519,7 @@
         <v>-21.299999999999997</v>
       </c>
       <c r="G126" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-13.499999999999998</v>
       </c>
       <c r="I126" s="4" t="s">
@@ -9529,11 +9572,14 @@
         <v>-21.9</v>
       </c>
       <c r="G127" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-15.299999999999997</v>
       </c>
       <c r="H127" s="4" t="s">
         <v>144</v>
+      </c>
+      <c r="I127" s="4" t="s">
+        <v>813</v>
       </c>
       <c r="K127" t="s">
         <v>677</v>
@@ -9581,8 +9627,11 @@
         <v>-10.200000000000003</v>
       </c>
       <c r="G128" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-5.6999999999999993</v>
+      </c>
+      <c r="H128" s="4" t="s">
+        <v>817</v>
       </c>
       <c r="I128" t="s">
         <v>145</v>
@@ -9633,7 +9682,7 @@
         <v>40.5</v>
       </c>
       <c r="G129" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>50.8</v>
       </c>
       <c r="H129" s="4" t="s">
@@ -9689,7 +9738,7 @@
         <v>-37.499999999999993</v>
       </c>
       <c r="G130" s="3">
-        <f t="shared" ref="G130:G193" si="2">E130+6.9+1.5</f>
+        <f t="shared" ref="G130:G193" si="3">E130+6.9+1.5</f>
         <v>-29</v>
       </c>
       <c r="H130" s="4" t="s">
@@ -9744,7 +9793,7 @@
         <v>29.4</v>
       </c>
       <c r="G131" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>33.1</v>
       </c>
       <c r="K131" t="s">
@@ -9793,7 +9842,7 @@
         <v>29.5</v>
       </c>
       <c r="G132" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="K132" t="s">
@@ -9842,7 +9891,7 @@
         <v>-37.999999999999993</v>
       </c>
       <c r="G133" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-36.700000000000003</v>
       </c>
       <c r="H133" s="4" t="s">
@@ -9897,7 +9946,7 @@
         <v>-23.400000000000006</v>
       </c>
       <c r="G134" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-18.299999999999997</v>
       </c>
       <c r="H134" s="4" t="s">
@@ -9952,7 +10001,7 @@
         <v>42.4</v>
       </c>
       <c r="G135" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>40.4</v>
       </c>
       <c r="H135" s="6" t="s">
@@ -10008,7 +10057,7 @@
         <v>40</v>
       </c>
       <c r="G136" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>41.5</v>
       </c>
       <c r="H136" s="4" t="s">
@@ -10064,7 +10113,7 @@
         <v>41.400000000000006</v>
       </c>
       <c r="G137" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>39.6</v>
       </c>
       <c r="H137" s="6" t="s">
@@ -10120,7 +10169,7 @@
         <v>46.4</v>
       </c>
       <c r="G138" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>36.700000000000003</v>
       </c>
       <c r="H138" s="4" t="s">
@@ -10176,7 +10225,7 @@
         <v>39.799999999999997</v>
       </c>
       <c r="G139" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>45.6</v>
       </c>
       <c r="H139" s="6" t="s">
@@ -10232,7 +10281,7 @@
         <v>10.899999999999999</v>
       </c>
       <c r="G140" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>13.9</v>
       </c>
       <c r="H140" s="6" t="s">
@@ -10288,7 +10337,7 @@
         <v>72.8</v>
       </c>
       <c r="G141" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>73.900000000000006</v>
       </c>
       <c r="H141" s="4" t="s">
@@ -10344,7 +10393,7 @@
         <v>15.399999999999999</v>
       </c>
       <c r="G142" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>15.4</v>
       </c>
       <c r="H142" s="4" t="s">
@@ -10400,7 +10449,7 @@
         <v>41.3</v>
       </c>
       <c r="G143" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>44.9</v>
       </c>
       <c r="H143" s="4" t="s">
@@ -10456,7 +10505,7 @@
         <v>25.9</v>
       </c>
       <c r="G144" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>30.4</v>
       </c>
       <c r="H144" s="6" t="s">
@@ -10512,7 +10561,7 @@
         <v>15.300000000000004</v>
       </c>
       <c r="G145" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>19.8</v>
       </c>
       <c r="H145" s="6" t="s">
@@ -10568,7 +10617,7 @@
         <v>-42.8</v>
       </c>
       <c r="G146" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-35.1</v>
       </c>
       <c r="H146" s="4" t="s">
@@ -10623,7 +10672,7 @@
         <v>11.199999999999996</v>
       </c>
       <c r="G147" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>19.100000000000001</v>
       </c>
       <c r="H147" s="6" t="s">
@@ -10679,7 +10728,7 @@
         <v>11.400000000000006</v>
       </c>
       <c r="G148" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>13.600000000000001</v>
       </c>
       <c r="H148" s="6" t="s">
@@ -10735,7 +10784,7 @@
         <v>-38.699999999999996</v>
       </c>
       <c r="G149" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-31.5</v>
       </c>
       <c r="H149" s="4" t="s">
@@ -10791,7 +10840,7 @@
         <v>-21.5</v>
       </c>
       <c r="G150" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-14.299999999999999</v>
       </c>
       <c r="H150" s="4" t="s">
@@ -10847,7 +10896,7 @@
         <v>7.8000000000000043</v>
       </c>
       <c r="G151" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>13.2</v>
       </c>
       <c r="H151" t="s">
@@ -10903,7 +10952,7 @@
         <v>8.3999999999999986</v>
       </c>
       <c r="G152" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8.6999999999999993</v>
       </c>
       <c r="H152" t="s">
@@ -10959,7 +11008,7 @@
         <v>-22.6</v>
       </c>
       <c r="G153" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-18</v>
       </c>
       <c r="H153" s="4" t="s">
@@ -11015,7 +11064,7 @@
         <v>-29.9</v>
       </c>
       <c r="G154" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-23.200000000000003</v>
       </c>
       <c r="H154" s="4" t="s">
@@ -11071,7 +11120,7 @@
         <v>-29.1</v>
       </c>
       <c r="G155" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-21.299999999999997</v>
       </c>
       <c r="H155" s="4" t="s">
@@ -11127,7 +11176,7 @@
         <v>-16</v>
       </c>
       <c r="G156" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-8.2999999999999989</v>
       </c>
       <c r="H156" s="4" t="s">
@@ -11183,7 +11232,7 @@
         <v>-31.900000000000006</v>
       </c>
       <c r="G157" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-24.700000000000003</v>
       </c>
       <c r="H157" s="4" t="s">
@@ -11239,7 +11288,7 @@
         <v>42.4</v>
       </c>
       <c r="G158" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>49.8</v>
       </c>
       <c r="H158" s="6" t="s">
@@ -11295,7 +11344,7 @@
         <v>-32.799999999999997</v>
       </c>
       <c r="G159" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-28.1</v>
       </c>
       <c r="H159" s="4" t="s">
@@ -11351,7 +11400,7 @@
         <v>-27.4</v>
       </c>
       <c r="G160" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-22</v>
       </c>
       <c r="H160" s="4" t="s">
@@ -11407,7 +11456,7 @@
         <v>-2.8999999999999986</v>
       </c>
       <c r="G161" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-9.9999999999999645E-2</v>
       </c>
       <c r="H161" s="4" t="s">
@@ -11463,7 +11512,7 @@
         <v>-4.4000000000000057</v>
       </c>
       <c r="G162" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-1.5999999999999996</v>
       </c>
       <c r="H162" s="4" t="s">
@@ -11519,7 +11568,7 @@
         <v>-0.40000000000000568</v>
       </c>
       <c r="G163" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="H163" s="4" t="s">
@@ -11575,7 +11624,7 @@
         <v>-25.9</v>
       </c>
       <c r="G164" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-23.1</v>
       </c>
       <c r="H164" s="4" t="s">
@@ -11631,7 +11680,7 @@
         <v>-29.6</v>
       </c>
       <c r="G165" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-22.9</v>
       </c>
       <c r="K165" t="s">
@@ -11680,7 +11729,7 @@
         <v>-16.299999999999997</v>
       </c>
       <c r="G166" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-11.299999999999999</v>
       </c>
       <c r="K166" t="s">
@@ -11729,7 +11778,7 @@
         <v>4.5</v>
       </c>
       <c r="G167" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12.5</v>
       </c>
       <c r="K167" t="s">
@@ -11778,7 +11827,7 @@
         <v>-21.700000000000003</v>
       </c>
       <c r="G168" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-14.899999999999999</v>
       </c>
       <c r="K168" t="s">
@@ -11827,7 +11876,7 @@
         <v>-42.699999999999996</v>
       </c>
       <c r="G169" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-38.9</v>
       </c>
       <c r="H169" s="4" t="s">
@@ -11882,7 +11931,7 @@
         <v>-36.500000000000007</v>
       </c>
       <c r="G170" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-32.9</v>
       </c>
       <c r="H170" s="4" t="s">
@@ -11937,7 +11986,7 @@
         <v>22.300000000000004</v>
       </c>
       <c r="G171" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>27.299999999999997</v>
       </c>
       <c r="H171" t="s">
@@ -11993,7 +12042,7 @@
         <v>-32.700000000000003</v>
       </c>
       <c r="G172" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-27.1</v>
       </c>
       <c r="H172" s="4" t="s">
@@ -12049,7 +12098,7 @@
         <v>-59.3</v>
       </c>
       <c r="G173" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-55.5</v>
       </c>
       <c r="H173" s="4" t="s">
@@ -12104,7 +12153,7 @@
         <v>-11</v>
       </c>
       <c r="G174" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-6.6</v>
       </c>
       <c r="H174" s="4" t="s">
@@ -12161,7 +12210,7 @@
         <v>-39.200000000000003</v>
       </c>
       <c r="G175" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-30</v>
       </c>
       <c r="K175" t="s">
@@ -12199,7 +12248,7 @@
         <v>52.3</v>
       </c>
       <c r="G176" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>56.099999999999994</v>
       </c>
       <c r="K176" t="s">
@@ -12237,7 +12286,7 @@
         <v>-32.299999999999997</v>
       </c>
       <c r="G177" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-27.800000000000004</v>
       </c>
       <c r="K177" t="s">
@@ -12275,7 +12324,7 @@
         <v>-29.900000000000006</v>
       </c>
       <c r="G178" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-25.800000000000004</v>
       </c>
       <c r="K178" t="s">
@@ -12313,7 +12362,7 @@
         <v>-29</v>
       </c>
       <c r="G179" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-25.600000000000009</v>
       </c>
       <c r="K179" t="s">
@@ -12351,7 +12400,7 @@
         <v>-32.099999999999994</v>
       </c>
       <c r="G180" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-23.4</v>
       </c>
       <c r="K180" t="s">
@@ -12388,7 +12437,7 @@
         <v>22.799999999999997</v>
       </c>
       <c r="G181" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>30.200000000000003</v>
       </c>
       <c r="H181" t="s">
@@ -12443,7 +12492,7 @@
         <v>-6.1000000000000014</v>
       </c>
       <c r="G182" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-1.0999999999999996</v>
       </c>
       <c r="I182" s="4" t="s">
@@ -12495,7 +12544,7 @@
         <v>-14.399999999999999</v>
       </c>
       <c r="G183" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-8.4</v>
       </c>
       <c r="K183" t="s">
@@ -12544,7 +12593,7 @@
         <v>20.6</v>
       </c>
       <c r="G184" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>26.700000000000003</v>
       </c>
       <c r="K184" t="s">
@@ -12593,7 +12642,7 @@
         <v>25.300000000000004</v>
       </c>
       <c r="G185" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>31.9</v>
       </c>
       <c r="K185" t="s">
@@ -12642,7 +12691,7 @@
         <v>80.600000000000009</v>
       </c>
       <c r="G186" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>81.600000000000009</v>
       </c>
       <c r="K186" t="s">
@@ -12691,7 +12740,7 @@
         <v>36.299999999999997</v>
       </c>
       <c r="G187" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>41.5</v>
       </c>
       <c r="K187" t="s">
@@ -12740,7 +12789,7 @@
         <v>9.8000000000000043</v>
       </c>
       <c r="G188" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>14.100000000000001</v>
       </c>
       <c r="K188" t="s">
@@ -12789,7 +12838,7 @@
         <v>63.1</v>
       </c>
       <c r="G189" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>67</v>
       </c>
       <c r="K189" t="s">
@@ -12838,7 +12887,7 @@
         <v>62.100000000000009</v>
       </c>
       <c r="G190" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>64.199999999999989</v>
       </c>
       <c r="K190" t="s">
@@ -12887,7 +12936,7 @@
         <v>21.6</v>
       </c>
       <c r="G191" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>22.200000000000003</v>
       </c>
       <c r="K191" t="s">
@@ -12936,7 +12985,7 @@
         <v>30.700000000000003</v>
       </c>
       <c r="G192" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>32</v>
       </c>
       <c r="K192" t="s">
@@ -12985,7 +13034,7 @@
         <v>27.299999999999997</v>
       </c>
       <c r="G193" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>27.200000000000003</v>
       </c>
       <c r="K193" t="s">
@@ -13034,7 +13083,7 @@
         <v>28.299999999999997</v>
       </c>
       <c r="G194" s="3">
-        <f t="shared" ref="G194:G257" si="3">E194+6.9+1.5</f>
+        <f t="shared" ref="G194:G257" si="4">E194+6.9+1.5</f>
         <v>28</v>
       </c>
       <c r="K194" t="s">
@@ -13083,7 +13132,7 @@
         <v>50.900000000000006</v>
       </c>
       <c r="G195" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>53.3</v>
       </c>
       <c r="K195" t="s">
@@ -13132,7 +13181,7 @@
         <v>27.4</v>
       </c>
       <c r="G196" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
       <c r="K196" t="s">
@@ -13181,7 +13230,7 @@
         <v>72.2</v>
       </c>
       <c r="G197" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>71.100000000000009</v>
       </c>
       <c r="K197" t="s">
@@ -13230,7 +13279,7 @@
         <v>35.299999999999997</v>
       </c>
       <c r="G198" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>34.6</v>
       </c>
       <c r="K198" t="s">
@@ -13279,7 +13328,7 @@
         <v>18.100000000000001</v>
       </c>
       <c r="G199" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>19.100000000000001</v>
       </c>
       <c r="K199" t="s">
@@ -13328,7 +13377,7 @@
         <v>-19.800000000000004</v>
       </c>
       <c r="G200" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-12.799999999999999</v>
       </c>
       <c r="K200" t="s">
@@ -13377,7 +13426,7 @@
         <v>-28.200000000000003</v>
       </c>
       <c r="G201" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-21.5</v>
       </c>
       <c r="K201" t="s">
@@ -13426,7 +13475,7 @@
         <v>8.5</v>
       </c>
       <c r="G202" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16.2</v>
       </c>
       <c r="K202" t="s">
@@ -13475,7 +13524,7 @@
         <v>-4</v>
       </c>
       <c r="G203" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.7</v>
       </c>
       <c r="K203" t="s">
@@ -13524,7 +13573,7 @@
         <v>-24.1</v>
       </c>
       <c r="G204" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-18.700000000000003</v>
       </c>
       <c r="K204" t="s">
@@ -13573,7 +13622,7 @@
         <v>26.700000000000003</v>
       </c>
       <c r="G205" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>31.6</v>
       </c>
       <c r="K205" t="s">
@@ -13622,7 +13671,7 @@
         <v>0.89999999999999858</v>
       </c>
       <c r="G206" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.1000000000000005</v>
       </c>
       <c r="K206" t="s">
@@ -13671,7 +13720,7 @@
         <v>2.0999999999999943</v>
       </c>
       <c r="G207" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.4</v>
       </c>
       <c r="K207" t="s">
@@ -13720,7 +13769,7 @@
         <v>-29.4</v>
       </c>
       <c r="G208" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-23.9</v>
       </c>
       <c r="K208" t="s">
@@ -13769,7 +13818,7 @@
         <v>-1</v>
       </c>
       <c r="G209" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.9000000000000004</v>
       </c>
       <c r="K209" t="s">
@@ -13818,7 +13867,7 @@
         <v>19.899999999999999</v>
       </c>
       <c r="G210" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>24.5</v>
       </c>
       <c r="K210" t="s">
@@ -13867,7 +13916,7 @@
         <v>48.5</v>
       </c>
       <c r="G211" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>46.1</v>
       </c>
       <c r="K211" t="s">
@@ -13916,7 +13965,7 @@
         <v>49.6</v>
       </c>
       <c r="G212" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>49.8</v>
       </c>
       <c r="K212" t="s">
@@ -13965,7 +14014,7 @@
         <v>-9.1999999999999957</v>
       </c>
       <c r="G213" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-3.5999999999999996</v>
       </c>
       <c r="K213" t="s">
@@ -14014,7 +14063,7 @@
         <v>7.1999999999999957</v>
       </c>
       <c r="G214" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>14.2</v>
       </c>
       <c r="K214" t="s">
@@ -14063,7 +14112,7 @@
         <v>20.9</v>
       </c>
       <c r="G215" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29.700000000000003</v>
       </c>
       <c r="K215" t="s">
@@ -14112,7 +14161,7 @@
         <v>37.499999999999993</v>
       </c>
       <c r="G216" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>44.1</v>
       </c>
       <c r="K216" t="s">
@@ -14161,7 +14210,7 @@
         <v>62.9</v>
       </c>
       <c r="G217" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>70.3</v>
       </c>
       <c r="K217" t="s">
@@ -14210,7 +14259,7 @@
         <v>-17.600000000000001</v>
       </c>
       <c r="G218" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-11.299999999999999</v>
       </c>
       <c r="K218" t="s">
@@ -14259,7 +14308,7 @@
         <v>-33.199999999999996</v>
       </c>
       <c r="G219" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-28.1</v>
       </c>
       <c r="K219" t="s">
@@ -14308,7 +14357,7 @@
         <v>-11.200000000000003</v>
       </c>
       <c r="G220" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-5.9</v>
       </c>
       <c r="K220" t="s">
@@ -14357,7 +14406,7 @@
         <v>-31.699999999999996</v>
       </c>
       <c r="G221" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-28.6</v>
       </c>
       <c r="H221" s="4" t="s">
@@ -14412,7 +14461,7 @@
         <v>26.1</v>
       </c>
       <c r="G222" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>28.799999999999997</v>
       </c>
       <c r="H222" t="s">
@@ -14468,7 +14517,7 @@
         <v>-24.299999999999997</v>
       </c>
       <c r="G223" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-20.799999999999997</v>
       </c>
       <c r="H223" s="4" t="s">
@@ -14523,7 +14572,7 @@
         <v>-37.900000000000006</v>
       </c>
       <c r="G224" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-34.1</v>
       </c>
       <c r="H224" s="4" t="s">
@@ -14578,7 +14627,7 @@
         <v>58.8</v>
       </c>
       <c r="G225" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>65.900000000000006</v>
       </c>
       <c r="K225" t="s">
@@ -14627,7 +14676,7 @@
         <v>-11.100000000000001</v>
       </c>
       <c r="G226" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-2.9000000000000004</v>
       </c>
       <c r="K226" t="s">
@@ -14676,7 +14725,7 @@
         <v>-18.400000000000006</v>
       </c>
       <c r="G227" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-11.499999999999998</v>
       </c>
       <c r="K227" t="s">
@@ -14725,7 +14774,7 @@
         <v>-18.799999999999997</v>
       </c>
       <c r="G228" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-12.6</v>
       </c>
       <c r="K228" t="s">
@@ -14774,7 +14823,7 @@
         <v>-14.200000000000003</v>
       </c>
       <c r="G229" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-9.9</v>
       </c>
       <c r="K229" t="s">
@@ -14823,7 +14872,7 @@
         <v>-24.799999999999997</v>
       </c>
       <c r="G230" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-18.200000000000003</v>
       </c>
       <c r="K230" t="s">
@@ -14872,7 +14921,7 @@
         <v>-41.4</v>
       </c>
       <c r="G231" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-34.200000000000003</v>
       </c>
       <c r="K231" t="s">
@@ -14921,7 +14970,7 @@
         <v>-51.300000000000004</v>
       </c>
       <c r="G232" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-45.4</v>
       </c>
       <c r="K232" t="s">
@@ -14970,7 +15019,7 @@
         <v>-7.2000000000000028</v>
       </c>
       <c r="G233" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-3.0999999999999996</v>
       </c>
       <c r="H233" s="4" t="s">
@@ -15026,7 +15075,7 @@
         <v>-26.900000000000006</v>
       </c>
       <c r="G234" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-21.1</v>
       </c>
       <c r="H234" s="4" t="s">
@@ -15082,7 +15131,7 @@
         <v>-11</v>
       </c>
       <c r="G235" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-4.6999999999999993</v>
       </c>
       <c r="H235" s="4" t="s">
@@ -15137,7 +15186,7 @@
         <v>6.4000000000000057</v>
       </c>
       <c r="G236" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="H236" s="4" t="s">
@@ -15193,7 +15242,7 @@
         <v>-51.800000000000004</v>
       </c>
       <c r="G237" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-45.4</v>
       </c>
       <c r="H237" s="4" t="s">
@@ -15248,7 +15297,7 @@
         <v>8.5</v>
       </c>
       <c r="G238" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10.7</v>
       </c>
       <c r="H238" s="6" t="s">
@@ -15303,7 +15352,7 @@
         <v>-11</v>
       </c>
       <c r="G239" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-5.6</v>
       </c>
       <c r="H239" s="4" t="s">
@@ -15358,7 +15407,7 @@
         <v>6.6999999999999957</v>
       </c>
       <c r="G240" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.7</v>
       </c>
       <c r="H240" s="6" t="s">
@@ -15413,7 +15462,7 @@
         <v>8.2000000000000028</v>
       </c>
       <c r="G241" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>11.2</v>
       </c>
       <c r="H241" s="6" t="s">
@@ -15468,7 +15517,7 @@
         <v>6</v>
       </c>
       <c r="G242" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10.4</v>
       </c>
       <c r="K242" t="s">
@@ -15517,7 +15566,7 @@
         <v>8.8999999999999986</v>
       </c>
       <c r="G243" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="K243" t="s">
@@ -15566,7 +15615,7 @@
         <v>24.4</v>
       </c>
       <c r="G244" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>27.1</v>
       </c>
       <c r="H244" t="s">
@@ -15622,7 +15671,7 @@
         <v>-5</v>
       </c>
       <c r="G245" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-4.1999999999999993</v>
       </c>
       <c r="H245" s="4" t="s">
@@ -15677,7 +15726,7 @@
         <v>14.100000000000001</v>
       </c>
       <c r="G246" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16.8</v>
       </c>
       <c r="H246" t="s">
@@ -15733,7 +15782,7 @@
         <v>-22.5</v>
       </c>
       <c r="G247" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-21.700000000000003</v>
       </c>
       <c r="H247" s="4" t="s">
@@ -15788,7 +15837,7 @@
         <v>12.399999999999999</v>
       </c>
       <c r="G248" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10.200000000000001</v>
       </c>
       <c r="H248" t="s">
@@ -15844,7 +15893,7 @@
         <v>19.700000000000003</v>
       </c>
       <c r="G249" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>14.8</v>
       </c>
       <c r="H249" s="6" t="s">
@@ -15900,7 +15949,7 @@
         <v>3.6000000000000014</v>
       </c>
       <c r="G250" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.2</v>
       </c>
       <c r="H250" s="4" t="s">
@@ -15955,7 +16004,7 @@
         <v>44.800000000000004</v>
       </c>
       <c r="G251" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>32.6</v>
       </c>
       <c r="H251" t="s">
@@ -16007,7 +16056,7 @@
         <v>19</v>
       </c>
       <c r="G252" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.3000000000000007</v>
       </c>
       <c r="H252" t="s">
@@ -16062,7 +16111,7 @@
         <v>62.600000000000009</v>
       </c>
       <c r="G253" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>59.199999999999996</v>
       </c>
       <c r="H253" t="s">
@@ -16118,7 +16167,7 @@
         <v>16.799999999999997</v>
       </c>
       <c r="G254" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.100000000000001</v>
       </c>
       <c r="H254" t="s">
@@ -16174,7 +16223,7 @@
         <v>34.299999999999997</v>
       </c>
       <c r="G255" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>32.299999999999997</v>
       </c>
       <c r="H255" s="4" t="s">
@@ -16230,7 +16279,7 @@
         <v>14.399999999999999</v>
       </c>
       <c r="G256" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>21.3</v>
       </c>
       <c r="K256" t="s">
@@ -16279,7 +16328,7 @@
         <v>5.8999999999999986</v>
       </c>
       <c r="G257" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.5</v>
       </c>
       <c r="K257" t="s">
@@ -16328,7 +16377,7 @@
         <v>10.699999999999996</v>
       </c>
       <c r="G258" s="3">
-        <f t="shared" ref="G258:G321" si="4">E258+6.9+1.5</f>
+        <f t="shared" ref="G258:G321" si="5">E258+6.9+1.5</f>
         <v>13.2</v>
       </c>
       <c r="K258" t="s">
@@ -16377,7 +16426,7 @@
         <v>-1.8000000000000043</v>
       </c>
       <c r="G259" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1.6999999999999993</v>
       </c>
       <c r="K259" t="s">
@@ -16426,7 +16475,7 @@
         <v>-2.3999999999999986</v>
       </c>
       <c r="G260" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-5.5</v>
       </c>
       <c r="K260" t="s">
@@ -16475,7 +16524,7 @@
         <v>11.299999999999997</v>
       </c>
       <c r="G261" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4.1000000000000005</v>
       </c>
       <c r="K261" t="s">
@@ -16524,7 +16573,7 @@
         <v>14.5</v>
       </c>
       <c r="G262" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.7000000000000011</v>
       </c>
       <c r="K262" t="s">
@@ -16573,7 +16622,7 @@
         <v>62.4</v>
       </c>
       <c r="G263" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>50.6</v>
       </c>
       <c r="K263" t="s">
@@ -16622,7 +16671,7 @@
         <v>29.299999999999997</v>
       </c>
       <c r="G264" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14.8</v>
       </c>
       <c r="K264" t="s">
@@ -16671,7 +16720,7 @@
         <v>60.100000000000009</v>
       </c>
       <c r="G265" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>54.3</v>
       </c>
       <c r="K265" t="s">
@@ -16720,7 +16769,7 @@
         <v>55.400000000000006</v>
       </c>
       <c r="G266" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>52.4</v>
       </c>
       <c r="K266" t="s">
@@ -16769,7 +16818,7 @@
         <v>52.099999999999994</v>
       </c>
       <c r="G267" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>49</v>
       </c>
       <c r="K267" t="s">
@@ -16818,7 +16867,7 @@
         <v>70.400000000000006</v>
       </c>
       <c r="G268" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>68.8</v>
       </c>
       <c r="K268" t="s">
@@ -16867,7 +16916,7 @@
         <v>-7.6000000000000014</v>
       </c>
       <c r="G269" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-16</v>
       </c>
       <c r="K269" t="s">
@@ -16916,7 +16965,7 @@
         <v>71.099999999999994</v>
       </c>
       <c r="G270" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>72</v>
       </c>
       <c r="K270" t="s">
@@ -16965,7 +17014,7 @@
         <v>76.900000000000006</v>
       </c>
       <c r="G271" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>67.7</v>
       </c>
       <c r="K271" t="s">
@@ -17014,7 +17063,7 @@
         <v>55</v>
       </c>
       <c r="G272" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>40.200000000000003</v>
       </c>
       <c r="K272" t="s">
@@ -17063,7 +17112,7 @@
         <v>70.399999999999991</v>
       </c>
       <c r="G273" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>56.699999999999996</v>
       </c>
       <c r="K273" t="s">
@@ -17112,7 +17161,7 @@
         <v>44.599999999999994</v>
       </c>
       <c r="G274" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>41.5</v>
       </c>
       <c r="K274" t="s">
@@ -17161,7 +17210,7 @@
         <v>10.100000000000001</v>
       </c>
       <c r="G275" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="K275" t="s">
@@ -17210,7 +17259,7 @@
         <v>9.1000000000000014</v>
       </c>
       <c r="G276" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11.7</v>
       </c>
       <c r="K276" t="s">
@@ -17259,7 +17308,7 @@
         <v>4.3999999999999986</v>
       </c>
       <c r="G277" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.200000000000001</v>
       </c>
       <c r="K277" t="s">
@@ -17309,7 +17358,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="G278" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>22.6</v>
       </c>
       <c r="K278" t="s">
@@ -17358,7 +17407,7 @@
         <v>-15.699999999999996</v>
       </c>
       <c r="G279" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-12.299999999999999</v>
       </c>
       <c r="K279" t="s">
@@ -17407,7 +17456,7 @@
         <v>11.299999999999997</v>
       </c>
       <c r="G280" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>16.100000000000001</v>
       </c>
       <c r="K280" t="s">
@@ -17456,7 +17505,7 @@
         <v>-18.100000000000001</v>
       </c>
       <c r="G281" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-12.6</v>
       </c>
       <c r="K281" t="s">
@@ -17505,7 +17554,7 @@
         <v>-20.199999999999996</v>
       </c>
       <c r="G282" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-14.700000000000003</v>
       </c>
       <c r="K282" t="s">
@@ -17554,7 +17603,7 @@
         <v>20.5</v>
       </c>
       <c r="G283" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>26.799999999999997</v>
       </c>
       <c r="K283" t="s">
@@ -17603,7 +17652,7 @@
         <v>25.1</v>
       </c>
       <c r="G284" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>27.700000000000003</v>
       </c>
       <c r="K284" t="s">
@@ -17652,7 +17701,7 @@
         <v>-6.8999999999999986</v>
       </c>
       <c r="G285" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-3.1999999999999993</v>
       </c>
       <c r="H285" t="s">
@@ -17708,7 +17757,7 @@
         <v>35.300000000000004</v>
       </c>
       <c r="G286" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>42.699999999999996</v>
       </c>
       <c r="H286" t="s">
@@ -17764,7 +17813,7 @@
         <v>-8.2999999999999972</v>
       </c>
       <c r="G287" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-5.1999999999999993</v>
       </c>
       <c r="H287" s="4" t="s">
@@ -17819,7 +17868,7 @@
         <v>46</v>
       </c>
       <c r="G288" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>53.699999999999996</v>
       </c>
       <c r="H288" s="6" t="s">
@@ -17875,7 +17924,7 @@
         <v>-15.399999999999999</v>
       </c>
       <c r="G289" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-9.4</v>
       </c>
       <c r="H289" s="4" t="s">
@@ -17930,7 +17979,7 @@
         <v>-16.299999999999997</v>
       </c>
       <c r="G290" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-8.6</v>
       </c>
       <c r="H290" s="4" t="s">
@@ -17985,7 +18034,7 @@
         <v>-11</v>
       </c>
       <c r="G291" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-5.4</v>
       </c>
       <c r="H291" s="4" t="s">
@@ -18040,7 +18089,7 @@
         <v>-17.700000000000003</v>
       </c>
       <c r="G292" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-11.200000000000001</v>
       </c>
       <c r="H292" s="4" t="s">
@@ -18095,7 +18144,7 @@
         <v>-13.800000000000004</v>
       </c>
       <c r="G293" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-7.4</v>
       </c>
       <c r="H293" s="4" t="s">
@@ -18150,7 +18199,7 @@
         <v>-16</v>
       </c>
       <c r="G294" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-9.2999999999999989</v>
       </c>
       <c r="H294" s="4" t="s">
@@ -18205,7 +18254,7 @@
         <v>-11</v>
       </c>
       <c r="G295" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1.0999999999999996</v>
       </c>
       <c r="H295" s="4" t="s">
@@ -18260,7 +18309,7 @@
         <v>49.999999999999993</v>
       </c>
       <c r="G296" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>54.6</v>
       </c>
       <c r="H296" s="6" t="s">
@@ -18316,7 +18365,7 @@
         <v>-17.199999999999996</v>
       </c>
       <c r="G297" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-8.4</v>
       </c>
       <c r="H297" s="4" t="s">
@@ -18371,7 +18420,7 @@
         <v>-16.100000000000001</v>
       </c>
       <c r="G298" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-6.6999999999999993</v>
       </c>
       <c r="H298" s="4" t="s">
@@ -18426,7 +18475,7 @@
         <v>-33.299999999999997</v>
       </c>
       <c r="G299" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-28.4</v>
       </c>
       <c r="H299" s="4" t="s">
@@ -18481,7 +18530,7 @@
         <v>0.19999999999999574</v>
       </c>
       <c r="G300" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.9</v>
       </c>
       <c r="H300" s="6" t="s">
@@ -18537,7 +18586,7 @@
         <v>-39.599999999999994</v>
       </c>
       <c r="G301" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-33.700000000000003</v>
       </c>
       <c r="H301" s="4" t="s">
@@ -18593,7 +18642,7 @@
         <v>43.699999999999996</v>
       </c>
       <c r="G302" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>48.6</v>
       </c>
       <c r="H302" t="s">
@@ -18649,7 +18698,7 @@
         <v>-40.400000000000006</v>
       </c>
       <c r="G303" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-34.200000000000003</v>
       </c>
       <c r="H303" s="4" t="s">
@@ -18705,7 +18754,7 @@
         <v>-21.199999999999996</v>
       </c>
       <c r="G304" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-15.299999999999997</v>
       </c>
       <c r="H304" s="4" t="s">
@@ -18761,7 +18810,7 @@
         <v>-29.800000000000004</v>
       </c>
       <c r="G305" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-26.200000000000003</v>
       </c>
       <c r="H305" s="4" t="s">
@@ -18817,7 +18866,7 @@
         <v>-9.6000000000000014</v>
       </c>
       <c r="G306" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-2.5999999999999996</v>
       </c>
       <c r="H306" s="4" t="s">
@@ -18873,7 +18922,7 @@
         <v>-14.700000000000003</v>
       </c>
       <c r="G307" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-7.1999999999999993</v>
       </c>
       <c r="H307" s="4" t="s">
@@ -18929,7 +18978,7 @@
         <v>-6.7000000000000028</v>
       </c>
       <c r="G308" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-2.0999999999999996</v>
       </c>
       <c r="H308" t="s">
@@ -18985,7 +19034,7 @@
         <v>-5.8000000000000043</v>
       </c>
       <c r="G309" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.70000000000000018</v>
       </c>
       <c r="H309" s="4" t="s">
@@ -19041,7 +19090,7 @@
         <v>57.599999999999994</v>
       </c>
       <c r="G310" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>63.4</v>
       </c>
       <c r="H310" t="s">
@@ -19097,7 +19146,7 @@
         <v>-28.900000000000006</v>
       </c>
       <c r="G311" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-21.6</v>
       </c>
       <c r="H311" s="4" t="s">
@@ -19152,7 +19201,7 @@
         <v>5.9000000000000057</v>
       </c>
       <c r="G312" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11.600000000000001</v>
       </c>
       <c r="H312" t="s">
@@ -19208,7 +19257,7 @@
         <v>-17.100000000000001</v>
       </c>
       <c r="G313" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-11.9</v>
       </c>
       <c r="H313" s="4" t="s">
@@ -19263,7 +19312,7 @@
         <v>-7.3999999999999986</v>
       </c>
       <c r="G314" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1.5999999999999996</v>
       </c>
       <c r="H314" s="4" t="s">
@@ -19318,8 +19367,11 @@
         <v>-21.4</v>
       </c>
       <c r="G315" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-13.1</v>
+      </c>
+      <c r="H315" s="4" t="s">
+        <v>815</v>
       </c>
       <c r="K315" t="s">
         <v>679</v>
@@ -19367,8 +19419,14 @@
         <v>-53.4</v>
       </c>
       <c r="G316" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-47.2</v>
+      </c>
+      <c r="H316" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="I316" t="s">
+        <v>414</v>
       </c>
       <c r="K316" t="s">
         <v>679</v>
@@ -19416,8 +19474,14 @@
         <v>-42.8</v>
       </c>
       <c r="G317" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-36.4</v>
+      </c>
+      <c r="H317" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="I317" t="s">
+        <v>415</v>
       </c>
       <c r="K317" t="s">
         <v>679</v>
@@ -19465,8 +19529,14 @@
         <v>-30.900000000000006</v>
       </c>
       <c r="G318" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-24.5</v>
+      </c>
+      <c r="H318" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="I318" t="s">
+        <v>416</v>
       </c>
       <c r="K318" t="s">
         <v>679</v>
@@ -19514,8 +19584,11 @@
         <v>-18.399999999999999</v>
       </c>
       <c r="G319" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-9.7999999999999989</v>
+      </c>
+      <c r="I319" t="s">
+        <v>417</v>
       </c>
       <c r="K319" t="s">
         <v>679</v>
@@ -19563,7 +19636,7 @@
         <v>38.800000000000004</v>
       </c>
       <c r="G320" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>46</v>
       </c>
       <c r="H320" s="6" t="s">
@@ -19619,7 +19692,7 @@
         <v>-24.300000000000004</v>
       </c>
       <c r="G321" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-18.700000000000003</v>
       </c>
       <c r="H321" s="4" t="s">
@@ -19675,7 +19748,7 @@
         <v>47</v>
       </c>
       <c r="G322" s="3">
-        <f t="shared" ref="G322:G385" si="5">E322+6.9+1.5</f>
+        <f t="shared" ref="G322:G385" si="6">E322+6.9+1.5</f>
         <v>54</v>
       </c>
       <c r="H322" s="6" t="s">
@@ -19731,7 +19804,7 @@
         <v>12.700000000000003</v>
       </c>
       <c r="G323" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>20.399999999999999</v>
       </c>
       <c r="H323" s="6" t="s">
@@ -19787,7 +19860,7 @@
         <v>8.7999999999999972</v>
       </c>
       <c r="G324" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="H324" s="6" t="s">
@@ -19843,7 +19916,7 @@
         <v>13.099999999999994</v>
       </c>
       <c r="G325" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>19.700000000000003</v>
       </c>
       <c r="H325" s="6" t="s">
@@ -19899,7 +19972,7 @@
         <v>4.5999999999999943</v>
       </c>
       <c r="G326" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.6999999999999993</v>
       </c>
       <c r="H326" s="4" t="s">
@@ -19954,7 +20027,7 @@
         <v>42.7</v>
       </c>
       <c r="G327" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>44.1</v>
       </c>
       <c r="H327" t="s">
@@ -20010,7 +20083,7 @@
         <v>80.8</v>
       </c>
       <c r="G328" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>85.7</v>
       </c>
       <c r="H328" s="6" t="s">
@@ -20063,7 +20136,7 @@
         <v>18.899999999999999</v>
       </c>
       <c r="G329" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>24.200000000000003</v>
       </c>
       <c r="H329" t="s">
@@ -20119,7 +20192,7 @@
         <v>32.300000000000004</v>
       </c>
       <c r="G330" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>37</v>
       </c>
       <c r="H330" s="6" t="s">
@@ -20175,7 +20248,7 @@
         <v>14.799999999999997</v>
       </c>
       <c r="G331" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>19.8</v>
       </c>
       <c r="H331" t="s">
@@ -20231,7 +20304,7 @@
         <v>0.60000000000000142</v>
       </c>
       <c r="G332" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.2</v>
       </c>
       <c r="H332" s="4" t="s">
@@ -20287,7 +20360,7 @@
         <v>-2.8999999999999986</v>
       </c>
       <c r="G333" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-9.9999999999999645E-2</v>
       </c>
       <c r="H333" s="4" t="s">
@@ -20343,7 +20416,7 @@
         <v>-36.5</v>
       </c>
       <c r="G334" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-29.5</v>
       </c>
       <c r="H334" s="4" t="s">
@@ -20399,7 +20472,7 @@
         <v>-4.0999999999999943</v>
       </c>
       <c r="G335" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.2</v>
       </c>
       <c r="H335" s="4" t="s">
@@ -20455,7 +20528,7 @@
         <v>-21.299999999999997</v>
       </c>
       <c r="G336" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-12.999999999999998</v>
       </c>
       <c r="H336" s="4" t="s">
@@ -20511,7 +20584,7 @@
         <v>19.899999999999999</v>
       </c>
       <c r="G337" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>27.6</v>
       </c>
       <c r="H337" s="6" t="s">
@@ -20567,7 +20640,7 @@
         <v>-45.2</v>
       </c>
       <c r="G338" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-37.1</v>
       </c>
       <c r="H338" s="4" t="s">
@@ -20623,7 +20696,7 @@
         <v>-31.5</v>
       </c>
       <c r="G339" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-25</v>
       </c>
       <c r="H339" s="4" t="s">
@@ -20679,7 +20752,7 @@
         <v>-37</v>
       </c>
       <c r="G340" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-29.6</v>
       </c>
       <c r="H340" s="4" t="s">
@@ -20735,7 +20808,7 @@
         <v>-20.700000000000003</v>
       </c>
       <c r="G341" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-14.4</v>
       </c>
       <c r="H341" s="4" t="s">
@@ -20791,7 +20864,7 @@
         <v>5.7999999999999972</v>
       </c>
       <c r="G342" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>13.9</v>
       </c>
       <c r="H342" t="s">
@@ -20847,7 +20920,7 @@
         <v>29</v>
       </c>
       <c r="G343" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>30.4</v>
       </c>
       <c r="K343" t="s">
@@ -20896,7 +20969,7 @@
         <v>13.599999999999994</v>
       </c>
       <c r="G344" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>15.100000000000001</v>
       </c>
       <c r="K344" t="s">
@@ -20945,7 +21018,7 @@
         <v>-8.7000000000000028</v>
       </c>
       <c r="G345" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-4.6999999999999993</v>
       </c>
       <c r="K345" t="s">
@@ -20994,7 +21067,7 @@
         <v>-10.600000000000001</v>
       </c>
       <c r="G346" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-5.6</v>
       </c>
       <c r="I346" t="s">
@@ -21046,7 +21119,7 @@
         <v>-37.4</v>
       </c>
       <c r="G347" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-34.6</v>
       </c>
       <c r="H347" s="4" t="s">
@@ -21101,7 +21174,7 @@
         <v>-18.600000000000001</v>
       </c>
       <c r="G348" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-15.200000000000003</v>
       </c>
       <c r="H348" s="4" t="s">
@@ -21156,7 +21229,7 @@
         <v>-18.199999999999996</v>
       </c>
       <c r="G349" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-14.4</v>
       </c>
       <c r="H349" s="4" t="s">
@@ -21211,7 +21284,7 @@
         <v>32.099999999999994</v>
       </c>
       <c r="G350" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>31.200000000000003</v>
       </c>
       <c r="H350" s="6" t="s">
@@ -21266,7 +21339,7 @@
         <v>-18.599999999999994</v>
       </c>
       <c r="G351" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-18</v>
       </c>
       <c r="H351" s="4" t="s">
@@ -21321,7 +21394,7 @@
         <v>-26.199999999999996</v>
       </c>
       <c r="G352" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-20.799999999999997</v>
       </c>
       <c r="H352" s="4" t="s">
@@ -21378,7 +21451,7 @@
         <v>-54.3</v>
       </c>
       <c r="G353" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-49.400000000000006</v>
       </c>
       <c r="K353" t="s">
@@ -21428,7 +21501,7 @@
         <v>-29.300000000000004</v>
       </c>
       <c r="G354" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-25.400000000000006</v>
       </c>
       <c r="K354" t="s">
@@ -21478,7 +21551,7 @@
         <v>-31.700000000000003</v>
       </c>
       <c r="G355" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-27.300000000000004</v>
       </c>
       <c r="K355" t="s">
@@ -21528,7 +21601,7 @@
         <v>-15.399999999999999</v>
       </c>
       <c r="G356" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-15.500000000000007</v>
       </c>
       <c r="K356" t="s">
@@ -21578,7 +21651,7 @@
         <v>-12.700000000000003</v>
       </c>
       <c r="G357" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-14.700000000000003</v>
       </c>
       <c r="K357" t="s">
@@ -21628,7 +21701,7 @@
         <v>-20.100000000000001</v>
       </c>
       <c r="G358" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-18.100000000000001</v>
       </c>
       <c r="K358" t="s">
@@ -21678,7 +21751,7 @@
         <v>-18.100000000000001</v>
       </c>
       <c r="G359" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-13.999999999999998</v>
       </c>
       <c r="K359" t="s">
@@ -21728,7 +21801,7 @@
         <v>-15.700000000000003</v>
       </c>
       <c r="G360" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-11.799999999999995</v>
       </c>
       <c r="K360" t="s">
@@ -21778,7 +21851,7 @@
         <v>-10.5</v>
       </c>
       <c r="G361" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-12.700000000000001</v>
       </c>
       <c r="K361" t="s">
@@ -21827,7 +21900,7 @@
         <v>-43.8</v>
       </c>
       <c r="G362" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-41</v>
       </c>
       <c r="H362" s="4" t="s">
@@ -21882,7 +21955,7 @@
         <v>-21.5</v>
       </c>
       <c r="G363" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-14.4</v>
       </c>
       <c r="H363" s="4" t="s">
@@ -21938,7 +22011,7 @@
         <v>-17.399999999999999</v>
       </c>
       <c r="G364" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-14.899999999999999</v>
       </c>
       <c r="H364" s="4" t="s">
@@ -21993,7 +22066,7 @@
         <v>-17.900000000000006</v>
       </c>
       <c r="G365" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-16.200000000000003</v>
       </c>
       <c r="H365" s="4" t="s">
@@ -22048,7 +22121,7 @@
         <v>-16.200000000000003</v>
       </c>
       <c r="G366" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-13.1</v>
       </c>
       <c r="H366" s="4" t="s">
@@ -22103,7 +22176,7 @@
         <v>-19.5</v>
       </c>
       <c r="G367" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-14.4</v>
       </c>
       <c r="H367" s="4" t="s">
@@ -22158,7 +22231,7 @@
         <v>31.5</v>
       </c>
       <c r="G368" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>31.799999999999997</v>
       </c>
       <c r="H368" t="s">
@@ -22214,7 +22287,7 @@
         <v>-16.699999999999996</v>
       </c>
       <c r="G369" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-19.200000000000003</v>
       </c>
       <c r="H369" s="4" t="s">
@@ -22270,7 +22343,7 @@
         <v>-8.6000000000000014</v>
       </c>
       <c r="G370" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-11.4</v>
       </c>
       <c r="H370" s="4" t="s">
@@ -22326,7 +22399,7 @@
         <v>-14.799999999999997</v>
       </c>
       <c r="G371" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-14.1</v>
       </c>
       <c r="H371" s="4" t="s">
@@ -22382,7 +22455,7 @@
         <v>-30</v>
       </c>
       <c r="G372" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-25.9</v>
       </c>
       <c r="H372" s="4" t="s">
@@ -22437,7 +22510,7 @@
         <v>-17.700000000000003</v>
       </c>
       <c r="G373" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-15.399999999999999</v>
       </c>
       <c r="H373" s="4" t="s">
@@ -22492,7 +22565,7 @@
         <v>-44.1</v>
       </c>
       <c r="G374" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-37.700000000000003</v>
       </c>
       <c r="H374" s="4" t="s">
@@ -22547,7 +22620,7 @@
         <v>-21.5</v>
       </c>
       <c r="G375" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-15.799999999999997</v>
       </c>
       <c r="H375" s="4" t="s">
@@ -22602,7 +22675,7 @@
         <v>-2.4000000000000057</v>
       </c>
       <c r="G376" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-9.4</v>
       </c>
       <c r="H376" s="4" t="s">
@@ -22657,7 +22730,7 @@
         <v>35.6</v>
       </c>
       <c r="G377" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>24.700000000000003</v>
       </c>
       <c r="H377" t="s">
@@ -22714,7 +22787,7 @@
         <v>-15.200000000000003</v>
       </c>
       <c r="G378" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-9.6</v>
       </c>
       <c r="H378" s="4" t="s">
@@ -22769,7 +22842,7 @@
         <v>63.6</v>
       </c>
       <c r="G379" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>63.199999999999996</v>
       </c>
       <c r="H379" t="s">
@@ -22825,7 +22898,7 @@
         <v>-46.199999999999996</v>
       </c>
       <c r="G380" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-43.2</v>
       </c>
       <c r="H380" s="4" t="s">
@@ -22881,7 +22954,7 @@
         <v>40.199999999999996</v>
       </c>
       <c r="G381" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>36.799999999999997</v>
       </c>
       <c r="H381" t="s">
@@ -22937,7 +23010,7 @@
         <v>-16.700000000000003</v>
       </c>
       <c r="G382" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-13.4</v>
       </c>
       <c r="H382" s="4" t="s">
@@ -22993,7 +23066,7 @@
         <v>-17.199999999999996</v>
       </c>
       <c r="G383" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-13.700000000000001</v>
       </c>
       <c r="H383" s="4" t="s">
@@ -23049,7 +23122,7 @@
         <v>-7.1999999999999957</v>
       </c>
       <c r="G384" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-6.2999999999999989</v>
       </c>
       <c r="H384" s="4" t="s">
@@ -23105,7 +23178,7 @@
         <v>-12.399999999999999</v>
       </c>
       <c r="G385" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-7.6</v>
       </c>
       <c r="H385" s="4" t="s">
@@ -23160,7 +23233,7 @@
         <v>-15.800000000000004</v>
       </c>
       <c r="G386" s="3">
-        <f t="shared" ref="G386:G436" si="6">E386+6.9+1.5</f>
+        <f t="shared" ref="G386:G436" si="7">E386+6.9+1.5</f>
         <v>-15.600000000000001</v>
       </c>
       <c r="H386" s="4" t="s">
@@ -23215,7 +23288,7 @@
         <v>-18.5</v>
       </c>
       <c r="G387" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-15.299999999999997</v>
       </c>
       <c r="H387" s="4" t="s">
@@ -23270,7 +23343,7 @@
         <v>-17.199999999999996</v>
       </c>
       <c r="G388" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-12.700000000000001</v>
       </c>
       <c r="H388" s="4" t="s">
@@ -23325,7 +23398,7 @@
         <v>9.5999999999999943</v>
       </c>
       <c r="G389" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1.9000000000000004</v>
       </c>
       <c r="H389" t="s">
@@ -23381,7 +23454,7 @@
         <v>43.000000000000007</v>
       </c>
       <c r="G390" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>38.799999999999997</v>
       </c>
       <c r="H390" s="6" t="s">
@@ -23437,7 +23510,7 @@
         <v>56.8</v>
       </c>
       <c r="G391" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>49.1</v>
       </c>
       <c r="H391" s="4" t="s">
@@ -23493,7 +23566,7 @@
         <v>-17.699999999999996</v>
       </c>
       <c r="G392" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-13.4</v>
       </c>
       <c r="H392" s="4" t="s">
@@ -23548,7 +23621,7 @@
         <v>-10.099999999999994</v>
       </c>
       <c r="G393" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-9.2999999999999989</v>
       </c>
       <c r="H393" s="4" t="s">
@@ -23604,7 +23677,7 @@
         <v>44.900000000000006</v>
       </c>
       <c r="G394" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>40.9</v>
       </c>
       <c r="H394" s="4" t="s">
@@ -23660,7 +23733,7 @@
         <v>2.8999999999999986</v>
       </c>
       <c r="G395" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1.6999999999999993</v>
       </c>
       <c r="H395" t="s">
@@ -23716,7 +23789,7 @@
         <v>-1.9000000000000057</v>
       </c>
       <c r="G396" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2</v>
       </c>
       <c r="H396" s="4" t="s">
@@ -23772,7 +23845,7 @@
         <v>-18.399999999999999</v>
       </c>
       <c r="G397" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-16.5</v>
       </c>
       <c r="H397" s="4" t="s">
@@ -23827,7 +23900,7 @@
         <v>62.399999999999991</v>
       </c>
       <c r="G398" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>64.599999999999994</v>
       </c>
       <c r="H398" t="s">
@@ -23883,7 +23956,7 @@
         <v>-17.800000000000004</v>
       </c>
       <c r="G399" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-12.499999999999998</v>
       </c>
       <c r="H399" s="4" t="s">
@@ -23939,7 +24012,7 @@
         <v>24.6</v>
       </c>
       <c r="G400" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>32</v>
       </c>
       <c r="K400" t="s">
@@ -23988,7 +24061,7 @@
         <v>-30.4</v>
       </c>
       <c r="G401" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-20.5</v>
       </c>
       <c r="K401" t="s">
@@ -24037,7 +24110,7 @@
         <v>-40.700000000000003</v>
       </c>
       <c r="G402" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-32.9</v>
       </c>
       <c r="K402" t="s">
@@ -24086,7 +24159,7 @@
         <v>-33</v>
       </c>
       <c r="G403" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-24</v>
       </c>
       <c r="K403" t="s">
@@ -24135,7 +24208,7 @@
         <v>35.399999999999991</v>
       </c>
       <c r="G404" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>43.199999999999996</v>
       </c>
       <c r="K404" t="s">
@@ -24185,7 +24258,7 @@
         <v>-6.6999999999999957</v>
       </c>
       <c r="G405" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.5000000000000018</v>
       </c>
       <c r="K405" t="s">
@@ -24235,7 +24308,7 @@
         <v>2</v>
       </c>
       <c r="G406" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8.2000000000000046</v>
       </c>
       <c r="K406" t="s">
@@ -24285,7 +24358,7 @@
         <v>38.1</v>
       </c>
       <c r="G407" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>43.000000000000007</v>
       </c>
       <c r="K407" t="s">
@@ -24335,7 +24408,7 @@
         <v>35.799999999999997</v>
       </c>
       <c r="G408" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>41.000000000000007</v>
       </c>
       <c r="K408" t="s">
@@ -24385,7 +24458,7 @@
         <v>-8.2000000000000028</v>
       </c>
       <c r="G409" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-3.7999999999999954</v>
       </c>
       <c r="K409" t="s">
@@ -24435,7 +24508,7 @@
         <v>-22.1</v>
       </c>
       <c r="G410" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-15.600000000000001</v>
       </c>
       <c r="K410" t="s">
@@ -24485,7 +24558,7 @@
         <v>6.6999999999999957</v>
       </c>
       <c r="G411" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11.299999999999999</v>
       </c>
       <c r="K411" t="s">
@@ -24535,7 +24608,7 @@
         <v>55.6</v>
       </c>
       <c r="G412" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>57.6</v>
       </c>
       <c r="K412" t="s">
@@ -24585,7 +24658,7 @@
         <v>-41.900000000000006</v>
       </c>
       <c r="G413" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-35.500000000000007</v>
       </c>
       <c r="K413" t="s">
@@ -24635,7 +24708,7 @@
         <v>18</v>
       </c>
       <c r="G414" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>16.700000000000003</v>
       </c>
       <c r="K414" t="s">
@@ -24685,7 +24758,7 @@
         <v>41.000000000000007</v>
       </c>
       <c r="G415" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>42.4</v>
       </c>
       <c r="K415" t="s">
@@ -24734,7 +24807,7 @@
         <v>30.4</v>
       </c>
       <c r="G416" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>36.9</v>
       </c>
       <c r="K416" t="s">
@@ -24783,7 +24856,7 @@
         <v>22.700000000000003</v>
       </c>
       <c r="G417" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>31.9</v>
       </c>
       <c r="K417" t="s">
@@ -24832,7 +24905,7 @@
         <v>-4.2000000000000028</v>
       </c>
       <c r="G418" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.1000000000000005</v>
       </c>
       <c r="K418" t="s">
@@ -24881,7 +24954,7 @@
         <v>-16.899999999999999</v>
       </c>
       <c r="G419" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-12.200000000000001</v>
       </c>
       <c r="K419" t="s">
@@ -24930,7 +25003,7 @@
         <v>-8.8999999999999986</v>
       </c>
       <c r="G420" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2.2999999999999989</v>
       </c>
       <c r="K420" t="s">
@@ -24979,7 +25052,7 @@
         <v>17.100000000000001</v>
       </c>
       <c r="G421" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>27.6</v>
       </c>
       <c r="K421" t="s">
@@ -25028,7 +25101,7 @@
         <v>75.099999999999994</v>
       </c>
       <c r="G422" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>82.9</v>
       </c>
       <c r="K422" t="s">
@@ -25077,7 +25150,7 @@
         <v>6.7000000000000028</v>
       </c>
       <c r="G423" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>14.100000000000001</v>
       </c>
       <c r="K423" t="s">
@@ -25126,7 +25199,7 @@
         <v>44.7</v>
       </c>
       <c r="G424" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>49.4</v>
       </c>
       <c r="K424" t="s">
@@ -25175,7 +25248,7 @@
         <v>17.600000000000001</v>
       </c>
       <c r="G425" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>26.299999999999997</v>
       </c>
       <c r="K425" t="s">
@@ -25224,7 +25297,7 @@
         <v>-44.5</v>
       </c>
       <c r="G426" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-36</v>
       </c>
       <c r="H426" s="4" t="s">
@@ -25279,7 +25352,7 @@
         <v>-42.100000000000009</v>
       </c>
       <c r="G427" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-31.200000000000003</v>
       </c>
       <c r="H427" s="4" t="s">
@@ -25334,7 +25407,7 @@
         <v>-2</v>
       </c>
       <c r="G428" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.9000000000000004</v>
       </c>
       <c r="K428" t="s">
@@ -25383,7 +25456,7 @@
         <v>41.7</v>
       </c>
       <c r="G429" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>48.4</v>
       </c>
       <c r="K429" t="s">
@@ -25432,7 +25505,7 @@
         <v>-4.6999999999999957</v>
       </c>
       <c r="G430" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K430" t="s">
@@ -25481,7 +25554,7 @@
         <v>52.899999999999991</v>
       </c>
       <c r="G431" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>59.8</v>
       </c>
       <c r="K431" t="s">
@@ -25530,7 +25603,7 @@
         <v>-22.800000000000004</v>
       </c>
       <c r="G432" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-13.700000000000001</v>
       </c>
       <c r="K432" t="s">
@@ -25579,7 +25652,7 @@
         <v>-15.600000000000001</v>
       </c>
       <c r="G433" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-7.9999999999999982</v>
       </c>
       <c r="K433" t="s">
@@ -25628,7 +25701,7 @@
         <v>-19.899999999999999</v>
       </c>
       <c r="G434" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-14.1</v>
       </c>
       <c r="K434" t="s">
@@ -25677,7 +25750,7 @@
         <v>-15.5</v>
       </c>
       <c r="G435" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-7.7999999999999989</v>
       </c>
       <c r="K435" t="s">
@@ -25726,7 +25799,7 @@
         <v>-43.300000000000004</v>
       </c>
       <c r="G436" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-37.800000000000004</v>
       </c>
       <c r="K436" t="s">
@@ -25752,8 +25825,32 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:G2 E376 E437:G1048576 E377:F436 E3:F375 G3:G436 K1:M1">
+  <conditionalFormatting sqref="E1:G1 E376 E437:G1048576 E377:F436 E9:F375 G9:G436 K1:M1">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:F8">
     <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G8">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="num" val="0"/>

--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/Desktop - Ben’s MacBook Air/house_model_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFB83BC-D5E4-E643-A459-12D3225096A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C034762A-6711-8F45-9CC2-E388A0E4FCD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5246" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5247" uniqueCount="823">
   <si>
     <t>State</t>
   </si>
@@ -2539,6 +2539,9 @@
   </si>
   <si>
     <t>Jacob, Mitchell</t>
+  </si>
+  <si>
+    <t>Nelson, Gina</t>
   </si>
 </sst>
 </file>
@@ -19587,6 +19590,9 @@
         <f t="shared" si="5"/>
         <v>-9.7999999999999989</v>
       </c>
+      <c r="H319" s="4" t="s">
+        <v>822</v>
+      </c>
       <c r="I319" t="s">
         <v>417</v>
       </c>

--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/Desktop - Ben’s MacBook Air/house_model_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C034762A-6711-8F45-9CC2-E388A0E4FCD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD2A898D-1355-524B-8B4A-99999F3160F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5247" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5248" uniqueCount="824">
   <si>
     <t>State</t>
   </si>
@@ -2542,6 +2542,9 @@
   </si>
   <si>
     <t>Nelson, Gina</t>
+  </si>
+  <si>
+    <t>Dunlap, Matthew</t>
   </si>
 </sst>
 </file>
@@ -12498,6 +12501,9 @@
         <f t="shared" si="3"/>
         <v>-1.0999999999999996</v>
       </c>
+      <c r="H182" s="4" t="s">
+        <v>823</v>
+      </c>
       <c r="I182" s="4" t="s">
         <v>807</v>
       </c>

--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/Desktop - Ben’s MacBook Air/house_model_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD2A898D-1355-524B-8B4A-99999F3160F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB831DC2-4ADE-E24A-91D9-F27AC3BA5E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5248" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5332" uniqueCount="875">
   <si>
     <t>State</t>
   </si>
@@ -2545,6 +2545,159 @@
   </si>
   <si>
     <t>Dunlap, Matthew</t>
+  </si>
+  <si>
+    <t>Gallant, Christopher</t>
+  </si>
+  <si>
+    <t>Halpin, Patrick</t>
+  </si>
+  <si>
+    <t>LiPetri, Michael</t>
+  </si>
+  <si>
+    <t>Driscoll, Jeanine</t>
+  </si>
+  <si>
+    <t>Marks, George</t>
+  </si>
+  <si>
+    <t>Chou, Joseph</t>
+  </si>
+  <si>
+    <t>Valdez, Claire</t>
+  </si>
+  <si>
+    <t>Rivera, Melvin</t>
+  </si>
+  <si>
+    <t>Mizrahi, Lewis</t>
+  </si>
+  <si>
+    <t>Azumah, Joel</t>
+  </si>
+  <si>
+    <t>Lander, Brad</t>
+  </si>
+  <si>
+    <t>Moore, Jennifer</t>
+  </si>
+  <si>
+    <t>DeCillis, Mike</t>
+  </si>
+  <si>
+    <t>Lasher, Micah</t>
+  </si>
+  <si>
+    <t>Shinkle, Caroline</t>
+  </si>
+  <si>
+    <t>Avila Chevalier, Darializa</t>
+  </si>
+  <si>
+    <t>Williams, Jomo</t>
+  </si>
+  <si>
+    <t>Hysenaj, Diamant</t>
+  </si>
+  <si>
+    <t>Sapaskis, Stylo</t>
+  </si>
+  <si>
+    <t>Cinquemani, Joseph</t>
+  </si>
+  <si>
+    <t>Conley, Cait</t>
+  </si>
+  <si>
+    <t>Auringer, Jackie Mary</t>
+  </si>
+  <si>
+    <t>Oberacker, Peter</t>
+  </si>
+  <si>
+    <t>Ambrosio, Ralph</t>
+  </si>
+  <si>
+    <t>Constantino, Anthony</t>
+  </si>
+  <si>
+    <t>Gendebein, Blake</t>
+  </si>
+  <si>
+    <t>Buller, Kailee Marie</t>
+  </si>
+  <si>
+    <t>Gies, Aaron</t>
+  </si>
+  <si>
+    <t>Ellman, Elissa</t>
+  </si>
+  <si>
+    <t>Morelle, Joseph</t>
+  </si>
+  <si>
+    <t>McIntyre, Virginia</t>
+  </si>
+  <si>
+    <t>Hannon, Dennis</t>
+  </si>
+  <si>
+    <t>Okpareke, Ndidiamaka Ekwua Charlene</t>
+  </si>
+  <si>
+    <t>Cunningham, Gregory</t>
+  </si>
+  <si>
+    <t>Zamora, Martin</t>
+  </si>
+  <si>
+    <t>Honeycutt, Jenny Costa</t>
+  </si>
+  <si>
+    <t>Lacore, Nancy</t>
+  </si>
+  <si>
+    <t>Khalifa, Zion</t>
+  </si>
+  <si>
+    <t>Wallace, Dave</t>
+  </si>
+  <si>
+    <t>Flowers, Bernie</t>
+  </si>
+  <si>
+    <t>McDermott, George</t>
+  </si>
+  <si>
+    <t>Boafo, Adrian</t>
+  </si>
+  <si>
+    <t>Chaffee, Chris</t>
+  </si>
+  <si>
+    <t>Ficker, Robin</t>
+  </si>
+  <si>
+    <t>Collier, Scott</t>
+  </si>
+  <si>
+    <t>Riley, Cheryl</t>
+  </si>
+  <si>
+    <t>McAdams, Ben</t>
+  </si>
+  <si>
+    <t>Owen, Riley</t>
+  </si>
+  <si>
+    <t>Crosby, Peter</t>
+  </si>
+  <si>
+    <t>Udell, Kent</t>
+  </si>
+  <si>
+    <t>Larsen, Johnny</t>
   </si>
 </sst>
 </file>
@@ -2979,7 +3132,8 @@
     <col min="5" max="6" width="20.6640625" style="3" customWidth="1"/>
     <col min="7" max="7" width="30.1640625" style="3" customWidth="1"/>
     <col min="8" max="8" width="23.33203125" customWidth="1"/>
-    <col min="9" max="10" width="24.1640625" customWidth="1"/>
+    <col min="9" max="9" width="32.5" customWidth="1"/>
+    <col min="10" max="10" width="24.1640625" customWidth="1"/>
     <col min="11" max="11" width="13.6640625" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="18.6640625" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="28" hidden="1" customWidth="1"/>
@@ -12556,6 +12710,9 @@
         <f t="shared" si="3"/>
         <v>-8.4</v>
       </c>
+      <c r="I183" t="s">
+        <v>243</v>
+      </c>
       <c r="K183" t="s">
         <v>676</v>
       </c>
@@ -12605,6 +12762,12 @@
         <f t="shared" si="3"/>
         <v>26.700000000000003</v>
       </c>
+      <c r="H184" t="s">
+        <v>244</v>
+      </c>
+      <c r="I184" s="4" t="s">
+        <v>862</v>
+      </c>
       <c r="K184" t="s">
         <v>676</v>
       </c>
@@ -12654,6 +12817,12 @@
         <f t="shared" si="3"/>
         <v>31.9</v>
       </c>
+      <c r="H185" t="s">
+        <v>245</v>
+      </c>
+      <c r="I185" s="4" t="s">
+        <v>863</v>
+      </c>
       <c r="K185" t="s">
         <v>676</v>
       </c>
@@ -12703,6 +12872,12 @@
         <f t="shared" si="3"/>
         <v>81.600000000000009</v>
       </c>
+      <c r="H186" t="s">
+        <v>246</v>
+      </c>
+      <c r="I186" s="4" t="s">
+        <v>864</v>
+      </c>
       <c r="K186" t="s">
         <v>676</v>
       </c>
@@ -12752,6 +12927,12 @@
         <f t="shared" si="3"/>
         <v>41.5</v>
       </c>
+      <c r="H187" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="I187" s="4" t="s">
+        <v>866</v>
+      </c>
       <c r="K187" t="s">
         <v>676</v>
       </c>
@@ -12801,6 +12982,12 @@
         <f t="shared" si="3"/>
         <v>14.100000000000001</v>
       </c>
+      <c r="H188" t="s">
+        <v>248</v>
+      </c>
+      <c r="I188" s="4" t="s">
+        <v>867</v>
+      </c>
       <c r="K188" t="s">
         <v>676</v>
       </c>
@@ -12850,6 +13037,12 @@
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
+      <c r="H189" t="s">
+        <v>249</v>
+      </c>
+      <c r="I189" s="4" t="s">
+        <v>868</v>
+      </c>
       <c r="K189" t="s">
         <v>676</v>
       </c>
@@ -12899,6 +13092,12 @@
         <f t="shared" si="3"/>
         <v>64.199999999999989</v>
       </c>
+      <c r="H190" t="s">
+        <v>250</v>
+      </c>
+      <c r="I190" s="4" t="s">
+        <v>869</v>
+      </c>
       <c r="K190" t="s">
         <v>676</v>
       </c>
@@ -16096,7 +16295,7 @@
         <v>700</v>
       </c>
       <c r="T252" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="253" spans="1:20" x14ac:dyDescent="0.2">
@@ -16291,6 +16490,12 @@
         <f t="shared" si="4"/>
         <v>21.3</v>
       </c>
+      <c r="H256" t="s">
+        <v>323</v>
+      </c>
+      <c r="I256" s="4" t="s">
+        <v>856</v>
+      </c>
       <c r="K256" t="s">
         <v>675</v>
       </c>
@@ -16313,7 +16518,7 @@
         <v>700</v>
       </c>
       <c r="T256" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="257" spans="1:20" x14ac:dyDescent="0.2">
@@ -16340,6 +16545,12 @@
         <f t="shared" si="4"/>
         <v>6.5</v>
       </c>
+      <c r="H257" t="s">
+        <v>324</v>
+      </c>
+      <c r="I257" s="4" t="s">
+        <v>857</v>
+      </c>
       <c r="K257" t="s">
         <v>675</v>
       </c>
@@ -16362,7 +16573,7 @@
         <v>700</v>
       </c>
       <c r="T257" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="258" spans="1:20" x14ac:dyDescent="0.2">
@@ -16389,6 +16600,12 @@
         <f t="shared" ref="G258:G321" si="5">E258+6.9+1.5</f>
         <v>13.2</v>
       </c>
+      <c r="H258" t="s">
+        <v>325</v>
+      </c>
+      <c r="I258" s="4" t="s">
+        <v>858</v>
+      </c>
       <c r="K258" t="s">
         <v>675</v>
       </c>
@@ -16411,7 +16628,7 @@
         <v>700</v>
       </c>
       <c r="T258" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="259" spans="1:20" x14ac:dyDescent="0.2">
@@ -16438,6 +16655,12 @@
         <f t="shared" si="5"/>
         <v>-1.6999999999999993</v>
       </c>
+      <c r="H259" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="I259" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="K259" t="s">
         <v>676</v>
       </c>
@@ -16460,7 +16683,7 @@
         <v>700</v>
       </c>
       <c r="T259" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="260" spans="1:20" x14ac:dyDescent="0.2">
@@ -16487,6 +16710,12 @@
         <f t="shared" si="5"/>
         <v>-5.5</v>
       </c>
+      <c r="H260" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="I260" t="s">
+        <v>327</v>
+      </c>
       <c r="K260" t="s">
         <v>676</v>
       </c>
@@ -16509,7 +16738,7 @@
         <v>700</v>
       </c>
       <c r="T260" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="261" spans="1:20" x14ac:dyDescent="0.2">
@@ -16536,6 +16765,12 @@
         <f t="shared" si="5"/>
         <v>4.1000000000000005</v>
       </c>
+      <c r="H261" t="s">
+        <v>328</v>
+      </c>
+      <c r="I261" s="4" t="s">
+        <v>826</v>
+      </c>
       <c r="K261" t="s">
         <v>676</v>
       </c>
@@ -16558,7 +16793,7 @@
         <v>700</v>
       </c>
       <c r="T261" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="262" spans="1:20" x14ac:dyDescent="0.2">
@@ -16585,6 +16820,12 @@
         <f t="shared" si="5"/>
         <v>9.7000000000000011</v>
       </c>
+      <c r="H262" t="s">
+        <v>329</v>
+      </c>
+      <c r="I262" s="4" t="s">
+        <v>827</v>
+      </c>
       <c r="K262" t="s">
         <v>676</v>
       </c>
@@ -16607,7 +16848,7 @@
         <v>700</v>
       </c>
       <c r="T262" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="263" spans="1:20" x14ac:dyDescent="0.2">
@@ -16634,6 +16875,12 @@
         <f t="shared" si="5"/>
         <v>50.6</v>
       </c>
+      <c r="H263" t="s">
+        <v>330</v>
+      </c>
+      <c r="I263" s="4" t="s">
+        <v>828</v>
+      </c>
       <c r="K263" t="s">
         <v>676</v>
       </c>
@@ -16656,7 +16903,7 @@
         <v>700</v>
       </c>
       <c r="T263" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="264" spans="1:20" x14ac:dyDescent="0.2">
@@ -16683,6 +16930,12 @@
         <f t="shared" si="5"/>
         <v>14.8</v>
       </c>
+      <c r="H264" t="s">
+        <v>331</v>
+      </c>
+      <c r="I264" s="4" t="s">
+        <v>829</v>
+      </c>
       <c r="K264" t="s">
         <v>676</v>
       </c>
@@ -16705,7 +16958,7 @@
         <v>700</v>
       </c>
       <c r="T264" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="265" spans="1:20" x14ac:dyDescent="0.2">
@@ -16732,6 +16985,12 @@
         <f t="shared" si="5"/>
         <v>54.3</v>
       </c>
+      <c r="H265" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="I265" s="4" t="s">
+        <v>831</v>
+      </c>
       <c r="K265" t="s">
         <v>676</v>
       </c>
@@ -16754,7 +17013,7 @@
         <v>700</v>
       </c>
       <c r="T265" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="266" spans="1:20" x14ac:dyDescent="0.2">
@@ -16781,6 +17040,12 @@
         <f t="shared" si="5"/>
         <v>52.4</v>
       </c>
+      <c r="H266" t="s">
+        <v>333</v>
+      </c>
+      <c r="I266" s="4" t="s">
+        <v>832</v>
+      </c>
       <c r="K266" t="s">
         <v>676</v>
       </c>
@@ -16803,7 +17068,7 @@
         <v>700</v>
       </c>
       <c r="T266" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="267" spans="1:20" x14ac:dyDescent="0.2">
@@ -16830,6 +17095,12 @@
         <f t="shared" si="5"/>
         <v>49</v>
       </c>
+      <c r="H267" t="s">
+        <v>334</v>
+      </c>
+      <c r="I267" s="4" t="s">
+        <v>833</v>
+      </c>
       <c r="K267" t="s">
         <v>676</v>
       </c>
@@ -16852,7 +17123,7 @@
         <v>700</v>
       </c>
       <c r="T267" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="268" spans="1:20" x14ac:dyDescent="0.2">
@@ -16879,6 +17150,12 @@
         <f t="shared" si="5"/>
         <v>68.8</v>
       </c>
+      <c r="H268" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="I268" s="4" t="s">
+        <v>835</v>
+      </c>
       <c r="K268" t="s">
         <v>676</v>
       </c>
@@ -16901,7 +17178,7 @@
         <v>700</v>
       </c>
       <c r="T268" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="269" spans="1:20" x14ac:dyDescent="0.2">
@@ -16928,6 +17205,12 @@
         <f t="shared" si="5"/>
         <v>-16</v>
       </c>
+      <c r="H269" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="I269" s="6" t="s">
+        <v>336</v>
+      </c>
       <c r="K269" t="s">
         <v>676</v>
       </c>
@@ -16950,7 +17233,7 @@
         <v>700</v>
       </c>
       <c r="T269" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="270" spans="1:20" x14ac:dyDescent="0.2">
@@ -16977,6 +17260,12 @@
         <f t="shared" si="5"/>
         <v>72</v>
       </c>
+      <c r="H270" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="I270" s="6" t="s">
+        <v>838</v>
+      </c>
       <c r="K270" t="s">
         <v>676</v>
       </c>
@@ -16999,7 +17288,7 @@
         <v>700</v>
       </c>
       <c r="T270" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="271" spans="1:20" x14ac:dyDescent="0.2">
@@ -17026,6 +17315,12 @@
         <f t="shared" si="5"/>
         <v>67.7</v>
       </c>
+      <c r="H271" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="I271" s="4" t="s">
+        <v>840</v>
+      </c>
       <c r="K271" t="s">
         <v>676</v>
       </c>
@@ -17048,7 +17343,7 @@
         <v>700</v>
       </c>
       <c r="T271" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="272" spans="1:20" x14ac:dyDescent="0.2">
@@ -17075,6 +17370,12 @@
         <f t="shared" si="5"/>
         <v>40.200000000000003</v>
       </c>
+      <c r="H272" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="I272" s="4" t="s">
+        <v>841</v>
+      </c>
       <c r="K272" t="s">
         <v>676</v>
       </c>
@@ -17097,7 +17398,7 @@
         <v>700</v>
       </c>
       <c r="T272" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="273" spans="1:20" x14ac:dyDescent="0.2">
@@ -17124,6 +17425,12 @@
         <f t="shared" si="5"/>
         <v>56.699999999999996</v>
       </c>
+      <c r="H273" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="I273" s="4" t="s">
+        <v>842</v>
+      </c>
       <c r="K273" t="s">
         <v>676</v>
       </c>
@@ -17146,7 +17453,7 @@
         <v>700</v>
       </c>
       <c r="T273" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="274" spans="1:20" x14ac:dyDescent="0.2">
@@ -17173,6 +17480,12 @@
         <f t="shared" si="5"/>
         <v>41.5</v>
       </c>
+      <c r="H274" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="I274" s="4" t="s">
+        <v>843</v>
+      </c>
       <c r="K274" t="s">
         <v>663</v>
       </c>
@@ -17195,7 +17508,7 @@
         <v>700</v>
       </c>
       <c r="T274" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="275" spans="1:20" x14ac:dyDescent="0.2">
@@ -17222,6 +17535,12 @@
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
+      <c r="H275" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="I275" s="6" t="s">
+        <v>342</v>
+      </c>
       <c r="K275" t="s">
         <v>663</v>
       </c>
@@ -17244,7 +17563,7 @@
         <v>700</v>
       </c>
       <c r="T275" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="276" spans="1:20" x14ac:dyDescent="0.2">
@@ -17271,6 +17590,12 @@
         <f t="shared" si="5"/>
         <v>11.7</v>
       </c>
+      <c r="H276" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="I276" s="4" t="s">
+        <v>845</v>
+      </c>
       <c r="K276" t="s">
         <v>663</v>
       </c>
@@ -17293,7 +17618,7 @@
         <v>700</v>
       </c>
       <c r="T276" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="277" spans="1:20" x14ac:dyDescent="0.2">
@@ -17320,6 +17645,12 @@
         <f t="shared" si="5"/>
         <v>10.200000000000001</v>
       </c>
+      <c r="H277" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="I277" s="4" t="s">
+        <v>846</v>
+      </c>
       <c r="K277" t="s">
         <v>663</v>
       </c>
@@ -17342,7 +17673,7 @@
         <v>700</v>
       </c>
       <c r="T277" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="278" spans="1:20" x14ac:dyDescent="0.2">
@@ -17370,6 +17701,12 @@
         <f t="shared" si="5"/>
         <v>22.6</v>
       </c>
+      <c r="H278" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="I278" s="4" t="s">
+        <v>847</v>
+      </c>
       <c r="K278" t="s">
         <v>663</v>
       </c>
@@ -17392,7 +17729,7 @@
         <v>700</v>
       </c>
       <c r="T278" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="279" spans="1:20" x14ac:dyDescent="0.2">
@@ -17419,6 +17756,12 @@
         <f t="shared" si="5"/>
         <v>-12.299999999999999</v>
       </c>
+      <c r="H279" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="I279" s="4" t="s">
+        <v>848</v>
+      </c>
       <c r="K279" t="s">
         <v>663</v>
       </c>
@@ -17441,7 +17784,7 @@
         <v>700</v>
       </c>
       <c r="T279" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="280" spans="1:20" x14ac:dyDescent="0.2">
@@ -17468,6 +17811,12 @@
         <f t="shared" si="5"/>
         <v>16.100000000000001</v>
       </c>
+      <c r="H280" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="I280" s="4" t="s">
+        <v>850</v>
+      </c>
       <c r="K280" t="s">
         <v>663</v>
       </c>
@@ -17490,7 +17839,7 @@
         <v>700</v>
       </c>
       <c r="T280" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="281" spans="1:20" x14ac:dyDescent="0.2">
@@ -17517,6 +17866,12 @@
         <f t="shared" si="5"/>
         <v>-12.6</v>
       </c>
+      <c r="H281" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="I281" s="6" t="s">
+        <v>348</v>
+      </c>
       <c r="K281" t="s">
         <v>663</v>
       </c>
@@ -17539,7 +17894,7 @@
         <v>700</v>
       </c>
       <c r="T281" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="282" spans="1:20" x14ac:dyDescent="0.2">
@@ -17566,6 +17921,12 @@
         <f t="shared" si="5"/>
         <v>-14.700000000000003</v>
       </c>
+      <c r="H282" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="I282" s="6" t="s">
+        <v>349</v>
+      </c>
       <c r="K282" t="s">
         <v>663</v>
       </c>
@@ -17588,7 +17949,7 @@
         <v>700</v>
       </c>
       <c r="T282" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="283" spans="1:20" x14ac:dyDescent="0.2">
@@ -17615,6 +17976,12 @@
         <f t="shared" si="5"/>
         <v>26.799999999999997</v>
       </c>
+      <c r="H283" s="6" t="s">
+        <v>853</v>
+      </c>
+      <c r="I283" s="4" t="s">
+        <v>854</v>
+      </c>
       <c r="K283" t="s">
         <v>663</v>
       </c>
@@ -17637,7 +18004,7 @@
         <v>700</v>
       </c>
       <c r="T283" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="284" spans="1:20" x14ac:dyDescent="0.2">
@@ -17664,6 +18031,12 @@
         <f t="shared" si="5"/>
         <v>27.700000000000003</v>
       </c>
+      <c r="H284" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="I284" s="4" t="s">
+        <v>855</v>
+      </c>
       <c r="K284" t="s">
         <v>663</v>
       </c>
@@ -17686,7 +18059,7 @@
         <v>700</v>
       </c>
       <c r="T284" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="285" spans="1:20" x14ac:dyDescent="0.2">
@@ -21033,6 +21406,12 @@
         <f t="shared" si="6"/>
         <v>-4.6999999999999993</v>
       </c>
+      <c r="H345" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="I345" s="4" t="s">
+        <v>859</v>
+      </c>
       <c r="K345" t="s">
         <v>677</v>
       </c>
@@ -21082,6 +21461,9 @@
         <f t="shared" si="6"/>
         <v>-5.6</v>
       </c>
+      <c r="H346" s="4" t="s">
+        <v>861</v>
+      </c>
       <c r="I346" t="s">
         <v>467</v>
       </c>
@@ -24027,6 +24409,12 @@
         <f t="shared" si="7"/>
         <v>32</v>
       </c>
+      <c r="H400" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="I400" s="4" t="s">
+        <v>871</v>
+      </c>
       <c r="K400" t="s">
         <v>666</v>
       </c>
@@ -24076,6 +24464,12 @@
         <f t="shared" si="7"/>
         <v>-20.5</v>
       </c>
+      <c r="H401" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="I401" s="6" t="s">
+        <v>570</v>
+      </c>
       <c r="K401" t="s">
         <v>666</v>
       </c>
@@ -24125,6 +24519,12 @@
         <f t="shared" si="7"/>
         <v>-32.9</v>
       </c>
+      <c r="H402" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="I402" s="6" t="s">
+        <v>571</v>
+      </c>
       <c r="K402" t="s">
         <v>666</v>
       </c>
@@ -24173,6 +24573,12 @@
       <c r="G403" s="3">
         <f t="shared" si="7"/>
         <v>-24</v>
+      </c>
+      <c r="H403" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="I403" s="6" t="s">
+        <v>572</v>
       </c>
       <c r="K403" t="s">
         <v>666</v>

--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/Desktop - Ben’s MacBook Air/house_model_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB831DC2-4ADE-E24A-91D9-F27AC3BA5E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9652D8DB-348E-2B41-BF29-C9FEFEEA0C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5332" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5333" uniqueCount="876">
   <si>
     <t>State</t>
   </si>
@@ -2698,6 +2698,9 @@
   </si>
   <si>
     <t>Larsen, Johnny</t>
+  </si>
+  <si>
+    <t>Schwartz, Dan</t>
   </si>
 </sst>
 </file>
@@ -3521,7 +3524,7 @@
         <v>-10</v>
       </c>
       <c r="G9" s="3">
-        <f t="shared" ref="G2:G65" si="1">E9+6.9+1.5</f>
+        <f t="shared" ref="G9:G65" si="1">E9+6.9+1.5</f>
         <v>-4.6999999999999993</v>
       </c>
       <c r="K9" t="s">
@@ -12710,6 +12713,9 @@
         <f t="shared" si="3"/>
         <v>-8.4</v>
       </c>
+      <c r="H183" s="4" t="s">
+        <v>875</v>
+      </c>
       <c r="I183" t="s">
         <v>243</v>
       </c>
@@ -26243,8 +26249,8 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:G1 E376 E437:G1048576 E377:F436 E9:F375 G9:G436 K1:M1">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="E2:F8">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="num" val="0"/>
@@ -26255,8 +26261,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:F8">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="E1:G1 E376 E437:G1048576 E377:F436 E9:F375 G9:G436 K1:M1">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="num" val="0"/>

--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/Desktop - Ben’s MacBook Air/house_model_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9652D8DB-348E-2B41-BF29-C9FEFEEA0C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D9DA56F-4475-4949-96C6-6CF413993FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5333" uniqueCount="876">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5345" uniqueCount="882">
   <si>
     <t>State</t>
   </si>
@@ -2701,6 +2701,24 @@
   </si>
   <si>
     <t>Schwartz, Dan</t>
+  </si>
+  <si>
+    <t>Kingston, James</t>
+  </si>
+  <si>
+    <t>Martin, Kevin</t>
+  </si>
+  <si>
+    <t>DeLancy, Pamela</t>
+  </si>
+  <si>
+    <t>Peterson, Christy</t>
+  </si>
+  <si>
+    <t>Laubacher, Ellen</t>
+  </si>
+  <si>
+    <t>Bennett, Tim</t>
   </si>
 </sst>
 </file>
@@ -7104,6 +7122,9 @@
         <f t="shared" si="2"/>
         <v>64.3</v>
       </c>
+      <c r="I75" s="4" t="s">
+        <v>879</v>
+      </c>
       <c r="K75" t="s">
         <v>666</v>
       </c>
@@ -7153,6 +7174,9 @@
         <f t="shared" si="2"/>
         <v>48.199999999999996</v>
       </c>
+      <c r="H76" t="s">
+        <v>86</v>
+      </c>
       <c r="K76" t="s">
         <v>666</v>
       </c>
@@ -7251,6 +7275,12 @@
         <f t="shared" si="2"/>
         <v>-9.9</v>
       </c>
+      <c r="H78" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="K78" t="s">
         <v>679</v>
       </c>
@@ -7300,6 +7330,9 @@
         <f t="shared" si="2"/>
         <v>-0.69999999999999929</v>
       </c>
+      <c r="I79" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="K79" t="s">
         <v>666</v>
       </c>
@@ -7349,6 +7382,9 @@
         <f t="shared" si="2"/>
         <v>28.200000000000003</v>
       </c>
+      <c r="H80" t="s">
+        <v>90</v>
+      </c>
       <c r="K80" t="s">
         <v>666</v>
       </c>
@@ -7398,6 +7434,12 @@
         <f t="shared" si="2"/>
         <v>23.4</v>
       </c>
+      <c r="H81" t="s">
+        <v>91</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>881</v>
+      </c>
       <c r="K81" t="s">
         <v>666</v>
       </c>
@@ -7447,6 +7489,9 @@
         <f t="shared" si="2"/>
         <v>6.6000000000000005</v>
       </c>
+      <c r="I82" t="s">
+        <v>92</v>
+      </c>
       <c r="K82" t="s">
         <v>666</v>
       </c>
@@ -9193,6 +9238,9 @@
       <c r="H117" s="4" t="s">
         <v>820</v>
       </c>
+      <c r="I117" s="4" t="s">
+        <v>876</v>
+      </c>
       <c r="K117" t="s">
         <v>677</v>
       </c>
@@ -9468,6 +9516,9 @@
       <c r="H122" t="s">
         <v>135</v>
       </c>
+      <c r="I122" s="4" t="s">
+        <v>877</v>
+      </c>
       <c r="K122" t="s">
         <v>677</v>
       </c>
@@ -9684,6 +9735,9 @@
       <c r="G126" s="3">
         <f t="shared" si="2"/>
         <v>-13.499999999999998</v>
+      </c>
+      <c r="H126" s="4" t="s">
+        <v>878</v>
       </c>
       <c r="I126" s="4" t="s">
         <v>142</v>

--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Desktop/Desktop - Ben’s MacBook Air/house_model_python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D9DA56F-4475-4949-96C6-6CF413993FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{EE18D553-BA91-8144-86B9-DEEDDF477CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -73,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5345" uniqueCount="882">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5350" uniqueCount="886">
   <si>
     <t>State</t>
   </si>
@@ -2719,6 +2720,18 @@
   </si>
   <si>
     <t>Bennett, Tim</t>
+  </si>
+  <si>
+    <t>Rutinel, Manny</t>
+  </si>
+  <si>
+    <t>Kiros, Milat</t>
+  </si>
+  <si>
+    <t>Romero, Dwayne</t>
+  </si>
+  <si>
+    <t>Killin, Jessica</t>
   </si>
 </sst>
 </file>
@@ -4336,7 +4349,7 @@
         <v>699</v>
       </c>
       <c r="T24" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.2">
@@ -7122,6 +7135,9 @@
         <f t="shared" si="2"/>
         <v>64.3</v>
       </c>
+      <c r="H75" s="4" t="s">
+        <v>883</v>
+      </c>
       <c r="I75" s="4" t="s">
         <v>879</v>
       </c>
@@ -7147,7 +7163,7 @@
         <v>700</v>
       </c>
       <c r="T75" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.2">
@@ -7199,7 +7215,7 @@
         <v>700</v>
       </c>
       <c r="T76" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.2">
@@ -7226,6 +7242,12 @@
         <f t="shared" si="2"/>
         <v>-1.2999999999999989</v>
       </c>
+      <c r="H77" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="K77" t="s">
         <v>666</v>
       </c>
@@ -7248,7 +7270,7 @@
         <v>700</v>
       </c>
       <c r="T77" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.2">
@@ -7303,7 +7325,7 @@
         <v>700</v>
       </c>
       <c r="T78" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.2">
@@ -7330,6 +7352,9 @@
         <f t="shared" si="2"/>
         <v>-0.69999999999999929</v>
       </c>
+      <c r="H79" s="4" t="s">
+        <v>885</v>
+      </c>
       <c r="I79" s="6" t="s">
         <v>89</v>
       </c>
@@ -7355,7 +7380,7 @@
         <v>700</v>
       </c>
       <c r="T79" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.2">
@@ -7407,7 +7432,7 @@
         <v>700</v>
       </c>
       <c r="T80" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.2">
@@ -7462,7 +7487,7 @@
         <v>700</v>
       </c>
       <c r="T81" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.2">
@@ -7489,6 +7514,9 @@
         <f t="shared" si="2"/>
         <v>6.6000000000000005</v>
       </c>
+      <c r="H82" s="4" t="s">
+        <v>882</v>
+      </c>
       <c r="I82" t="s">
         <v>92</v>
       </c>
@@ -7514,7 +7542,7 @@
         <v>700</v>
       </c>
       <c r="T82" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.2">

--- a/House Model Data.xlsx
+++ b/House Model Data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{EE18D553-BA91-8144-86B9-DEEDDF477CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
+    <workbookView xWindow="1460" yWindow="1540" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
   <sheets>
     <sheet name="House Model Data" sheetId="1" r:id="rId1"/>
